--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>I WANNA ROCK</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B132" t="str">
         <v/>
@@ -5391,7 +5391,7 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>I WANNA ROCK - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G132" t="str">
         <v>3:44</v>
@@ -5409,7 +5409,7 @@
         <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L132" t="str">
-        <v>I WANNA ROCK - Cash Cobain</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="133">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:L204"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B39" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>9 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4426,13 +4426,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Therapy at the Club</v>
+        <v>Smoking pt. 2 (feat. Rick Ross)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://music.apple.com/us/song/smoking-pt-2-feat-rick-ross/1894333434</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-08</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Wave Gods 2: Cosmos Brothers</v>
       </c>
       <c r="G107" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H107" t="str">
-        <v>FLO</v>
+        <v>French Montana</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v>https://music.apple.com/us/album/smoking-pt-2-feat-rick-ross/1894333428</v>
       </c>
       <c r="L107" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Smoking pt. 2 (feat. Rick Ross) - French Montana</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>linknb</v>
+        <v>Therapy at the Club</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-08</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>new avatar</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G108" t="str">
-        <v>1:55</v>
+        <v>2:47</v>
       </c>
       <c r="H108" t="str">
-        <v>Kelela</v>
+        <v>FLO</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
       </c>
       <c r="L108" t="str">
-        <v>linknb - Kelela</v>
+        <v>Therapy at the Club - FLO</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-08</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G109" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H109" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L109" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Baby</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-08</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Baby - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G110" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H110" t="str">
-        <v>Prospa</v>
+        <v>elkan</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L110" t="str">
-        <v>Baby - Prospa</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Baby</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-08</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>Baby - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>2:39</v>
+        <v>3:13</v>
       </c>
       <c r="H111" t="str">
-        <v>Russell Dickerson</v>
+        <v>Prospa</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/baby/1895418297</v>
       </c>
       <c r="L111" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Baby - Prospa</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Bed of Roses</v>
+        <v>Boots (feat. Fetty Wap)</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-08</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Boots (feat. Fetty Wap) - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H112" t="str">
-        <v>Teyana Taylor</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
       </c>
       <c r="L112" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Bed of Roses</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-08</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>Bed of Roses - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H113" t="str">
-        <v>Bruno Mars</v>
+        <v>Teyana Taylor</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
       </c>
       <c r="L113" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Bed of Roses - Teyana Taylor</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Big Dog</v>
+        <v>Lo Arriesgo Todo</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-08</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Big Dog - Single</v>
+        <v>Lo Arriesgo Todo - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H114" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
       </c>
       <c r="L114" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Lo Arriesgo Todo - Bruno Mars</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Eastside Girls</v>
+        <v>Big Dog</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-08</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Big Dog - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H115" t="str">
-        <v>MUNA</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
       </c>
       <c r="L115" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>Big Dog - The Last Dinner Party</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>In The Stars</v>
+        <v>Eastside Girls</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-08</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Foreign Tongues</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G116" t="str">
-        <v>4:13</v>
+        <v>3:50</v>
       </c>
       <c r="H116" t="str">
-        <v>The Rolling Stones</v>
+        <v>MUNA</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
       </c>
       <c r="L116" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Eastside Girls - MUNA</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Home to Us</v>
+        <v>In The Stars</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-08</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Foreign Tongues</v>
       </c>
       <c r="G117" t="str">
-        <v>3:11</v>
+        <v>4:13</v>
       </c>
       <c r="H117" t="str">
-        <v>Paul McCartney</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
       </c>
       <c r="L117" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>In The Stars - The Rolling Stones</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Hurts Like You</v>
+        <v>Home to Us</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-08</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Night Champion</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G118" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H118" t="str">
-        <v>Koe Wetzel</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
       </c>
       <c r="L118" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Home to Us - Paul McCartney</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Find Us Again</v>
+        <v>Hurts Like You</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-08</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Find Us Again - Single</v>
+        <v>The Night Champion</v>
       </c>
       <c r="G119" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H119" t="str">
-        <v>Xavi</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
       </c>
       <c r="L119" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hurts Like You - Koe Wetzel</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Tied Up</v>
+        <v>Find Us Again</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-08</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Tied Up - Single</v>
+        <v>Find Us Again - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H120" t="str">
-        <v>Khalid</v>
+        <v>Xavi</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
       </c>
       <c r="L120" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Find Us Again - Xavi</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Antes De Ti</v>
+        <v>Tied Up</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-08</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Tied Up - Single</v>
       </c>
       <c r="G121" t="str">
         <v>2:56</v>
       </c>
       <c r="H121" t="str">
-        <v>Silvana Estrada</v>
+        <v>Khalid</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/khalid/82842423</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
       </c>
       <c r="L121" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Tied Up - Khalid</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>En La Misma Cama</v>
+        <v>Antes De Ti</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-08</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>MUDA</v>
+        <v>Antes De Ti - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Carín León</v>
+        <v>Silvana Estrada</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
       </c>
       <c r="L122" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Antes De Ti - Silvana Estrada</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>lovergirl</v>
+        <v>En La Misma Cama</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-08</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>locket deluxe</v>
+        <v>MUDA</v>
       </c>
       <c r="G123" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H123" t="str">
-        <v>Madison Beer</v>
+        <v>Carín León</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
       </c>
       <c r="L123" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>En La Misma Cama - Carín León</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>PANIKI</v>
+        <v>lovergirl</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-08</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>locket deluxe</v>
       </c>
       <c r="G124" t="str">
-        <v>2:36</v>
+        <v>3:21</v>
       </c>
       <c r="H124" t="str">
-        <v>Chuyin</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
       </c>
       <c r="L124" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>lovergirl - Madison Beer</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>DesOrden</v>
+        <v>PANIKI</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-08</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>DesOrden - Single</v>
+        <v>Los Locos Nunca Mueren</v>
       </c>
       <c r="G125" t="str">
         <v>2:36</v>
       </c>
       <c r="H125" t="str">
-        <v>Alleh</v>
+        <v>Chuyin</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/paniki/1892533803</v>
       </c>
       <c r="L125" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>PANIKI - Chuyin</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>The Payoff</v>
+        <v>DesOrden</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-08</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>The Payoff - Single</v>
+        <v>DesOrden - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>5:51</v>
+        <v>2:36</v>
       </c>
       <c r="H126" t="str">
-        <v>Father John Misty</v>
+        <v>Alleh</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/desorden/1896069663</v>
       </c>
       <c r="L126" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>DesOrden - Alleh</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>The Weak</v>
+        <v>LA Nights</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-08</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Ville</v>
       </c>
       <c r="G127" t="str">
-        <v>3:15</v>
+        <v>2:18</v>
       </c>
       <c r="H127" t="str">
-        <v>Iceage</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
       </c>
       <c r="L127" t="str">
-        <v>The Weak - Iceage</v>
+        <v>LA Nights - Trap Dickey</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Life Of The Faaji</v>
+        <v>The Payoff</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-08</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Fuji Xtra</v>
+        <v>The Payoff - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:29</v>
+        <v>5:51</v>
       </c>
       <c r="H128" t="str">
-        <v>Adekunle Gold</v>
+        <v>Father John Misty</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
       </c>
       <c r="L128" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>The Payoff - Father John Misty</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Satisfy</v>
+        <v>The Weak</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-08</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Satisfy - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G129" t="str">
-        <v>3:06</v>
+        <v>3:15</v>
       </c>
       <c r="H129" t="str">
-        <v>Calvin Harris</v>
+        <v>Iceage</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
       </c>
       <c r="L129" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>The Weak - Iceage</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>Life Of The Faaji</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-08</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>Fuji Xtra</v>
       </c>
       <c r="G130" t="str">
-        <v>3:03</v>
+        <v>2:29</v>
       </c>
       <c r="H130" t="str">
-        <v>DEAN</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
       </c>
       <c r="L130" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>Life Of The Faaji - Adekunle Gold</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Satisfy</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-08</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Satisfy - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:48</v>
+        <v>3:06</v>
       </c>
       <c r="H131" t="str">
-        <v>6LACK</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
       </c>
       <c r="L131" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Satisfy - Calvin Harris</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>I Wanna Rock</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-08</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:44</v>
+        <v>3:03</v>
       </c>
       <c r="H132" t="str">
-        <v>Cash Cobain</v>
+        <v>DEAN</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/dean/2770824</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
       </c>
       <c r="L132" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>Ashin' the Blunt</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-08</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G133" t="str">
-        <v>4:33</v>
+        <v>3:48</v>
       </c>
       <c r="H133" t="str">
-        <v>James Blake</v>
+        <v>6LACK</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
       </c>
       <c r="L133" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>Ashin' the Blunt - 6LACK</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>One Two Police</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-08</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>One Two Police - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:46</v>
+        <v>3:44</v>
       </c>
       <c r="H134" t="str">
-        <v>BUNT.</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L134" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>Trying Times - A COLORS SHOW</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-08</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>Trying Times - A COLORS SHOW - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:16</v>
+        <v>4:33</v>
       </c>
       <c r="H135" t="str">
-        <v>Stephen Sanchez</v>
+        <v>James Blake</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
       </c>
       <c r="L135" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>Trying Times - A COLORS SHOW - James Blake</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Illuminate</v>
+        <v>One Two Police</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-08</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>One Two Police - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:03</v>
+        <v>2:46</v>
       </c>
       <c r="H136" t="str">
-        <v>Jessie Reyez</v>
+        <v>BUNT.</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
       </c>
       <c r="L136" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>One Two Police - BUNT.</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>OKAY!</v>
+        <v>HOME TO MOTHER</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-08</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>OKAY! - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G137" t="str">
-        <v>4:34</v>
+        <v>3:16</v>
       </c>
       <c r="H137" t="str">
-        <v>Forrest Frank</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
       </c>
       <c r="L137" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>HOME TO MOTHER - Stephen Sanchez</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>FLOW</v>
+        <v>Illuminate</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-08</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>FLOW - Single</v>
+        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>4:20</v>
+        <v>3:03</v>
       </c>
       <c r="H138" t="str">
-        <v>iZaak</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
       </c>
       <c r="L138" t="str">
-        <v>FLOW - iZaak</v>
+        <v>Illuminate - Jessie Reyez</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>aiaiaiaiai</v>
+        <v>OKAY!</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-08</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>OKAY! - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:20</v>
+        <v>4:34</v>
       </c>
       <c r="H139" t="str">
-        <v>Mau y Ricky</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/okay/1896077066</v>
       </c>
       <c r="L139" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>OKAY! - Forrest Frank</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Control</v>
+        <v>FLOW</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-08</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>God Must Really Love Me</v>
+        <v>FLOW - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>2:32</v>
+        <v>4:20</v>
       </c>
       <c r="H140" t="str">
-        <v>Tori Kelly</v>
+        <v>iZaak</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/flow/1895961693</v>
       </c>
       <c r="L140" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>FLOW - iZaak</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ORIGAMI!</v>
+        <v>aiaiaiaiai</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-08</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>aiaiaiaiai - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:34</v>
+        <v>2:20</v>
       </c>
       <c r="H141" t="str">
-        <v>Kesha</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
       </c>
       <c r="L141" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>aiaiaiaiai - Mau y Ricky</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Love Is Kind</v>
+        <v>Control</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-08</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>God Must Really Love Me</v>
       </c>
       <c r="G142" t="str">
-        <v>4:07</v>
+        <v>2:32</v>
       </c>
       <c r="H142" t="str">
-        <v>The Chainsmokers</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/control/1895974889</v>
       </c>
       <c r="L142" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>Control - Tori Kelly</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Feathers In A Storm</v>
+        <v>ORIGAMI!</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-08</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Let It Die Here</v>
+        <v>ORIGAMI! - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:00</v>
+        <v>2:34</v>
       </c>
       <c r="H143" t="str">
-        <v>Linda Perry</v>
+        <v>Kesha</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/kesha/334854763</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/origami/1892544026</v>
       </c>
       <c r="L143" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>ORIGAMI! - Kesha</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Playing God</v>
+        <v>Love Is Kind</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-08</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Decades</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G144" t="str">
-        <v>3:39</v>
+        <v>4:07</v>
       </c>
       <c r="H144" t="str">
-        <v>Motionless In White</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
       </c>
       <c r="L144" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Love Is Kind - The Chainsmokers</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Cut</v>
+        <v>Feathers In A Storm</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-08</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>VINDICATE</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G145" t="str">
-        <v>3:59</v>
+        <v>4:00</v>
       </c>
       <c r="H145" t="str">
-        <v>Black Veil Brides</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
       </c>
       <c r="L145" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Feathers In A Storm - Linda Perry</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Freaking Out</v>
+        <v>Playing God</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-08</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Over Before You Know It</v>
+        <v>Decades</v>
       </c>
       <c r="G146" t="str">
-        <v>3:03</v>
+        <v>3:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Michigander</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
       </c>
       <c r="L146" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Playing God - Motionless In White</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>FIYAH</v>
+        <v>Cut</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-08</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>FIYAH - Single</v>
+        <v>VINDICATE</v>
       </c>
       <c r="G147" t="str">
-        <v>3:12</v>
+        <v>3:59</v>
       </c>
       <c r="H147" t="str">
-        <v>YG Marley</v>
+        <v>Black Veil Brides</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/cut/1879494510</v>
       </c>
       <c r="L147" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Cut - Black Veil Brides</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Ten to Midnight</v>
+        <v>Freaking Out</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-08</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Wild</v>
+        <v>Over Before You Know It</v>
       </c>
       <c r="G148" t="str">
-        <v>3:12</v>
+        <v>3:03</v>
       </c>
       <c r="H148" t="str">
-        <v>Ashley McBryde</v>
+        <v>Michigander</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
       </c>
       <c r="L148" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>Freaking Out - Michigander</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Carry On</v>
+        <v>FIYAH</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-08</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Carry On - Single</v>
+        <v>FIYAH - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H149" t="str">
-        <v>Kenny Chesney</v>
+        <v>YG Marley</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
       </c>
       <c r="L149" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>FIYAH - YG Marley</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>[PRESS]</v>
+        <v>Ten to Midnight</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-08</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G150" t="str">
-        <v>1:40</v>
+        <v>3:12</v>
       </c>
       <c r="H150" t="str">
-        <v>Armani White</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
       </c>
       <c r="L150" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Ten to Midnight - Ashley McBryde</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>Carry On</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-08</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Carry On - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>3:17</v>
+        <v>3:00</v>
       </c>
       <c r="H151" t="str">
-        <v>Myles Smith</v>
+        <v>Kenny Chesney</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
       </c>
       <c r="L151" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>Carry On - Kenny Chesney</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>[PRESS]</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-08</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>[PRESS] - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:53</v>
+        <v>1:40</v>
       </c>
       <c r="H152" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Armani White</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/press/1895898254</v>
       </c>
       <c r="L152" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>[PRESS] - Armani White</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Wide Eyed</v>
+        <v>Hold Me In The Dark</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-08</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Wide Eyed</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G153" t="str">
-        <v>3:24</v>
+        <v>3:17</v>
       </c>
       <c r="H153" t="str">
-        <v>Mack Keane</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
       </c>
       <c r="L153" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Hold Me In The Dark - Myles Smith</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Changes</v>
+        <v>Lo Que Me Pasa Con Vos</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-08</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Changes - Single</v>
+        <v>Lo Que Me Pasa Con Vos - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:18</v>
+        <v>2:53</v>
       </c>
       <c r="H154" t="str">
-        <v>Tommy Richman</v>
+        <v>Sebastián Yatra</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
       </c>
       <c r="L154" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-08</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="G155" t="str">
-        <v>4:33</v>
+        <v>3:24</v>
       </c>
       <c r="H155" t="str">
-        <v>The War And Treaty</v>
+        <v>Mack Keane</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
       </c>
       <c r="L155" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Wide Eyed - Mack Keane</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>depressed on the internet</v>
+        <v>Changes</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-08</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>Changes - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:57</v>
+        <v>3:18</v>
       </c>
       <c r="H156" t="str">
-        <v>Bea Miller</v>
+        <v>Tommy Richman</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/changes/1895418156</v>
       </c>
       <c r="L156" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Changes - Tommy Richman</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Dear Burt</v>
+        <v>Don't Say Goodbye</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-08</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>The Story of Michael and Tanya</v>
       </c>
       <c r="G157" t="str">
-        <v>2:53</v>
+        <v>4:33</v>
       </c>
       <c r="H157" t="str">
-        <v>Stephan Moccio</v>
+        <v>The War And Treaty</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
       </c>
       <c r="L157" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>Don't Say Goodbye - The War And Treaty</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Alla Blues</v>
+        <v>depressed on the internet</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-08</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Black Mozart</v>
+        <v>depressed on the internet - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:50</v>
+        <v>2:57</v>
       </c>
       <c r="H158" t="str">
-        <v>Jon Batiste</v>
+        <v>Bea Miller</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
       </c>
       <c r="L158" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>depressed on the internet - Bea Miller</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Think About Me</v>
+        <v>Dear Burt</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-08</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Think About Me - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G159" t="str">
-        <v>2:39</v>
+        <v>2:53</v>
       </c>
       <c r="H159" t="str">
-        <v>Gabriella Rose</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
       </c>
       <c r="L159" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>Dear Burt - Stephan Moccio</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Meet Again</v>
+        <v>Alla Blues</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-08</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Meet Again - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G160" t="str">
-        <v>3:26</v>
+        <v>2:50</v>
       </c>
       <c r="H160" t="str">
-        <v>Kaskade</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
       </c>
       <c r="L160" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Alla Blues - Jon Batiste</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Happy Now</v>
+        <v>Think About Me</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-08</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>The Afterparty</v>
+        <v>Think About Me - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:42</v>
+        <v>2:39</v>
       </c>
       <c r="H161" t="str">
-        <v>Lykke Li</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
       </c>
       <c r="L161" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Think About Me - Gabriella Rose</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Oblivion</v>
+        <v>Meet Again</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-08</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Oblivion - Single</v>
+        <v>Meet Again - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:21</v>
+        <v>3:26</v>
       </c>
       <c r="H162" t="str">
-        <v>Agents Of Time</v>
+        <v>Kaskade</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
       </c>
       <c r="L162" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>Meet Again - Kaskade</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Happy Now</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-08</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G163" t="str">
-        <v>4:03</v>
+        <v>2:42</v>
       </c>
       <c r="H163" t="str">
-        <v>Papa Roach</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
       </c>
       <c r="L163" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Happy Now - Lykke Li</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Top of the Hill</v>
+        <v>Oblivion</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-08</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>Oblivion - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>1:50</v>
+        <v>2:21</v>
       </c>
       <c r="H164" t="str">
-        <v>DDG</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
       </c>
       <c r="L164" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>Oblivion - Agents Of Time</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Oh Savannah</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-08</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Change Of Plans</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:05</v>
+        <v>4:03</v>
       </c>
       <c r="H165" t="str">
-        <v>49 Winchester</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
       </c>
       <c r="L165" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Top of the Hill</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-08</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Top of the Hill - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:29</v>
+        <v>1:50</v>
       </c>
       <c r="H166" t="str">
-        <v>Little Simz</v>
+        <v>DDG</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/ddg/3954994</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
       </c>
       <c r="L166" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Top of the Hill - DDG</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>How to Forget</v>
+        <v>Oh Savannah</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-08</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>ARCADE</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G167" t="str">
-        <v>4:01</v>
+        <v>3:05</v>
       </c>
       <c r="H167" t="str">
-        <v>Deb Never</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
       </c>
       <c r="L167" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Oh Savannah - 49 Winchester</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>Game On (feat. JT)</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-08</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>Sugar Girl - EP</v>
       </c>
       <c r="G168" t="str">
-        <v>2:49</v>
+        <v>2:29</v>
       </c>
       <c r="H168" t="str">
-        <v>ear</v>
+        <v>Little Simz</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
       </c>
       <c r="L168" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>Game On (feat. JT) - Little Simz</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Mirror</v>
+        <v>How to Forget</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-08</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Mirror - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G169" t="str">
-        <v>3:19</v>
+        <v>4:01</v>
       </c>
       <c r="H169" t="str">
-        <v>MOD SUN</v>
+        <v>Deb Never</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
       </c>
       <c r="L169" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>How to Forget - Deb Never</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Miel Con Licor</v>
+        <v>Ne Plus Ultra</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-08</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Bandera Blanca</v>
+        <v>Ne Plus Ultra - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:27</v>
+        <v>2:49</v>
       </c>
       <c r="H170" t="str">
-        <v>Christian Nodal</v>
+        <v>ear</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
       </c>
       <c r="L170" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Ne Plus Ultra - ear</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Mirror</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-08</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Mirror - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:31</v>
+        <v>3:19</v>
       </c>
       <c r="H171" t="str">
-        <v>aron!</v>
+        <v>MOD SUN</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/mirror/1895402181</v>
       </c>
       <c r="L171" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Mirror - MOD SUN</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown)</v>
+        <v>Miel Con Licor</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
+        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-08</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>The Last Balloon</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G172" t="str">
-        <v>3:14</v>
+        <v>3:27</v>
       </c>
       <c r="H172" t="str">
-        <v>Tank and the Bangas</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-david-shaw-austin-brown/1882831446</v>
+        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
       </c>
       <c r="L172" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown) - Tank and the Bangas</v>
+        <v>Miel Con Licor - Christian Nodal</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Macramé (feat. Mei Semones)</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-08</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>Macramé (feat. Mei Semones) - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:14</v>
+        <v>3:31</v>
       </c>
       <c r="H173" t="str">
-        <v>Darkthrone</v>
+        <v>aron!</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
       </c>
       <c r="L173" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Macramé (feat. Mei Semones) - aron!</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Cloudfall</v>
+        <v>Nighttime (feat. David Shaw &amp; Austin Brown)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-08</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G174" t="str">
-        <v>4:06</v>
+        <v>3:14</v>
       </c>
       <c r="H174" t="str">
-        <v>REZN</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-david-shaw-austin-brown/1882831446</v>
       </c>
       <c r="L174" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>Nighttime (feat. David Shaw &amp; Austin Brown) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Doom in Bloom</v>
+        <v>They Found One Of My Graves</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-08</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Hum of Hurt</v>
+        <v>Pre-Historic Metal</v>
       </c>
       <c r="G175" t="str">
-        <v>3:17</v>
+        <v>5:14</v>
       </c>
       <c r="H175" t="str">
-        <v>Converge</v>
+        <v>Darkthrone</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
       </c>
       <c r="L175" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>They Found One Of My Graves - Darkthrone</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Cloudfall</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-08</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Remember The Humans</v>
+        <v>Cycles in the Infinite Dream</v>
       </c>
       <c r="G176" t="str">
-        <v>3:27</v>
+        <v>4:06</v>
       </c>
       <c r="H176" t="str">
-        <v>Broken Social Scene</v>
+        <v>REZN</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
       </c>
       <c r="L176" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Cloudfall - REZN</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Zoom 97</v>
+        <v>Doom in Bloom</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-08</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G177" t="str">
-        <v>4:54</v>
+        <v>3:17</v>
       </c>
       <c r="H177" t="str">
-        <v>Kurt Vile</v>
+        <v>Converge</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
       </c>
       <c r="L177" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Doom in Bloom - Converge</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Switch Up</v>
+        <v>Only The Good I Keep</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-08</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Switch Up - Single</v>
+        <v>Remember The Humans</v>
       </c>
       <c r="G178" t="str">
-        <v>3:35</v>
+        <v>3:27</v>
       </c>
       <c r="H178" t="str">
-        <v>Mike D</v>
+        <v>Broken Social Scene</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
       </c>
       <c r="L178" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>Only The Good I Keep - Broken Social Scene</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Surprise</v>
+        <v>Zoom 97</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-08</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Doe Or Die III</v>
+        <v>Philadelphia's been good to me</v>
       </c>
       <c r="G179" t="str">
-        <v>2:48</v>
+        <v>4:54</v>
       </c>
       <c r="H179" t="str">
-        <v>AZ</v>
+        <v>Kurt Vile</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
       </c>
       <c r="L179" t="str">
-        <v>Surprise - AZ</v>
+        <v>Zoom 97 - Kurt Vile</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Better Days</v>
+        <v>Switch Up</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-08</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Better Days - Single</v>
+        <v>Switch Up - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:22</v>
+        <v>3:35</v>
       </c>
       <c r="H180" t="str">
-        <v>Naomi Sharon</v>
+        <v>Mike D</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
       </c>
       <c r="L180" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Switch Up - Mike D</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>Surprise</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-08</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Doe Or Die III</v>
       </c>
       <c r="G181" t="str">
-        <v>3:14</v>
+        <v>2:48</v>
       </c>
       <c r="H181" t="str">
-        <v>Debbii Dawson</v>
+        <v>AZ</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/az/35299</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/surprise/1894873352</v>
       </c>
       <c r="L181" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>Surprise - AZ</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>No Pressure</v>
+        <v>Better Days</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-08</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>No Pressure - Single</v>
+        <v>Better Days - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:09</v>
+        <v>3:22</v>
       </c>
       <c r="H182" t="str">
-        <v>JYT</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/better-days/1895293758</v>
       </c>
       <c r="L182" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Better Days - Naomi Sharon</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Pachamama</v>
+        <v>Where Have All The Good Men Gone?</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-08</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Así Es La Vida</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G183" t="str">
-        <v>3:20</v>
+        <v>3:14</v>
       </c>
       <c r="H183" t="str">
-        <v>Codiciado</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
       </c>
       <c r="L183" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Multiplied</v>
+        <v>No Pressure</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-08</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Multiplied - Single</v>
+        <v>No Pressure - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:02</v>
+        <v>3:09</v>
       </c>
       <c r="H184" t="str">
-        <v>Luna Li</v>
+        <v>JYT</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
       </c>
       <c r="L184" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>No Pressure - JYT</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Six String</v>
+        <v>What's the Point!</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-08</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Six String - Single</v>
+        <v>Night at the Opera - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>3:11</v>
+        <v>2:43</v>
       </c>
       <c r="H185" t="str">
-        <v>Lila Dupont</v>
+        <v>Emei</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/emei/1583968554</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
       </c>
       <c r="L185" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>What's the Point! - Emei</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Take Heart</v>
+        <v>Pachamama</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-08</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Harbour</v>
+        <v>Así Es La Vida</v>
       </c>
       <c r="G186" t="str">
-        <v>4:07</v>
+        <v>3:20</v>
       </c>
       <c r="H186" t="str">
-        <v>Jon Bryant</v>
+        <v>Codiciado</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
       </c>
       <c r="L186" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Pachamama - Codiciado</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Clarion</v>
+        <v>Multiplied</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-08</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>You Are Spring!</v>
+        <v>Multiplied - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H187" t="str">
-        <v>Tasha</v>
+        <v>Luna Li</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
       </c>
       <c r="L187" t="str">
-        <v>Clarion - Tasha</v>
+        <v>Multiplied - Luna Li</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Stepping Stone</v>
+        <v>Six String</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-08</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Beams - Single</v>
+        <v>Six String - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:49</v>
+        <v>3:11</v>
       </c>
       <c r="H188" t="str">
-        <v>DERBY</v>
+        <v>Lila Dupont</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/six-string/1892171725</v>
       </c>
       <c r="L188" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>Six String - Lila Dupont</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>confessions part iii</v>
+        <v>Take Heart</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-08</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>autogratis</v>
+        <v>Harbour</v>
       </c>
       <c r="G189" t="str">
-        <v>2:01</v>
+        <v>4:07</v>
       </c>
       <c r="H189" t="str">
-        <v>Chanpan</v>
+        <v>Jon Bryant</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
       </c>
       <c r="L189" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Take Heart - Jon Bryant</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>cherry garcia</v>
+        <v>Clarion</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-08</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>cherry garcia - Single</v>
+        <v>You Are Spring!</v>
       </c>
       <c r="G190" t="str">
-        <v>2:30</v>
+        <v>3:23</v>
       </c>
       <c r="H190" t="str">
-        <v>supermodel*</v>
+        <v>Tasha</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/clarion/1887589690</v>
       </c>
       <c r="L190" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>Clarion - Tasha</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Night at the Opera</v>
+        <v>Stepping Stone</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/night-at-the-opera/1886811060</v>
+        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-08</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>Beams - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:04</v>
+        <v>2:49</v>
       </c>
       <c r="H191" t="str">
-        <v>Emei</v>
+        <v>DERBY</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/derby/1772719795</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/night-at-the-opera/1886811055</v>
+        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
       </c>
       <c r="L191" t="str">
-        <v>Night at the Opera - Emei</v>
+        <v>Stepping Stone - DERBY</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Disco Cherry</v>
+        <v>confessions part iii</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-08</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>autogratis</v>
       </c>
       <c r="G192" t="str">
-        <v>3:20</v>
+        <v>2:01</v>
       </c>
       <c r="H192" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Chanpan</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
       </c>
       <c r="L192" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>confessions part iii - Chanpan</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Tal Vez</v>
+        <v>cherry garcia</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-08</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>El Amante</v>
+        <v>cherry garcia - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:14</v>
+        <v>2:30</v>
       </c>
       <c r="H193" t="str">
-        <v>Dariel Amant</v>
+        <v>supermodel*</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
       </c>
       <c r="L193" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>cherry garcia - supermodel*</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>The Voyager</v>
+        <v>Disco Cherry</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-08</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>The Voyager - Single</v>
+        <v>Disco Cherry - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:37</v>
+        <v>3:20</v>
       </c>
       <c r="H194" t="str">
-        <v>Chance Peña</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
       </c>
       <c r="L194" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Disco Cherry - Purple Disco Machine</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pictures of You</v>
+        <v>Tal Vez</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-08</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Pictures of You</v>
+        <v>El Amante</v>
       </c>
       <c r="G195" t="str">
-        <v>3:34</v>
+        <v>2:14</v>
       </c>
       <c r="H195" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Dariel Amant</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
       </c>
       <c r="L195" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>Tal Vez - Dariel Amant</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Buy What U Want</v>
+        <v>The Voyager</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-08</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>The Voyager - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:47</v>
+        <v>4:37</v>
       </c>
       <c r="H196" t="str">
-        <v>Black Fortune</v>
+        <v>Chance Peña</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
       </c>
       <c r="L196" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>The Voyager - Chance Peña</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Pictures of You</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-08</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Pictures of You</v>
       </c>
       <c r="G197" t="str">
-        <v>2:29</v>
+        <v>3:34</v>
       </c>
       <c r="H197" t="str">
-        <v>Lil Naay</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
       </c>
       <c r="L197" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Pictures of You - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>high school sweetheart</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-08</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>ashley cooke</v>
+        <v>Road To Osshland: The Series</v>
       </c>
       <c r="G198" t="str">
-        <v>3:11</v>
+        <v>3:47</v>
       </c>
       <c r="H198" t="str">
-        <v>Ashley Cooke</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
       </c>
       <c r="L198" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>MOOD BRAZIL</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-08</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>MOOD BRAZIL - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>2:55</v>
+        <v>2:29</v>
       </c>
       <c r="H199" t="str">
-        <v>Ray Vaughn</v>
+        <v>Lil Naay</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
       </c>
       <c r="L199" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>MOOD BRAZIL - Lil Naay</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>big plans</v>
+        <v>high school sweetheart</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-08</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>counting horses</v>
+        <v>ashley cooke</v>
       </c>
       <c r="G200" t="str">
-        <v>3:14</v>
+        <v>3:11</v>
       </c>
       <c r="H200" t="str">
-        <v>Tom Siletto</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
       </c>
       <c r="L200" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Running</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-08</v>
@@ -8013,68 +8013,144 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Running - Single</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:38</v>
+        <v>2:55</v>
       </c>
       <c r="H201" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
       </c>
       <c r="L201" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
+        <v>big plans</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>counting horses</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:14</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Tom Siletto</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+      </c>
+      <c r="L202" t="str">
+        <v>big plans - Tom Siletto</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Running</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/running/6764878724</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Running - Single</v>
+      </c>
+      <c r="G203" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/running/1895947036</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Running - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
         <v>FA-TAL!</v>
       </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
-      <c r="D202" t="str">
-        <v>2026-05-08</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
+      <c r="D204" t="str">
+        <v>2026-05-08</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
         <v>FA-TAL! - Single</v>
       </c>
-      <c r="G202" t="str">
+      <c r="G204" t="str">
         <v>2:46</v>
       </c>
-      <c r="H202" t="str">
+      <c r="H204" t="str">
         <v>ROBI</v>
       </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
         <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
-      <c r="K202" t="str">
+      <c r="K204" t="str">
         <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
       </c>
-      <c r="L202" t="str">
+      <c r="L204" t="str">
         <v>FA-TAL! - ROBI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L202"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>8d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9d ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B39" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10d ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>10d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11d ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B46" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B49" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4426,13 +4426,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Smoking pt. 2 (feat. Rick Ross)</v>
+        <v>Smoking pt. 2</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/smoking-pt-2-feat-rick-ross/1894333434</v>
+        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-08</v>
@@ -4456,10 +4456,10 @@
         <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/smoking-pt-2-feat-rick-ross/1894333428</v>
+        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
       </c>
       <c r="L107" t="str">
-        <v>Smoking pt. 2 (feat. Rick Ross) - French Montana</v>
+        <v>Smoking pt. 2 - French Montana</v>
       </c>
     </row>
     <row r="108">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,19 +439,19 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6268,7 +6268,7 @@
         <v>Wide Eyed</v>
       </c>
       <c r="G155" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H155" t="str">
         <v>Mack Keane</v>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-08</v>
+        <v>2026-05-09</v>
       </c>
       <c r="E204" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -629,7 +629,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>3 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1693,7 +1693,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1579,7 +1579,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E204" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B2" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B4" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B5" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B6" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8 days ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B7" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>8 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B8" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B9" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B10" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B11" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B13" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B18" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B19" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B20" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B21" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B22" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B31" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9 days ago</v>
+        <v>9d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10 days ago</v>
+        <v>10d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B37" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>10 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B41" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B43" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B44" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B45" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B46" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B48" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
       </c>
       <c r="B55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
       </c>
       <c r="B57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Matt Hansen - VISION (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Meghan Trainor - Rich Man (Official Audio)</v>
       </c>
       <c r="B60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Lukas Graham - To Know A Girl</v>
       </c>
       <c r="B61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Foo Fighters - Window (Official Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>Ruel - Hate Myself (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Haiden Henderson - freak for you (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Conan Gray - Do I Dare (Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Foo Fighters - Unconditional (Lyric Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
       </c>
       <c r="B67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
       </c>
       <c r="B68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>Sam Feldt x TAME - Lost In Desire</v>
       </c>
       <c r="B70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>Niall Horan - Little More Time (Seaside Visual)</v>
       </c>
       <c r="B71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
       </c>
       <c r="B72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>DANNA - MOVIE STAR</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
       </c>
       <c r="B77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Dermot Kennedy - Endless (Official Visualiser)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
       </c>
       <c r="B79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Beck - Ride Lonesome (Official Music Video)</v>
       </c>
       <c r="B80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
       </c>
       <c r="B81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
       </c>
       <c r="B82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
       </c>
       <c r="B83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Beck - Ride Lonesome (Audio)</v>
       </c>
       <c r="B84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
       </c>
       <c r="B86" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Madonna - I Feel So Free (Official Visualizer)</v>
       </c>
       <c r="B88" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>Céline Dion - Dansons (Vidéo officielle)</v>
       </c>
       <c r="B90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
       </c>
       <c r="B91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
       </c>
       <c r="B92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Jessie Ware - Superbloom</v>
       </c>
       <c r="B93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>The Kid LAROI - I CONDEMN (Official Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>ERNEST - Time Is A Thief (Visualizer)</v>
       </c>
       <c r="B95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
       </c>
       <c r="B97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Bella White - Pink Living Room (Official Music Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Kip Moore - Faith In The Wind (Official)</v>
       </c>
       <c r="B99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
       </c>
       <c r="B101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3 weeks ago</v>
+        <v>3w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
+        <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>9d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
+        <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,13 +451,13 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>9d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>SIENNA SPIRO</v>
+        <v>Harry Styles</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
+        <v>Harry Styles - Dance No More (Official Video) - Harry Styles</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Rick Astley - Raindrops (Official Video)</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>8d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
+        <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-10</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>Rick Astley</v>
+        <v>Eagles</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
+        <v>Eagles - One Of These Nights (Through The Years - Official Video) - Eagles</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video)</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>9d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
+        <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-10</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>9d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>Jessie J</v>
+        <v>Nora Fatehi</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
+        <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video] - Nora Fatehi</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>The Takes - Ain't Love (Lyric Video)</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>8d ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
+        <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-10</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>8d ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>The Takes</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
+        <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>8d ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
+        <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-10</v>
@@ -603,13 +603,13 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>8d ago</v>
+        <v>1 month ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>The Offspring</v>
+        <v>Eurovision Song Contest and Alis</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
+        <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026 - Eurovision Song Contest and Alis</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>9d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
+        <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-10</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>9d ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Eurovision Song Contest</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
+        <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026 - Eurovision Song Contest</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
+        <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>9d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
+        <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-10</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>9d ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>The Beaches</v>
+        <v>The Head And The Heart</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
+        <v>The Head And The Heart - Grace (Official Music Video) - The Head And The Heart</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song)</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
+        <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-10</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>9d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>The Kiffness</v>
+        <v>Simply Red</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
+        <v>Simply Red - Something Got Me Started (Live in Santiago) - Simply Red</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
+        <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>9d ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
+        <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-10</v>
@@ -755,13 +755,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>9d ago</v>
+        <v>5 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>Dennis Lloyd</v>
+        <v>Talking Heads</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
+        <v>Talking Heads - Stay Up Late (Official Video) - Talking Heads</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
+        <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
+        <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-10</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>Anna Graves</v>
+        <v>Ellise</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
+        <v>Ellise - Liplock (Official Music Video) - Ellise</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
+        <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
+        <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-10</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>Brandon Lake and NICK JONAS</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
+        <v>Tori Kelly - Dive (Official Music Video) - Tori Kelly</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer)</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
+        <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
         <v>2026-05-10</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>Letdown.</v>
+        <v>David Gilmour</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
+        <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024) - David Gilmour</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
+        <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
         <v>2026-05-10</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>Maroon 5</v>
+        <v>Scorpions</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
+        <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
+        <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
         <v>2026-05-10</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>Olivia O'Brien</v>
+        <v>Claire Leslie</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
+        <v>Claire Leslie - Passenger Seat (Official Music Video) - Claire Leslie</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
+        <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
+        <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
         <v>2026-05-10</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>ERNEST</v>
+        <v>Michael Schulte</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
+        <v>Michael Schulte - Lovesick (Official Video) - Michael Schulte</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
+        <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
+        <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
         <v>2026-05-10</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Caity Baser</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
+        <v>Caity Baser - Holiday Song (Official Video) - Caity Baser</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Halsey - Nothing! (Official Audio)</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
+        <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
         <v>2026-05-10</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>Halsey</v>
+        <v>Sam Fischer</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
+        <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser) - Sam Fischer</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
+        <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
+        <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
         <v>2026-05-10</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>Zara Larsson</v>
+        <v>Porches</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>Porches- HABIT (Official Video) - Porches</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Halsey - Carry the Weight (Official Audio)</v>
+        <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
+        <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
         <v>2026-05-10</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>Halsey</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
+        <v>Charli xcx - Rock Music (Official Video) - Charli xcx</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official)</v>
+        <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
+        <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
         <v>2026-05-10</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>Bishop Briggs</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
+        <v>Jon Batiste - Alla Blues (Audio) - Jon Batiste</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
+        <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
         <v>2026-05-10</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>Louis Tomlinson</v>
+        <v>Tigirlily Gold</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
+        <v>Tigirlily Gold - I Do or Die (Official Music Video) - Tigirlily Gold</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>almost monday - no more regrets (official video)</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
+        <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
         <v>2026-05-10</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>almost monday</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>almost monday - no more regrets (official video) - almost monday</v>
+        <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
+        <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-05-10</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
+        <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video] - Bruno Mars</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
+        <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
+        <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
         <v>2026-05-10</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
+        <v>Tori Kelly - Control (Official Visualizer) - Tori Kelly</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
+        <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
         <v>2026-05-10</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>NIGHTLY and Fly By Midnight</v>
+        <v>bea miller</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
+        <v>Bea Miller - depressed on the internet (Lyric Video) - bea miller</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
+        <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
         <v>2026-05-10</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>Zara Larsson</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
+        <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
+        <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
+        <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
         <v>2026-05-10</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>Jordana Bryant</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
+        <v>Madison Beer - free (Official Audio) - Madison Beer</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video)</v>
+        <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
+        <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
         <v>2026-05-10</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>Leanna Crawford</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
+        <v>Tori Kelly - Dive (Official Audio) - Tori Kelly</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
+        <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
+        <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-05-10</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>Girl Tones</v>
+        <v>JeremyCampMusic</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
+        <v>Jeremy Camp - Reflector (Official Audio) - JeremyCampMusic</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
+        <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
         <v>2026-05-10</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>Tauren Wells</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
+        <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer) - The Chainsmokers</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Matthew Ifield - Thinking (Official Video)</v>
+        <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
+        <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-05-10</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>9d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
       </c>
       <c r="H32" t="str">
-        <v>Matthew Ifield</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
+        <v>Ashley Cooke - high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Dons - Is There Something</v>
+        <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
+        <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-05-10</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
       </c>
       <c r="H33" t="str">
-        <v>Dons</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Dons - Is There Something - Dons</v>
+        <v>Ari Abdul - Ego (Visualizer) - Ari Abdul</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
+        <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
         <v>2026-05-10</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>Recording Academy / GRAMMYs and 3 more</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
+        <v>Quinn XCII - HOOPLA (Official Music Video) - Quinn XCII</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Maya Hawke - Lioness (Official Audio)</v>
+        <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
+        <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
         <v>2026-05-10</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
       </c>
       <c r="H35" t="str">
-        <v>Maya Hawke</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
+        <v>Madison Beer - lovergirl (Official Music Video) - Madison Beer</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
+        <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
         <v>2026-05-10</v>
@@ -1743,13 +1743,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>10d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>Laufey</v>
+        <v>David J</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
+        <v>David J - WHAT IF I'M IN LOVE (Official Video) - David J</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
+        <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
+        <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
         <v>2026-05-10</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
       </c>
       <c r="H37" t="str">
-        <v>Keith Urban</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
+        <v>The Last Dinner Party - Big Dog (On The Road) - The Last Dinner Party</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DANNA - AGAIN</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
+        <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
         <v>2026-05-10</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
       </c>
       <c r="H38" t="str">
-        <v>Danna</v>
+        <v>Ocean Alley</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>DANNA - AGAIN - Danna</v>
+        <v>OCEAN ALLEY - HOLD ON (Official Video) - Ocean Alley</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
+        <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-05-10</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>11d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>Armik</v>
+        <v>Dagny</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
+        <v>Dagny - Closet Disco Queen (Lyric Video) - Dagny</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>EUROPE - One on One (Official Video)</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>12d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
+        <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
         <v>2026-05-10</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>12d ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
       </c>
       <c r="H40" t="str">
-        <v>Europe</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>EUROPE - One on One (Official Video) - Europe</v>
+        <v>Purple Disco Machine - Disco Cherry (Official Video) - Purple Disco Machine</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
+        <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
         <v>2026-05-10</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
       </c>
       <c r="H41" t="str">
-        <v>Foo Fighters</v>
+        <v>Paris Paloma</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
+        <v>Paris Paloma - Stem the Flow [Official Music Video] - Paris Paloma</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
+        <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
+        <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
         <v>2026-05-10</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>Lady Gaga and Doechii</v>
+        <v>Lucy Blue</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
+        <v>Lucy Blue - Who you love (Visualiser) - Lucy Blue</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
+        <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-05-10</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>12d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
       </c>
       <c r="H43" t="str">
-        <v>Muse</v>
+        <v>Olivia Dean</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
+        <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026) - Olivia Dean</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
+        <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>13d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
+        <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-05-10</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>13d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Aaron Frazer</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
+        <v>Aaron Frazer - It's A Shame (Official Video) - Aaron Frazer</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Shaboozey - Born To Die (Official Video)</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
+        <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-05-10</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
       </c>
       <c r="H45" t="str">
-        <v>Shaboozey</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
+        <v>Holly Humberstone - White Noise (Live) | Presented By Spotify - Holly Humberstone</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
+        <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
+        <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
         <v>2026-05-10</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>2w ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
       </c>
       <c r="H46" t="str">
-        <v>Scorpions</v>
+        <v>Danna</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
+        <v>DANNA - OUT OF MY BODY - Danna</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>2w ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
+        <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
         <v>2026-05-10</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>2w ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
+        <v>The Rolling Stones - In The Stars (Official Lyric Video) - The Rolling Stones</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>2w ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
+        <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
         <v>2026-05-10</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>2w ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
       </c>
       <c r="H48" t="str">
-        <v>Lolo Zouaï</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
+        <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Bonnie Tyler - One World One Home</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
+        <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
         <v>2026-05-10</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
       </c>
       <c r="H49" t="str">
-        <v>Bonnie Tyler</v>
+        <v>SIENNA SPIRO</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
+        <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2) - SIENNA SPIRO</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
+        <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
+        <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-05-10</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
       </c>
       <c r="H50" t="str">
-        <v>Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
+        <v>Rick Astley - Raindrops (Official Video) - Rick Astley</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Icona Pop - Dance To This (Official Video)</v>
+        <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
+        <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
         <v>2026-05-10</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
       </c>
       <c r="H51" t="str">
-        <v>Icona Pop</v>
+        <v>Jessie J</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
+        <v>Jessie J - THREW IT AWAY (Official Video) - Jessie J</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Michael Jackson - Human Nature (Official Video)</v>
+        <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
+        <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-05-10</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
       </c>
       <c r="H52" t="str">
-        <v>Michael Jackson</v>
+        <v>The Takes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
+        <v>The Takes - Ain't Love (Lyric Video) - The Takes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>The All-American Rejects - King Kong</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
+        <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-05-10</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
       </c>
       <c r="H53" t="str">
-        <v>The All-American Rejects</v>
+        <v>The Offspring</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
+        <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary - The Offspring</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
+        <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
         <v>2026-05-10</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
       </c>
       <c r="H54" t="str">
-        <v>Ringo Starr</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
+        <v>Louis Tomlinson - Sunflowers (Official Performance Video) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france)</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=kxqeX_2FUs0</v>
+        <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
         <v>2026-05-10</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
       </c>
       <c r="H55" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>The Beaches</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Olivia Rodrigo - drop dead (taken that eurostar to france) - Olivia Rodrigo</v>
+        <v>The Beaches - Should've Known Better (Official Visualizer) - The Beaches</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video)</v>
+        <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=iRjHD3SjL9M</v>
+        <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
         <v>2026-05-10</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
       </c>
       <c r="H56" t="str">
-        <v>Demi Lovato</v>
+        <v>The Kiffness</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Demi Lovato - Love Controller (Official Lyric Video) - Demi Lovato</v>
+        <v>The Kiffness - Serafino (Singing Cat Song) - The Kiffness</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video)</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=X-KyrJRhYUw</v>
+        <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-05-10</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
       </c>
       <c r="H57" t="str">
-        <v>Dean Lewis</v>
+        <v>Dennis Lloyd</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Lyric Video) - Dean Lewis</v>
+        <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer) - Dennis Lloyd</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video)</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=ElBF34vjq1A</v>
+        <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
         <v>2026-05-10</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
       </c>
       <c r="H58" t="str">
-        <v>Matt Hansen</v>
+        <v>Anna Graves</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Matt Hansen - VISION (Official Lyric Video) - Matt Hansen</v>
+        <v>Anna Graves - Damn In Love (Official Visualizer) - Anna Graves</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video)</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=A3G_7XgK2B4</v>
+        <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
         <v>2026-05-10</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
       </c>
       <c r="H59" t="str">
-        <v>Ella Langley</v>
+        <v>Brandon Lake and NICK JONAS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Ella Langley &amp; Morgan Wallen - I Can’t Love You Anymore (Official Lyric Video) - Ella Langley</v>
+        <v>Brandon Lake, Nick Jonas - The Author (Lyric Video) - Brandon Lake and NICK JONAS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio)</v>
+        <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=6FGHAAo_5w0</v>
+        <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-05-10</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
       </c>
       <c r="H60" t="str">
-        <v>Meghan Trainor</v>
+        <v>Letdown.</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Meghan Trainor - Rich Man (Official Audio) - Meghan Trainor</v>
+        <v>Letdown. - Do It For The Love (Visualizer) - Letdown.</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lukas Graham - To Know A Girl</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Dujfx7rfd6E</v>
+        <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
         <v>2026-05-10</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
       </c>
       <c r="H61" t="str">
-        <v>Lukas Graham</v>
+        <v>Maroon 5</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lukas Graham - To Know A Girl - Lukas Graham</v>
+        <v>Maroon 5 - Heroine (Official Lyric Video) - Maroon 5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Foo Fighters - Window (Official Video)</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=OZ-ywVT052U</v>
+        <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
         <v>2026-05-10</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
       </c>
       <c r="H62" t="str">
-        <v>Foo Fighters</v>
+        <v>Olivia O'Brien</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Foo Fighters - Window (Official Video) - Foo Fighters</v>
+        <v>Olivia O'Brien - I'm Perfect (Official Visualizer) - Olivia O'Brien</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Ruel - Hate Myself (Official Music Video)</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=w6x-_krg7O0</v>
+        <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-05-10</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>RUEL</v>
+        <v>ERNEST</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Ruel - Hate Myself (Official Music Video) - RUEL</v>
+        <v>ERNEST - What's A Little Rain (Official Music Video) - ERNEST</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer)</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=8HwOwvLqcko</v>
+        <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
         <v>2026-05-10</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
       </c>
       <c r="H64" t="str">
-        <v>Haiden Henderson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Haiden Henderson - freak for you (Official Visualizer) - Haiden Henderson</v>
+        <v>Claire Rosinkranz - Just A Man (Official Audio) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video)</v>
+        <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=3V86E_eNp7w</v>
+        <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
         <v>2026-05-10</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>Conan Gray</v>
+        <v>Halsey</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Conan Gray - Do I Dare (Lyric Video) - Conan Gray</v>
+        <v>Halsey - Nothing! (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video)</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=2IaBmbicE1s</v>
+        <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-05-10</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
       </c>
       <c r="H66" t="str">
-        <v>Foo Fighters</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Foo Fighters - Unconditional (Lyric Video) - Foo Fighters</v>
+        <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer)</v>
+        <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Dd7Ly7uCZTg</v>
+        <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
         <v>2026-05-10</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
       </c>
       <c r="H67" t="str">
-        <v>Ringo Starr</v>
+        <v>Halsey</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Ringo Starr - Baby Don't Go (Visualizer) - Ringo Starr</v>
+        <v>Halsey - Carry the Weight (Official Audio) - Halsey</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live]</v>
+        <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=02sxdNxUvaE</v>
+        <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-05-10</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
       </c>
       <c r="H68" t="str">
-        <v>Michael Bublé</v>
+        <v>Bishop Briggs</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Michael Bublé - You'll Never Find Another Love like Mine (with Laura Pausini) [Live] - Michael Bublé</v>
+        <v>Bishop Briggs - Blood From A Stone (Official) - Bishop Briggs</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video)</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=3KQjOE1AuN4</v>
+        <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
         <v>2026-05-10</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
       </c>
       <c r="H69" t="str">
-        <v>Malcolm Todd</v>
+        <v>Louis Tomlinson</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Malcolm Todd - I Saw Your Face (Official Video) - Malcolm Todd</v>
+        <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio) - Louis Tomlinson</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire</v>
+        <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=-Nu0T4MMD6k</v>
+        <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
         <v>2026-05-10</v>
@@ -3035,13 +3035,13 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
       </c>
       <c r="H70" t="str">
-        <v>Sam Feldt</v>
+        <v>almost monday</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Sam Feldt x TAME - Lost In Desire - Sam Feldt</v>
+        <v>almost monday - no more regrets (official video) - almost monday</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual)</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=ScqYsvFpft4</v>
+        <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
         <v>2026-05-10</v>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
       </c>
       <c r="H71" t="str">
-        <v>Niall Horan</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Niall Horan - Little More Time (Seaside Visual) - Niall Horan</v>
+        <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=EyCvEHTQGAo</v>
+        <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
         <v>2026-05-10</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
       </c>
       <c r="H72" t="str">
-        <v>Dermot Kennedy</v>
+        <v>★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Dermot Kennedy - Refuge | Live From Vevo Studios - Dermot Kennedy</v>
+        <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video) - ★ 𝑲𝒂𝒄𝒆𝒚 𝑴𝒖𝒔𝒈𝒓𝒂𝒗𝒆𝒔 ★</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video]</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=W1-2XVQs46U</v>
+        <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
         <v>2026-05-10</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
       </c>
       <c r="H73" t="str">
-        <v>Duran Duran</v>
+        <v>NIGHTLY and Fly By Midnight</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Duran Duran - Free to Love (feat. Nile Rodgers) [Official Music Video] - Duran Duran</v>
+        <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video) - NIGHTLY and Fly By Midnight</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London)</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=_SdshlZk-po</v>
+        <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-05-10</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
       </c>
       <c r="H74" t="str">
-        <v>Freya Skye</v>
+        <v>Zara Larsson</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Freya Skye - golden boy (Stars Align Tour: Live from London) - Freya Skye</v>
+        <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer) - Zara Larsson</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=Gc8N1rptDIY</v>
+        <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-05-10</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
       </c>
       <c r="H75" t="str">
-        <v>OneRepublic and Nova's Red Room</v>
+        <v>Jordana Bryant</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>OneRepublic - "Need Your Love" | Live in Nova's Red Room - OneRepublic and Nova's Red Room</v>
+        <v>JORDANA BRYANT - Truth Is (Official Video) - Jordana Bryant</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>DANNA - MOVIE STAR</v>
+        <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=NK-4pxhXLNI</v>
+        <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
         <v>2026-05-10</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
       </c>
       <c r="H76" t="str">
-        <v>Danna</v>
+        <v>Leanna Crawford</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>DANNA - MOVIE STAR - Danna</v>
+        <v>Leanna Crawford - Thank God (Lyric Video) - Leanna Crawford</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=qWUpI6Z43BA</v>
+        <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-05-10</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
       </c>
       <c r="H77" t="str">
-        <v>Purple Disco Machine</v>
+        <v>Girl Tones</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>PURPLE DISCO MACHINE - PURPLE DISCO TALES APRIL 2026 - Purple Disco Machine</v>
+        <v>Girl Tones - Stubborn Mouth (Official Music Video) - Girl Tones</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser)</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=pMVcie8qT1w</v>
+        <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
         <v>2026-05-10</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
       </c>
       <c r="H78" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Tauren Wells</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Dermot Kennedy - Endless (Official Visualiser) - Dermot Kennedy</v>
+        <v>Tauren Wells - What A Miracle Feels Like (Official Audio) - Tauren Wells</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios</v>
+        <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Z8Sp5O1M0gw</v>
+        <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
         <v>2026-05-10</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>2w ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
       </c>
       <c r="H79" t="str">
-        <v>Cannons</v>
+        <v>Matthew Ifield</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Cannons - Light as a Feather | Live From Vevo Studios - Cannons</v>
+        <v>Matthew Ifield - Thinking (Official Video) - Matthew Ifield</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video)</v>
+        <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=VqQmgHcIHN0</v>
+        <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
         <v>2026-05-10</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
       </c>
       <c r="H80" t="str">
-        <v>Beck</v>
+        <v>Dons</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Beck - Ride Lonesome (Official Music Video) - Beck</v>
+        <v>Dons - Is There Something - Dons</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video)</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=X82AIwGxOYE</v>
+        <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
         <v>2026-05-10</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
       </c>
       <c r="H81" t="str">
-        <v>Frank Walker and salem ilese</v>
+        <v>Recording Academy / GRAMMYs and 3 more</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Frank Walker, salem ilese - All Cried Out (Official Video) - Frank Walker and salem ilese</v>
+        <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris - Recording Academy / GRAMMYs and 3 more</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live)</v>
+        <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=lIKj-M0jGKI</v>
+        <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-05-10</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>2w ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
       </c>
       <c r="H82" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Mumford &amp; Sons, Hozier - Rubber Band Man (Live On Saturday Night Live) - Mumford &amp; Sons</v>
+        <v>Maya Hawke - Lioness (Official Audio) - Maya Hawke</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session)</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ivTHqhTryQU</v>
+        <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
         <v>2026-05-10</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
       </c>
       <c r="H83" t="str">
-        <v>Digster Pop Music</v>
+        <v>Laufey</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Sienna Spiro - Die On This Hill (1LIVE Session) - Digster Pop Music</v>
+        <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance - Laufey</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Beck - Ride Lonesome (Audio)</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=wuCgArBTl7Q</v>
+        <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
         <v>2026-05-10</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
       </c>
       <c r="H84" t="str">
-        <v>Beck</v>
+        <v>Keith Urban</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Beck - Ride Lonesome (Audio) - Beck</v>
+        <v>Keith Urban - Summer Breeze (Official Lyric Video) - Keith Urban</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video)</v>
+        <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=74M-8j4bFQE</v>
+        <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
         <v>2026-05-10</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
       </c>
       <c r="H85" t="str">
-        <v>The All-American Rejects</v>
+        <v>Danna</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>The All-American Rejects - King Kong (Official Lyric Video) - The All-American Rejects</v>
+        <v>DANNA - AGAIN - Danna</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video]</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=-FyKGVCPsuQ</v>
+        <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
         <v>2026-05-10</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
       </c>
       <c r="H86" t="str">
-        <v>Armin van Buuren</v>
+        <v>Armik</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Armin van Buuren - Temporality (from 'Piano' album) [Official Video] - Armin van Buuren</v>
+        <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar) - Armik</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video)</v>
+        <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=SDq2JK61Glo</v>
+        <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
         <v>2026-05-10</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
       </c>
       <c r="H87" t="str">
-        <v>Demi Lovato</v>
+        <v>Europe</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Demi Lovato - Low Rise Jeans (Official Lyric Video) - Demi Lovato</v>
+        <v>EUROPE - One on One (Official Video) - Europe</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer)</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Zx83eVfP64A</v>
+        <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
         <v>2026-05-10</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
       </c>
       <c r="H88" t="str">
-        <v>Madonna</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Madonna - I Feel So Free (Official Visualizer) - Madonna</v>
+        <v>Foo Fighters - Caught In The Echo (SNL UK) - Foo Fighters</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video)</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=vOjbJFl0ytA</v>
+        <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
         <v>2026-05-10</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>3w ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
       </c>
       <c r="H89" t="str">
-        <v>Freya Ridings</v>
+        <v>Lady Gaga and Doechii</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Freya Ridings - Dancing In The Kitchen (Official Video) - Freya Ridings</v>
+        <v>Lady Gaga, Doechii - RUNWAY (Official Music Video) - Lady Gaga and Doechii</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle)</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>3w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=FHL5wBjqXCI</v>
+        <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
         <v>2026-05-10</v>
@@ -3795,13 +3795,13 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>3w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
       </c>
       <c r="H90" t="str">
-        <v>Celine Dion</v>
+        <v>Muse</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Céline Dion - Dansons (Vidéo officielle) - Celine Dion</v>
+        <v>MUSE - Cryogen (Live from O2 Academy Brixton) - Muse</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix)</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>3w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=_KMiXJpSpnE</v>
+        <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
         <v>2026-05-10</v>
@@ -3833,13 +3833,13 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>3w ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
       </c>
       <c r="H91" t="str">
-        <v>Peter Gabriel</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Peter Gabriel - Till Your Mind Is Shining (Bright-Side Mix) - Peter Gabriel</v>
+        <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023)</v>
+        <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=HDBT7ResL1k</v>
+        <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-05-10</v>
@@ -3871,13 +3871,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
       </c>
       <c r="H92" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Shaboozey</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Nothing But Thieves - Impossible (Live from Reading Festival, 2023) - Nothing But Thieves</v>
+        <v>Shaboozey - Born To Die (Official Video) - Shaboozey</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Jessie Ware - Superbloom</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=HIfqcdCPdJw</v>
+        <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
         <v>2026-05-10</v>
@@ -3909,13 +3909,13 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
       </c>
       <c r="H93" t="str">
-        <v>Jessie Ware</v>
+        <v>Scorpions</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Jessie Ware - Superbloom - Jessie Ware</v>
+        <v>Scorpions - Peacemaker (Madison Square Garden 2022) - Scorpions</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video)</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ojNO4eUMpRQ</v>
+        <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
         <v>2026-05-10</v>
@@ -3947,13 +3947,13 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
       </c>
       <c r="H94" t="str">
-        <v>The Kid LAROI.</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>The Kid LAROI - I CONDEMN (Official Video) - The Kid LAROI.</v>
+        <v>Meghan Trainor - Shimmer (Official Music Video) - Meghan Trainor</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer)</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=sbUwBJu4nNQ</v>
+        <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
         <v>2026-05-10</v>
@@ -3985,13 +3985,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
       </c>
       <c r="H95" t="str">
-        <v>ERNEST</v>
+        <v>Lolo Zouaï</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>ERNEST - Time Is A Thief (Visualizer) - ERNEST</v>
+        <v>Lolo Zouaï - Baggy Jeans (Official Video) - Lolo Zouaï</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=uJTiE5ILxxs</v>
+        <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
         <v>2026-05-10</v>
@@ -4023,13 +4023,13 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
       </c>
       <c r="H96" t="str">
-        <v>DisneyMusicVEVO</v>
+        <v>Bonnie Tyler</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Miley Cyrus, Lainey Wilson - Younger You (From the "Hannah Montana 20th Anniversary Special") - DisneyMusicVEVO</v>
+        <v>Bonnie Tyler - One World One Home - Bonnie Tyler</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video)</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=ZLqvlv3ArZo</v>
+        <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
         <v>2026-05-10</v>
@@ -4061,13 +4061,13 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
       </c>
       <c r="H97" t="str">
-        <v>Dean Lewis</v>
+        <v>Jacob Gurevitsch and Prisma Music Group</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Dean Lewis - Seconds Before The Sunrise (Official Video) - Dean Lewis</v>
+        <v>Jacob Gurevitsch | Dream Catcher | Official Music Video - Jacob Gurevitsch and Prisma Music Group</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video)</v>
+        <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=IifB_lXqewA</v>
+        <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-05-10</v>
@@ -4099,13 +4099,13 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
       </c>
       <c r="H98" t="str">
-        <v>Bella White</v>
+        <v>Icona Pop</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Bella White - Pink Living Room (Official Music Video) - Bella White</v>
+        <v>Icona Pop - Dance To This (Official Video) - Icona Pop</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Kip Moore - Faith In The Wind (Official)</v>
+        <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=APq-FZVPrDI</v>
+        <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
         <v>2026-05-10</v>
@@ -4137,13 +4137,13 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
       </c>
       <c r="H99" t="str">
-        <v>Kip Moore</v>
+        <v>Michael Jackson</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Kip Moore - Faith In The Wind (Official) - Kip Moore</v>
+        <v>Michael Jackson - Human Nature (Official Video) - Michael Jackson</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video)</v>
+        <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=78wrful9cVU</v>
+        <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
         <v>2026-05-10</v>
@@ -4175,13 +4175,13 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
       </c>
       <c r="H100" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>The All-American Rejects</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Olivia Rodrigo - drop dead (Official Music Video) - Olivia Rodrigo</v>
+        <v>The All-American Rejects - King Kong - The All-American Rejects</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=NRAwyRBr-YA</v>
+        <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-05-10</v>
@@ -4213,13 +4213,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>3w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
       </c>
       <c r="H101" t="str">
-        <v>Ben Gallaher</v>
+        <v>Ringo Starr</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,7 +4231,7 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ben Gallaher - I'll Take You (The Taylor Gold Acoustic Version) - Official Video - Ben Gallaher</v>
+        <v>Ringo Starr - Long Long Road (Official Music Video) - Ringo Starr</v>
       </c>
     </row>
     <row r="102">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>5 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>5 hours ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G89" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>7 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G10" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>8 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-11</v>
       </c>
       <c r="E204" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L204"/>
+  <dimension ref="A1:L205"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>1 month ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 month ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -4274,13 +4274,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Rock Music</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-11</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Rock Music - Single</v>
+        <v>American Stories</v>
       </c>
       <c r="G103" t="str">
-        <v>1:55</v>
+        <v>3:53</v>
       </c>
       <c r="H103" t="str">
-        <v>Charli xcx</v>
+        <v>Rostam</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L103" t="str">
-        <v>Rock Music - Charli xcx</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>TNT</v>
+        <v>Rock Music</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/tnt/1887671066</v>
+        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-11</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Rock Music - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:02</v>
+        <v>1:55</v>
       </c>
       <c r="H104" t="str">
-        <v>CORTIS</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/tnt/1887671065</v>
+        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
       </c>
       <c r="L104" t="str">
-        <v>TNT - CORTIS</v>
+        <v>Rock Music - Charli xcx</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Go</v>
+        <v>TNT</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/go/6765588421</v>
+        <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-11</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Go - Single</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G105" t="str">
-        <v>2:24</v>
+        <v>2:02</v>
       </c>
       <c r="H105" t="str">
-        <v>Key Glock</v>
+        <v>CORTIS</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/go/1896001876</v>
+        <v>https://music.apple.com/us/album/tnt/1887671065</v>
       </c>
       <c r="L105" t="str">
-        <v>Go - Key Glock</v>
+        <v>TNT - CORTIS</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>For The Moment</v>
+        <v>Go</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
+        <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-11</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>BROWN</v>
+        <v>Go - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H106" t="str">
-        <v>Chris Brown</v>
+        <v>Key Glock</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
+        <v>https://music.apple.com/us/album/go/1896001876</v>
       </c>
       <c r="L106" t="str">
-        <v>For The Moment - Chris Brown</v>
+        <v>Go - Key Glock</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Smoking pt. 2</v>
+        <v>For The Moment</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
+        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-11</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Wave Gods 2: Cosmos Brothers</v>
+        <v>BROWN</v>
       </c>
       <c r="G107" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H107" t="str">
-        <v>French Montana</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
+        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
       </c>
       <c r="L107" t="str">
-        <v>Smoking pt. 2 - French Montana</v>
+        <v>For The Moment - Chris Brown</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Therapy at the Club</v>
+        <v>Smoking pt. 2</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-11</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Wave Gods 2: Cosmos Brothers</v>
       </c>
       <c r="G108" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H108" t="str">
-        <v>FLO</v>
+        <v>French Montana</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
       </c>
       <c r="L108" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Smoking pt. 2 - French Montana</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>linknb</v>
+        <v>Therapy at the Club</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-11</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>new avatar</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G109" t="str">
-        <v>1:55</v>
+        <v>2:47</v>
       </c>
       <c r="H109" t="str">
-        <v>Kelela</v>
+        <v>FLO</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
       </c>
       <c r="L109" t="str">
-        <v>linknb - Kelela</v>
+        <v>Therapy at the Club - FLO</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-11</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G110" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H110" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L110" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Baby</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-11</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Baby - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H111" t="str">
-        <v>Prospa</v>
+        <v>elkan</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L111" t="str">
-        <v>Baby - Prospa</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Baby</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-11</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>Baby - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>2:39</v>
+        <v>3:13</v>
       </c>
       <c r="H112" t="str">
-        <v>Russell Dickerson</v>
+        <v>Prospa</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/baby/1895418297</v>
       </c>
       <c r="L112" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Baby - Prospa</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Bed of Roses</v>
+        <v>Boots (feat. Fetty Wap)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-11</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Boots (feat. Fetty Wap) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H113" t="str">
-        <v>Teyana Taylor</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
       </c>
       <c r="L113" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Bed of Roses</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-11</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>Bed of Roses - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H114" t="str">
-        <v>Bruno Mars</v>
+        <v>Teyana Taylor</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
       </c>
       <c r="L114" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Bed of Roses - Teyana Taylor</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Big Dog</v>
+        <v>Lo Arriesgo Todo</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-11</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Big Dog - Single</v>
+        <v>Lo Arriesgo Todo - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H115" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
       </c>
       <c r="L115" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Lo Arriesgo Todo - Bruno Mars</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Eastside Girls</v>
+        <v>Big Dog</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-11</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Big Dog - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H116" t="str">
-        <v>MUNA</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
       </c>
       <c r="L116" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>Big Dog - The Last Dinner Party</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>In The Stars</v>
+        <v>Eastside Girls</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-11</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Foreign Tongues</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G117" t="str">
-        <v>4:13</v>
+        <v>3:50</v>
       </c>
       <c r="H117" t="str">
-        <v>The Rolling Stones</v>
+        <v>MUNA</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
       </c>
       <c r="L117" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Eastside Girls - MUNA</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Home to Us</v>
+        <v>In The Stars</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-11</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Foreign Tongues</v>
       </c>
       <c r="G118" t="str">
-        <v>3:11</v>
+        <v>4:13</v>
       </c>
       <c r="H118" t="str">
-        <v>Paul McCartney</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
       </c>
       <c r="L118" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>In The Stars - The Rolling Stones</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Hurts Like You</v>
+        <v>Home to Us</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-11</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Night Champion</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G119" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H119" t="str">
-        <v>Koe Wetzel</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
       </c>
       <c r="L119" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Home to Us - Paul McCartney</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Find Us Again</v>
+        <v>Hurts Like You</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-11</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Find Us Again - Single</v>
+        <v>The Night Champion</v>
       </c>
       <c r="G120" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H120" t="str">
-        <v>Xavi</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
       </c>
       <c r="L120" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hurts Like You - Koe Wetzel</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Tied Up</v>
+        <v>Find Us Again</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-11</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Tied Up - Single</v>
+        <v>Find Us Again - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H121" t="str">
-        <v>Khalid</v>
+        <v>Xavi</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
       </c>
       <c r="L121" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Find Us Again - Xavi</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Antes De Ti</v>
+        <v>Tied Up</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-11</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Tied Up - Single</v>
       </c>
       <c r="G122" t="str">
         <v>2:56</v>
       </c>
       <c r="H122" t="str">
-        <v>Silvana Estrada</v>
+        <v>Khalid</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/khalid/82842423</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
       </c>
       <c r="L122" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Tied Up - Khalid</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>En La Misma Cama</v>
+        <v>Antes De Ti</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-11</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>MUDA</v>
+        <v>Antes De Ti - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Carín León</v>
+        <v>Silvana Estrada</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
       </c>
       <c r="L123" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Antes De Ti - Silvana Estrada</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>lovergirl</v>
+        <v>En La Misma Cama</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-11</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>locket deluxe</v>
+        <v>MUDA</v>
       </c>
       <c r="G124" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H124" t="str">
-        <v>Madison Beer</v>
+        <v>Carín León</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
       </c>
       <c r="L124" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>En La Misma Cama - Carín León</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>PANIKI</v>
+        <v>lovergirl</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-11</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>locket deluxe</v>
       </c>
       <c r="G125" t="str">
-        <v>2:36</v>
+        <v>3:21</v>
       </c>
       <c r="H125" t="str">
-        <v>Chuyin</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
       </c>
       <c r="L125" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>lovergirl - Madison Beer</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>DesOrden</v>
+        <v>PANIKI</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-11</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>DesOrden - Single</v>
+        <v>Los Locos Nunca Mueren</v>
       </c>
       <c r="G126" t="str">
         <v>2:36</v>
       </c>
       <c r="H126" t="str">
-        <v>Alleh</v>
+        <v>Chuyin</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/paniki/1892533803</v>
       </c>
       <c r="L126" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>PANIKI - Chuyin</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>LA Nights</v>
+        <v>DesOrden</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-11</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>The Ville</v>
+        <v>DesOrden - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>2:18</v>
+        <v>2:36</v>
       </c>
       <c r="H127" t="str">
-        <v>Trap Dickey</v>
+        <v>Alleh</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/desorden/1896069663</v>
       </c>
       <c r="L127" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>DesOrden - Alleh</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>The Payoff</v>
+        <v>LA Nights</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-11</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Payoff - Single</v>
+        <v>The Ville</v>
       </c>
       <c r="G128" t="str">
-        <v>5:51</v>
+        <v>2:18</v>
       </c>
       <c r="H128" t="str">
-        <v>Father John Misty</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
       </c>
       <c r="L128" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>LA Nights - Trap Dickey</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>The Weak</v>
+        <v>The Payoff</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-11</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Payoff - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>3:15</v>
+        <v>5:51</v>
       </c>
       <c r="H129" t="str">
-        <v>Iceage</v>
+        <v>Father John Misty</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
       </c>
       <c r="L129" t="str">
-        <v>The Weak - Iceage</v>
+        <v>The Payoff - Father John Misty</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Life Of The Faaji</v>
+        <v>The Weak</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-11</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Fuji Xtra</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G130" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H130" t="str">
-        <v>Adekunle Gold</v>
+        <v>Iceage</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
       </c>
       <c r="L130" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>The Weak - Iceage</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Satisfy</v>
+        <v>Life Of The Faaji</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-11</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Satisfy - Single</v>
+        <v>Fuji Xtra</v>
       </c>
       <c r="G131" t="str">
-        <v>3:06</v>
+        <v>2:29</v>
       </c>
       <c r="H131" t="str">
-        <v>Calvin Harris</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
       </c>
       <c r="L131" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>Life Of The Faaji - Adekunle Gold</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>Satisfy</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-11</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>Satisfy - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H132" t="str">
-        <v>DEAN</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
       </c>
       <c r="L132" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>Satisfy - Calvin Harris</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-11</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:48</v>
+        <v>3:03</v>
       </c>
       <c r="H133" t="str">
-        <v>6LACK</v>
+        <v>DEAN</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/dean/2770824</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
       </c>
       <c r="L133" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>I Wanna Rock</v>
+        <v>Ashin' the Blunt</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-11</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G134" t="str">
-        <v>3:44</v>
+        <v>3:48</v>
       </c>
       <c r="H134" t="str">
-        <v>Cash Cobain</v>
+        <v>6LACK</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
       </c>
       <c r="L134" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Ashin' the Blunt - 6LACK</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-11</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>4:33</v>
+        <v>3:44</v>
       </c>
       <c r="H135" t="str">
-        <v>James Blake</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L135" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>One Two Police</v>
+        <v>Trying Times - A COLORS SHOW</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-11</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>One Two Police - Single</v>
+        <v>Trying Times - A COLORS SHOW - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:46</v>
+        <v>4:33</v>
       </c>
       <c r="H136" t="str">
-        <v>BUNT.</v>
+        <v>James Blake</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
       </c>
       <c r="L136" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>Trying Times - A COLORS SHOW - James Blake</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>One Two Police</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-11</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>One Two Police - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:16</v>
+        <v>2:46</v>
       </c>
       <c r="H137" t="str">
-        <v>Stephen Sanchez</v>
+        <v>BUNT.</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
       </c>
       <c r="L137" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>One Two Police - BUNT.</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Illuminate</v>
+        <v>HOME TO MOTHER</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-11</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G138" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H138" t="str">
-        <v>Jessie Reyez</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
       </c>
       <c r="L138" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>HOME TO MOTHER - Stephen Sanchez</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>OKAY!</v>
+        <v>Illuminate</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-11</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>OKAY! - Single</v>
+        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>4:34</v>
+        <v>3:03</v>
       </c>
       <c r="H139" t="str">
-        <v>Forrest Frank</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
       </c>
       <c r="L139" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>Illuminate - Jessie Reyez</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>FLOW</v>
+        <v>OKAY!</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-11</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>FLOW - Single</v>
+        <v>OKAY! - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>4:20</v>
+        <v>4:34</v>
       </c>
       <c r="H140" t="str">
-        <v>iZaak</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/okay/1896077066</v>
       </c>
       <c r="L140" t="str">
-        <v>FLOW - iZaak</v>
+        <v>OKAY! - Forrest Frank</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>aiaiaiaiai</v>
+        <v>FLOW</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-11</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>FLOW - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:20</v>
+        <v>4:20</v>
       </c>
       <c r="H141" t="str">
-        <v>Mau y Ricky</v>
+        <v>iZaak</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/flow/1895961693</v>
       </c>
       <c r="L141" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>FLOW - iZaak</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Control</v>
+        <v>aiaiaiaiai</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-11</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>God Must Really Love Me</v>
+        <v>aiaiaiaiai - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:32</v>
+        <v>2:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Tori Kelly</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
       </c>
       <c r="L142" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>aiaiaiaiai - Mau y Ricky</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ORIGAMI!</v>
+        <v>Control</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-11</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>God Must Really Love Me</v>
       </c>
       <c r="G143" t="str">
-        <v>2:34</v>
+        <v>2:32</v>
       </c>
       <c r="H143" t="str">
-        <v>Kesha</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/control/1895974889</v>
       </c>
       <c r="L143" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Control - Tori Kelly</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Love Is Kind</v>
+        <v>ORIGAMI!</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-11</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>ORIGAMI! - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>4:07</v>
+        <v>2:34</v>
       </c>
       <c r="H144" t="str">
-        <v>The Chainsmokers</v>
+        <v>Kesha</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/kesha/334854763</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/origami/1892544026</v>
       </c>
       <c r="L144" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>ORIGAMI! - Kesha</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Love Is Kind</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-11</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Let It Die Here</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G145" t="str">
-        <v>4:00</v>
+        <v>4:07</v>
       </c>
       <c r="H145" t="str">
-        <v>Linda Perry</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
       </c>
       <c r="L145" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Love Is Kind - The Chainsmokers</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Playing God</v>
+        <v>Feathers In A Storm</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-11</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Decades</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G146" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H146" t="str">
-        <v>Motionless In White</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
       </c>
       <c r="L146" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Feathers In A Storm - Linda Perry</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Cut</v>
+        <v>Playing God</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-11</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>VINDICATE</v>
+        <v>Decades</v>
       </c>
       <c r="G147" t="str">
-        <v>3:59</v>
+        <v>3:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Black Veil Brides</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
       </c>
       <c r="L147" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Playing God - Motionless In White</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Freaking Out</v>
+        <v>Cut</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-11</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Over Before You Know It</v>
+        <v>VINDICATE</v>
       </c>
       <c r="G148" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H148" t="str">
-        <v>Michigander</v>
+        <v>Black Veil Brides</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/cut/1879494510</v>
       </c>
       <c r="L148" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Cut - Black Veil Brides</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FIYAH</v>
+        <v>Freaking Out</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-11</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>FIYAH - Single</v>
+        <v>Over Before You Know It</v>
       </c>
       <c r="G149" t="str">
-        <v>3:12</v>
+        <v>3:03</v>
       </c>
       <c r="H149" t="str">
-        <v>YG Marley</v>
+        <v>Michigander</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
       </c>
       <c r="L149" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Freaking Out - Michigander</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Ten to Midnight</v>
+        <v>FIYAH</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-11</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Wild</v>
+        <v>FIYAH - Single</v>
       </c>
       <c r="G150" t="str">
         <v>3:12</v>
       </c>
       <c r="H150" t="str">
-        <v>Ashley McBryde</v>
+        <v>YG Marley</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
       </c>
       <c r="L150" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>FIYAH - YG Marley</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Carry On</v>
+        <v>Ten to Midnight</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-11</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Carry On - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G151" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H151" t="str">
-        <v>Kenny Chesney</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
       </c>
       <c r="L151" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>Ten to Midnight - Ashley McBryde</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>[PRESS]</v>
+        <v>Carry On</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-11</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Carry On - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>1:40</v>
+        <v>3:00</v>
       </c>
       <c r="H152" t="str">
-        <v>Armani White</v>
+        <v>Kenny Chesney</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
       </c>
       <c r="L152" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Carry On - Kenny Chesney</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>[PRESS]</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-11</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>[PRESS] - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:17</v>
+        <v>1:40</v>
       </c>
       <c r="H153" t="str">
-        <v>Myles Smith</v>
+        <v>Armani White</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/press/1895898254</v>
       </c>
       <c r="L153" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>[PRESS] - Armani White</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Hold Me In The Dark</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-11</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G154" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H154" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
       </c>
       <c r="L154" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Hold Me In The Dark - Myles Smith</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-11</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H155" t="str">
-        <v>Mack Keane</v>
+        <v>Sebastián Yatra</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
       </c>
       <c r="L155" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Changes</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-11</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Changes - Single</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="G156" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H156" t="str">
-        <v>Tommy Richman</v>
+        <v>Mack Keane</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
       </c>
       <c r="L156" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Wide Eyed - Mack Keane</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Changes</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-11</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Changes - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>4:33</v>
+        <v>3:18</v>
       </c>
       <c r="H157" t="str">
-        <v>The War And Treaty</v>
+        <v>Tommy Richman</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/changes/1895418156</v>
       </c>
       <c r="L157" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Changes - Tommy Richman</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>depressed on the internet</v>
+        <v>Don't Say Goodbye</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-11</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>The Story of Michael and Tanya</v>
       </c>
       <c r="G158" t="str">
-        <v>2:57</v>
+        <v>4:33</v>
       </c>
       <c r="H158" t="str">
-        <v>Bea Miller</v>
+        <v>The War And Treaty</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
       </c>
       <c r="L158" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Don't Say Goodbye - The War And Treaty</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Dear Burt</v>
+        <v>depressed on the internet</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-11</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>depressed on the internet - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:53</v>
+        <v>2:57</v>
       </c>
       <c r="H159" t="str">
-        <v>Stephan Moccio</v>
+        <v>Bea Miller</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
       </c>
       <c r="L159" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>depressed on the internet - Bea Miller</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Alla Blues</v>
+        <v>Dear Burt</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-11</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Black Mozart</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G160" t="str">
-        <v>2:50</v>
+        <v>2:53</v>
       </c>
       <c r="H160" t="str">
-        <v>Jon Batiste</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
       </c>
       <c r="L160" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>Dear Burt - Stephan Moccio</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Think About Me</v>
+        <v>Alla Blues</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-11</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Think About Me - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G161" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H161" t="str">
-        <v>Gabriella Rose</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
       </c>
       <c r="L161" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>Alla Blues - Jon Batiste</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Meet Again</v>
+        <v>Think About Me</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-11</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Meet Again - Single</v>
+        <v>Think About Me - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>3:26</v>
+        <v>2:39</v>
       </c>
       <c r="H162" t="str">
-        <v>Kaskade</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
       </c>
       <c r="L162" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Think About Me - Gabriella Rose</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Happy Now</v>
+        <v>Meet Again</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-11</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>The Afterparty</v>
+        <v>Meet Again - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H163" t="str">
-        <v>Lykke Li</v>
+        <v>Kaskade</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
       </c>
       <c r="L163" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Meet Again - Kaskade</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Oblivion</v>
+        <v>Happy Now</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-11</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Oblivion - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G164" t="str">
-        <v>2:21</v>
+        <v>2:42</v>
       </c>
       <c r="H164" t="str">
-        <v>Agents Of Time</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
       </c>
       <c r="L164" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>Happy Now - Lykke Li</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Oblivion</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-11</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>Oblivion - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>4:03</v>
+        <v>2:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Papa Roach</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
       </c>
       <c r="L165" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Oblivion - Agents Of Time</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Top of the Hill</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-11</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>1:50</v>
+        <v>4:03</v>
       </c>
       <c r="H166" t="str">
-        <v>DDG</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
       </c>
       <c r="L166" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Oh Savannah</v>
+        <v>Top of the Hill</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-11</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Change Of Plans</v>
+        <v>Top of the Hill - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:05</v>
+        <v>1:50</v>
       </c>
       <c r="H167" t="str">
-        <v>49 Winchester</v>
+        <v>DDG</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/ddg/3954994</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
       </c>
       <c r="L167" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Top of the Hill - DDG</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Oh Savannah</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-11</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G168" t="str">
-        <v>2:29</v>
+        <v>3:05</v>
       </c>
       <c r="H168" t="str">
-        <v>Little Simz</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
       </c>
       <c r="L168" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Oh Savannah - 49 Winchester</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>How to Forget</v>
+        <v>Game On (feat. JT)</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-11</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>ARCADE</v>
+        <v>Sugar Girl - EP</v>
       </c>
       <c r="G169" t="str">
-        <v>4:01</v>
+        <v>2:29</v>
       </c>
       <c r="H169" t="str">
-        <v>Deb Never</v>
+        <v>Little Simz</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
       </c>
       <c r="L169" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Game On (feat. JT) - Little Simz</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>How to Forget</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-11</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G170" t="str">
-        <v>2:49</v>
+        <v>4:01</v>
       </c>
       <c r="H170" t="str">
-        <v>ear</v>
+        <v>Deb Never</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
       </c>
       <c r="L170" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>How to Forget - Deb Never</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Mirror</v>
+        <v>Ne Plus Ultra</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-11</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Mirror - Single</v>
+        <v>Ne Plus Ultra - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H171" t="str">
-        <v>MOD SUN</v>
+        <v>ear</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
       </c>
       <c r="L171" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>Ne Plus Ultra - ear</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Miel Con Licor</v>
+        <v>Mirror</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-11</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Bandera Blanca</v>
+        <v>Mirror - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H172" t="str">
-        <v>Christian Nodal</v>
+        <v>MOD SUN</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/mirror/1895402181</v>
       </c>
       <c r="L172" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Mirror - MOD SUN</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Miel Con Licor</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-11</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G173" t="str">
-        <v>3:31</v>
+        <v>3:27</v>
       </c>
       <c r="H173" t="str">
-        <v>aron!</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
       </c>
       <c r="L173" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Miel Con Licor - Christian Nodal</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown)</v>
+        <v>Macramé (feat. Mei Semones)</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
+        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-11</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>The Last Balloon</v>
+        <v>Macramé (feat. Mei Semones) - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H174" t="str">
-        <v>Tank and the Bangas</v>
+        <v>aron!</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-david-shaw-austin-brown/1882831446</v>
+        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
       </c>
       <c r="L174" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown) - Tank and the Bangas</v>
+        <v>Macramé (feat. Mei Semones) - aron!</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Nighttime (feat. David Shaw &amp; Austin Brown)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-11</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G175" t="str">
-        <v>5:14</v>
+        <v>3:14</v>
       </c>
       <c r="H175" t="str">
-        <v>Darkthrone</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-david-shaw-austin-brown/1882831446</v>
       </c>
       <c r="L175" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Nighttime (feat. David Shaw &amp; Austin Brown) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Cloudfall</v>
+        <v>They Found One Of My Graves</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-11</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Pre-Historic Metal</v>
       </c>
       <c r="G176" t="str">
-        <v>4:06</v>
+        <v>5:14</v>
       </c>
       <c r="H176" t="str">
-        <v>REZN</v>
+        <v>Darkthrone</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
       </c>
       <c r="L176" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>They Found One Of My Graves - Darkthrone</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Doom in Bloom</v>
+        <v>Cloudfall</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-11</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Hum of Hurt</v>
+        <v>Cycles in the Infinite Dream</v>
       </c>
       <c r="G177" t="str">
-        <v>3:17</v>
+        <v>4:06</v>
       </c>
       <c r="H177" t="str">
-        <v>Converge</v>
+        <v>REZN</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
       </c>
       <c r="L177" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Cloudfall - REZN</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Doom in Bloom</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-11</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Remember The Humans</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G178" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H178" t="str">
-        <v>Broken Social Scene</v>
+        <v>Converge</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
       </c>
       <c r="L178" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Doom in Bloom - Converge</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Zoom 97</v>
+        <v>Only The Good I Keep</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-11</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Remember The Humans</v>
       </c>
       <c r="G179" t="str">
-        <v>4:54</v>
+        <v>3:27</v>
       </c>
       <c r="H179" t="str">
-        <v>Kurt Vile</v>
+        <v>Broken Social Scene</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
       </c>
       <c r="L179" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Only The Good I Keep - Broken Social Scene</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Switch Up</v>
+        <v>Zoom 97</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-11</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Switch Up - Single</v>
+        <v>Philadelphia's been good to me</v>
       </c>
       <c r="G180" t="str">
-        <v>3:35</v>
+        <v>4:54</v>
       </c>
       <c r="H180" t="str">
-        <v>Mike D</v>
+        <v>Kurt Vile</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
       </c>
       <c r="L180" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>Zoom 97 - Kurt Vile</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Surprise</v>
+        <v>Switch Up</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-11</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Doe Or Die III</v>
+        <v>Switch Up - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H181" t="str">
-        <v>AZ</v>
+        <v>Mike D</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
       </c>
       <c r="L181" t="str">
-        <v>Surprise - AZ</v>
+        <v>Switch Up - Mike D</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Better Days</v>
+        <v>Surprise</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-11</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Better Days - Single</v>
+        <v>Doe Or Die III</v>
       </c>
       <c r="G182" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H182" t="str">
-        <v>Naomi Sharon</v>
+        <v>AZ</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/az/35299</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/surprise/1894873352</v>
       </c>
       <c r="L182" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Surprise - AZ</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>Better Days</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-11</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Better Days - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H183" t="str">
-        <v>Debbii Dawson</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/better-days/1895293758</v>
       </c>
       <c r="L183" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>Better Days - Naomi Sharon</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>No Pressure</v>
+        <v>Where Have All The Good Men Gone?</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-11</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>No Pressure - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H184" t="str">
-        <v>JYT</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
       </c>
       <c r="L184" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>What's the Point!</v>
+        <v>No Pressure</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-11</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>No Pressure - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>2:43</v>
+        <v>3:09</v>
       </c>
       <c r="H185" t="str">
-        <v>Emei</v>
+        <v>JYT</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
       </c>
       <c r="L185" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>No Pressure - JYT</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Pachamama</v>
+        <v>What's the Point!</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-11</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Así Es La Vida</v>
+        <v>Night at the Opera - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>3:20</v>
+        <v>2:43</v>
       </c>
       <c r="H186" t="str">
-        <v>Codiciado</v>
+        <v>Emei</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/emei/1583968554</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
       </c>
       <c r="L186" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>What's the Point! - Emei</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Multiplied</v>
+        <v>Pachamama</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-11</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Multiplied - Single</v>
+        <v>Así Es La Vida</v>
       </c>
       <c r="G187" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H187" t="str">
-        <v>Luna Li</v>
+        <v>Codiciado</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
       </c>
       <c r="L187" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Pachamama - Codiciado</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Six String</v>
+        <v>Multiplied</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-11</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Six String - Single</v>
+        <v>Multiplied - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H188" t="str">
-        <v>Lila Dupont</v>
+        <v>Luna Li</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
       </c>
       <c r="L188" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Multiplied - Luna Li</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Take Heart</v>
+        <v>Six String</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-11</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Harbour</v>
+        <v>Six String - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:07</v>
+        <v>3:11</v>
       </c>
       <c r="H189" t="str">
-        <v>Jon Bryant</v>
+        <v>Lila Dupont</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/six-string/1892171725</v>
       </c>
       <c r="L189" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Six String - Lila Dupont</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Clarion</v>
+        <v>Take Heart</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-11</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>You Are Spring!</v>
+        <v>Harbour</v>
       </c>
       <c r="G190" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H190" t="str">
-        <v>Tasha</v>
+        <v>Jon Bryant</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
       </c>
       <c r="L190" t="str">
-        <v>Clarion - Tasha</v>
+        <v>Take Heart - Jon Bryant</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Stepping Stone</v>
+        <v>Clarion</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-11</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Beams - Single</v>
+        <v>You Are Spring!</v>
       </c>
       <c r="G191" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H191" t="str">
-        <v>DERBY</v>
+        <v>Tasha</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/clarion/1887589690</v>
       </c>
       <c r="L191" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>Clarion - Tasha</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>confessions part iii</v>
+        <v>Stepping Stone</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-11</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>autogratis</v>
+        <v>Beams - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:01</v>
+        <v>2:49</v>
       </c>
       <c r="H192" t="str">
-        <v>Chanpan</v>
+        <v>DERBY</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/derby/1772719795</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
       </c>
       <c r="L192" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Stepping Stone - DERBY</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>cherry garcia</v>
+        <v>confessions part iii</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-11</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>cherry garcia - Single</v>
+        <v>autogratis</v>
       </c>
       <c r="G193" t="str">
-        <v>2:30</v>
+        <v>2:01</v>
       </c>
       <c r="H193" t="str">
-        <v>supermodel*</v>
+        <v>Chanpan</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
       </c>
       <c r="L193" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>confessions part iii - Chanpan</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Disco Cherry</v>
+        <v>cherry garcia</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-11</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>cherry garcia - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:20</v>
+        <v>2:30</v>
       </c>
       <c r="H194" t="str">
-        <v>Purple Disco Machine</v>
+        <v>supermodel*</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
       </c>
       <c r="L194" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>cherry garcia - supermodel*</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Tal Vez</v>
+        <v>Disco Cherry</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-11</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>El Amante</v>
+        <v>Disco Cherry - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H195" t="str">
-        <v>Dariel Amant</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
       </c>
       <c r="L195" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>Disco Cherry - Purple Disco Machine</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Voyager</v>
+        <v>Tal Vez</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-11</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Voyager - Single</v>
+        <v>El Amante</v>
       </c>
       <c r="G196" t="str">
-        <v>4:37</v>
+        <v>2:14</v>
       </c>
       <c r="H196" t="str">
-        <v>Chance Peña</v>
+        <v>Dariel Amant</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
       </c>
       <c r="L196" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Tal Vez - Dariel Amant</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-11</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H197" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Chance Peña</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
       </c>
       <c r="L197" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>The Voyager - Chance Peña</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Buy What U Want</v>
+        <v>Pictures of You</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-11</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>Pictures of You</v>
       </c>
       <c r="G198" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H198" t="str">
-        <v>Black Fortune</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
       </c>
       <c r="L198" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Pictures of You - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-11</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Road To Osshland: The Series</v>
       </c>
       <c r="G199" t="str">
-        <v>2:29</v>
+        <v>3:47</v>
       </c>
       <c r="H199" t="str">
-        <v>Lil Naay</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
       </c>
       <c r="L199" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>high school sweetheart</v>
+        <v>MOOD BRAZIL</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-11</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>ashley cooke</v>
+        <v>MOOD BRAZIL - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H200" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lil Naay</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
       </c>
       <c r="L200" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>MOOD BRAZIL - Lil Naay</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>high school sweetheart</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-11</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>ashley cooke</v>
       </c>
       <c r="G201" t="str">
-        <v>2:55</v>
+        <v>3:11</v>
       </c>
       <c r="H201" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
       </c>
       <c r="L201" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>big plans</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-11</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>counting horses</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H202" t="str">
-        <v>Tom Siletto</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
       </c>
       <c r="L202" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Running</v>
+        <v>big plans</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-11</v>
@@ -8089,68 +8089,106 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Running - Single</v>
+        <v>counting horses</v>
       </c>
       <c r="G203" t="str">
-        <v>2:38</v>
+        <v>3:14</v>
       </c>
       <c r="H203" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
       </c>
       <c r="L203" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>big plans - Tom Siletto</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
+        <v>Running</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/running/6764878724</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Running - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/running/1895947036</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Running - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
         <v>FA-TAL!</v>
       </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
-      <c r="D204" t="str">
-        <v>2026-05-11</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
+      <c r="D205" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
         <v>FA-TAL! - Single</v>
       </c>
-      <c r="G204" t="str">
+      <c r="G205" t="str">
         <v>2:46</v>
       </c>
-      <c r="H204" t="str">
+      <c r="H205" t="str">
         <v>ROBI</v>
       </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
         <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
-      <c r="K204" t="str">
+      <c r="K205" t="str">
         <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
       </c>
-      <c r="L204" t="str">
+      <c r="L205" t="str">
         <v>FA-TAL! - ROBI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L204"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>1 month ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 month ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Una A La Vez</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-11</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>OMERTA</v>
+        <v>American Stories</v>
       </c>
       <c r="G102" t="str">
-        <v>2:32</v>
+        <v>3:53</v>
       </c>
       <c r="H102" t="str">
-        <v>J Balvin</v>
+        <v>Rostam</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L102" t="str">
-        <v>Una A La Vez - J Balvin</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Una A La Vez</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-11</v>
@@ -4289,25 +4289,25 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>American Stories</v>
+        <v>OMERTA</v>
       </c>
       <c r="G103" t="str">
-        <v>3:53</v>
+        <v>2:32</v>
       </c>
       <c r="H103" t="str">
-        <v>Rostam</v>
+        <v>J Balvin</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
       </c>
       <c r="L103" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Una A La Vez - J Balvin</v>
       </c>
     </row>
     <row r="104">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -7010,13 +7010,13 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown)</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-david-shaw-austin-brown/1882831738</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-11</v>
@@ -7040,10 +7040,10 @@
         <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-david-shaw-austin-brown/1882831446</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
       </c>
       <c r="L175" t="str">
-        <v>Nighttime (feat. David Shaw &amp; Austin Brown) - Tank and the Bangas</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="176">

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-12</v>
       </c>
       <c r="E205" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>10 days ago</v>
+        <v>11 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Hardy (feat. Clairo)</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-12</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>American Stories</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G102" t="str">
-        <v>3:53</v>
+        <v>2:27</v>
       </c>
       <c r="H102" t="str">
-        <v>Rostam</v>
+        <v>MICO</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L102" t="str">
-        <v>Hardy (feat. Clairo) - Rostam</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Una A La Vez</v>
+        <v>Hardy (feat. Clairo)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
+        <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D103" t="str">
         <v>2026-05-12</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>OMERTA</v>
+        <v>American Stories</v>
       </c>
       <c r="G103" t="str">
-        <v>2:32</v>
+        <v>3:53</v>
       </c>
       <c r="H103" t="str">
-        <v>J Balvin</v>
+        <v>Rostam</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
+        <v>https://music.apple.com/us/artist/rostam/1245703560</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
+        <v>https://music.apple.com/us/album/hardy-feat-clairo/1876952750</v>
       </c>
       <c r="L103" t="str">
-        <v>Una A La Vez - J Balvin</v>
+        <v>Hardy (feat. Clairo) - Rostam</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Rock Music</v>
+        <v>Una A La Vez</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
+        <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D104" t="str">
         <v>2026-05-12</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Rock Music - Single</v>
+        <v>OMERTA</v>
       </c>
       <c r="G104" t="str">
-        <v>1:55</v>
+        <v>2:32</v>
       </c>
       <c r="H104" t="str">
-        <v>Charli xcx</v>
+        <v>J Balvin</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
+        <v>https://music.apple.com/us/artist/j-balvin/444520760</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
+        <v>https://music.apple.com/us/album/una-a-la-vez/1890287852</v>
       </c>
       <c r="L104" t="str">
-        <v>Rock Music - Charli xcx</v>
+        <v>Una A La Vez - J Balvin</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>TNT</v>
+        <v>Rock Music</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/tnt/1887671066</v>
+        <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D105" t="str">
         <v>2026-05-12</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>GREENGREEN - EP</v>
+        <v>Rock Music - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:02</v>
+        <v>1:55</v>
       </c>
       <c r="H105" t="str">
-        <v>CORTIS</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
+        <v>https://music.apple.com/us/artist/charli-xcx/432942256</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/tnt/1887671065</v>
+        <v>https://music.apple.com/us/album/rock-music/6766314069</v>
       </c>
       <c r="L105" t="str">
-        <v>TNT - CORTIS</v>
+        <v>Rock Music - Charli xcx</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Go</v>
+        <v>TNT</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/go/6765588421</v>
+        <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D106" t="str">
         <v>2026-05-12</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Go - Single</v>
+        <v>GREENGREEN - EP</v>
       </c>
       <c r="G106" t="str">
-        <v>2:24</v>
+        <v>2:02</v>
       </c>
       <c r="H106" t="str">
-        <v>Key Glock</v>
+        <v>CORTIS</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
+        <v>https://music.apple.com/us/artist/cortis/1831651635</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/go/1896001876</v>
+        <v>https://music.apple.com/us/album/tnt/1887671065</v>
       </c>
       <c r="L106" t="str">
-        <v>Go - Key Glock</v>
+        <v>TNT - CORTIS</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>For The Moment</v>
+        <v>Go</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
+        <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D107" t="str">
         <v>2026-05-12</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>BROWN</v>
+        <v>Go - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:26</v>
+        <v>2:24</v>
       </c>
       <c r="H107" t="str">
-        <v>Chris Brown</v>
+        <v>Key Glock</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/key-glock/1199258326</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
+        <v>https://music.apple.com/us/album/go/1896001876</v>
       </c>
       <c r="L107" t="str">
-        <v>For The Moment - Chris Brown</v>
+        <v>Go - Key Glock</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Smoking pt. 2</v>
+        <v>For The Moment</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
+        <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D108" t="str">
         <v>2026-05-12</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Wave Gods 2: Cosmos Brothers</v>
+        <v>BROWN</v>
       </c>
       <c r="G108" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H108" t="str">
-        <v>French Montana</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
+        <v>https://music.apple.com/us/album/for-the-moment/1895772091</v>
       </c>
       <c r="L108" t="str">
-        <v>Smoking pt. 2 - French Montana</v>
+        <v>For The Moment - Chris Brown</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Therapy at the Club</v>
+        <v>Smoking pt. 2</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D109" t="str">
         <v>2026-05-12</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>Wave Gods 2: Cosmos Brothers</v>
       </c>
       <c r="G109" t="str">
-        <v>2:47</v>
+        <v>3:21</v>
       </c>
       <c r="H109" t="str">
-        <v>FLO</v>
+        <v>French Montana</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/french-montana/475816358</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v>https://music.apple.com/us/album/smoking-pt-2/1894333428</v>
       </c>
       <c r="L109" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Smoking pt. 2 - French Montana</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>linknb</v>
+        <v>Therapy at the Club</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-12</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>new avatar</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G110" t="str">
-        <v>1:55</v>
+        <v>2:47</v>
       </c>
       <c r="H110" t="str">
-        <v>Kelela</v>
+        <v>FLO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
       </c>
       <c r="L110" t="str">
-        <v>linknb - Kelela</v>
+        <v>Therapy at the Club - FLO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-12</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G111" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H111" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L111" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Baby</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-12</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Baby - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H112" t="str">
-        <v>Prospa</v>
+        <v>elkan</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L112" t="str">
-        <v>Baby - Prospa</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Baby</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-12</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>Baby - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:39</v>
+        <v>3:13</v>
       </c>
       <c r="H113" t="str">
-        <v>Russell Dickerson</v>
+        <v>Prospa</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/baby/1895418297</v>
       </c>
       <c r="L113" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Baby - Prospa</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Bed of Roses</v>
+        <v>Boots (feat. Fetty Wap)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-12</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Boots (feat. Fetty Wap) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H114" t="str">
-        <v>Teyana Taylor</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
       </c>
       <c r="L114" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Bed of Roses</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-12</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>Bed of Roses - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H115" t="str">
-        <v>Bruno Mars</v>
+        <v>Teyana Taylor</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
       </c>
       <c r="L115" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Bed of Roses - Teyana Taylor</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Big Dog</v>
+        <v>Lo Arriesgo Todo</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-12</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Big Dog - Single</v>
+        <v>Lo Arriesgo Todo - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H116" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
       </c>
       <c r="L116" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Lo Arriesgo Todo - Bruno Mars</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Eastside Girls</v>
+        <v>Big Dog</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-12</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Big Dog - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H117" t="str">
-        <v>MUNA</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
       </c>
       <c r="L117" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>Big Dog - The Last Dinner Party</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>In The Stars</v>
+        <v>Eastside Girls</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-12</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Foreign Tongues</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G118" t="str">
-        <v>4:13</v>
+        <v>3:50</v>
       </c>
       <c r="H118" t="str">
-        <v>The Rolling Stones</v>
+        <v>MUNA</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
       </c>
       <c r="L118" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Eastside Girls - MUNA</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Home to Us</v>
+        <v>In The Stars</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-12</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Foreign Tongues</v>
       </c>
       <c r="G119" t="str">
-        <v>3:11</v>
+        <v>4:13</v>
       </c>
       <c r="H119" t="str">
-        <v>Paul McCartney</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
       </c>
       <c r="L119" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>In The Stars - The Rolling Stones</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Hurts Like You</v>
+        <v>Home to Us</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-12</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Night Champion</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G120" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H120" t="str">
-        <v>Koe Wetzel</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
       </c>
       <c r="L120" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Home to Us - Paul McCartney</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Find Us Again</v>
+        <v>Hurts Like You</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-12</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Find Us Again - Single</v>
+        <v>The Night Champion</v>
       </c>
       <c r="G121" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H121" t="str">
-        <v>Xavi</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
       </c>
       <c r="L121" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hurts Like You - Koe Wetzel</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Tied Up</v>
+        <v>Find Us Again</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-12</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Tied Up - Single</v>
+        <v>Find Us Again - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H122" t="str">
-        <v>Khalid</v>
+        <v>Xavi</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
       </c>
       <c r="L122" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Find Us Again - Xavi</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Antes De Ti</v>
+        <v>Tied Up</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-12</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Tied Up - Single</v>
       </c>
       <c r="G123" t="str">
         <v>2:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Silvana Estrada</v>
+        <v>Khalid</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/khalid/82842423</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
       </c>
       <c r="L123" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Tied Up - Khalid</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>En La Misma Cama</v>
+        <v>Antes De Ti</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-12</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>MUDA</v>
+        <v>Antes De Ti - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Carín León</v>
+        <v>Silvana Estrada</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
       </c>
       <c r="L124" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Antes De Ti - Silvana Estrada</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>lovergirl</v>
+        <v>En La Misma Cama</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-12</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>locket deluxe</v>
+        <v>MUDA</v>
       </c>
       <c r="G125" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H125" t="str">
-        <v>Madison Beer</v>
+        <v>Carín León</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
       </c>
       <c r="L125" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>En La Misma Cama - Carín León</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>PANIKI</v>
+        <v>lovergirl</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-12</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>locket deluxe</v>
       </c>
       <c r="G126" t="str">
-        <v>2:36</v>
+        <v>3:21</v>
       </c>
       <c r="H126" t="str">
-        <v>Chuyin</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
       </c>
       <c r="L126" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>lovergirl - Madison Beer</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>DesOrden</v>
+        <v>PANIKI</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-12</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>DesOrden - Single</v>
+        <v>Los Locos Nunca Mueren</v>
       </c>
       <c r="G127" t="str">
         <v>2:36</v>
       </c>
       <c r="H127" t="str">
-        <v>Alleh</v>
+        <v>Chuyin</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/paniki/1892533803</v>
       </c>
       <c r="L127" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>PANIKI - Chuyin</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>LA Nights</v>
+        <v>DesOrden</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-12</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>The Ville</v>
+        <v>DesOrden - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>2:18</v>
+        <v>2:36</v>
       </c>
       <c r="H128" t="str">
-        <v>Trap Dickey</v>
+        <v>Alleh</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/desorden/1896069663</v>
       </c>
       <c r="L128" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>DesOrden - Alleh</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>The Payoff</v>
+        <v>LA Nights</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-12</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>The Payoff - Single</v>
+        <v>The Ville</v>
       </c>
       <c r="G129" t="str">
-        <v>5:51</v>
+        <v>2:18</v>
       </c>
       <c r="H129" t="str">
-        <v>Father John Misty</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
       </c>
       <c r="L129" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>LA Nights - Trap Dickey</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>The Weak</v>
+        <v>The Payoff</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-12</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Payoff - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:15</v>
+        <v>5:51</v>
       </c>
       <c r="H130" t="str">
-        <v>Iceage</v>
+        <v>Father John Misty</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
       </c>
       <c r="L130" t="str">
-        <v>The Weak - Iceage</v>
+        <v>The Payoff - Father John Misty</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Life Of The Faaji</v>
+        <v>The Weak</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-12</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Fuji Xtra</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G131" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H131" t="str">
-        <v>Adekunle Gold</v>
+        <v>Iceage</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
       </c>
       <c r="L131" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>The Weak - Iceage</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Satisfy</v>
+        <v>Life Of The Faaji</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-12</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Satisfy - Single</v>
+        <v>Fuji Xtra</v>
       </c>
       <c r="G132" t="str">
-        <v>3:06</v>
+        <v>2:29</v>
       </c>
       <c r="H132" t="str">
-        <v>Calvin Harris</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
       </c>
       <c r="L132" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>Life Of The Faaji - Adekunle Gold</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>Satisfy</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-12</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>Satisfy - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H133" t="str">
-        <v>DEAN</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
       </c>
       <c r="L133" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>Satisfy - Calvin Harris</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-12</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:48</v>
+        <v>3:03</v>
       </c>
       <c r="H134" t="str">
-        <v>6LACK</v>
+        <v>DEAN</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/dean/2770824</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
       </c>
       <c r="L134" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>I Wanna Rock</v>
+        <v>Ashin' the Blunt</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-12</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G135" t="str">
-        <v>3:44</v>
+        <v>3:48</v>
       </c>
       <c r="H135" t="str">
-        <v>Cash Cobain</v>
+        <v>6LACK</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
       </c>
       <c r="L135" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Ashin' the Blunt - 6LACK</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-12</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>4:33</v>
+        <v>3:44</v>
       </c>
       <c r="H136" t="str">
-        <v>James Blake</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L136" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>One Two Police</v>
+        <v>Trying Times - A COLORS SHOW</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-12</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>One Two Police - Single</v>
+        <v>Trying Times - A COLORS SHOW - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>2:46</v>
+        <v>4:33</v>
       </c>
       <c r="H137" t="str">
-        <v>BUNT.</v>
+        <v>James Blake</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
       </c>
       <c r="L137" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>Trying Times - A COLORS SHOW - James Blake</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>One Two Police</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-12</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>One Two Police - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>3:16</v>
+        <v>2:46</v>
       </c>
       <c r="H138" t="str">
-        <v>Stephen Sanchez</v>
+        <v>BUNT.</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
       </c>
       <c r="L138" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>One Two Police - BUNT.</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Illuminate</v>
+        <v>HOME TO MOTHER</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-12</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G139" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H139" t="str">
-        <v>Jessie Reyez</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
       </c>
       <c r="L139" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>HOME TO MOTHER - Stephen Sanchez</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>OKAY!</v>
+        <v>Illuminate</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-12</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>OKAY! - Single</v>
+        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>4:34</v>
+        <v>3:03</v>
       </c>
       <c r="H140" t="str">
-        <v>Forrest Frank</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
       </c>
       <c r="L140" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>Illuminate - Jessie Reyez</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>FLOW</v>
+        <v>OKAY!</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-12</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>FLOW - Single</v>
+        <v>OKAY! - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>4:20</v>
+        <v>4:34</v>
       </c>
       <c r="H141" t="str">
-        <v>iZaak</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/okay/1896077066</v>
       </c>
       <c r="L141" t="str">
-        <v>FLOW - iZaak</v>
+        <v>OKAY! - Forrest Frank</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>aiaiaiaiai</v>
+        <v>FLOW</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-12</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>FLOW - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:20</v>
+        <v>4:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Mau y Ricky</v>
+        <v>iZaak</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/flow/1895961693</v>
       </c>
       <c r="L142" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>FLOW - iZaak</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Control</v>
+        <v>aiaiaiaiai</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-12</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>God Must Really Love Me</v>
+        <v>aiaiaiaiai - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:32</v>
+        <v>2:20</v>
       </c>
       <c r="H143" t="str">
-        <v>Tori Kelly</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
       </c>
       <c r="L143" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>aiaiaiaiai - Mau y Ricky</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ORIGAMI!</v>
+        <v>Control</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-12</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>God Must Really Love Me</v>
       </c>
       <c r="G144" t="str">
-        <v>2:34</v>
+        <v>2:32</v>
       </c>
       <c r="H144" t="str">
-        <v>Kesha</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/control/1895974889</v>
       </c>
       <c r="L144" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Control - Tori Kelly</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Love Is Kind</v>
+        <v>ORIGAMI!</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-12</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>ORIGAMI! - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>4:07</v>
+        <v>2:34</v>
       </c>
       <c r="H145" t="str">
-        <v>The Chainsmokers</v>
+        <v>Kesha</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/kesha/334854763</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/origami/1892544026</v>
       </c>
       <c r="L145" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>ORIGAMI! - Kesha</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Love Is Kind</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-12</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Let It Die Here</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G146" t="str">
-        <v>4:00</v>
+        <v>4:07</v>
       </c>
       <c r="H146" t="str">
-        <v>Linda Perry</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
       </c>
       <c r="L146" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Love Is Kind - The Chainsmokers</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Playing God</v>
+        <v>Feathers In A Storm</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-12</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Decades</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G147" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H147" t="str">
-        <v>Motionless In White</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
       </c>
       <c r="L147" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Feathers In A Storm - Linda Perry</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Cut</v>
+        <v>Playing God</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-12</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>VINDICATE</v>
+        <v>Decades</v>
       </c>
       <c r="G148" t="str">
-        <v>3:59</v>
+        <v>3:39</v>
       </c>
       <c r="H148" t="str">
-        <v>Black Veil Brides</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
       </c>
       <c r="L148" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Playing God - Motionless In White</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Freaking Out</v>
+        <v>Cut</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-12</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Over Before You Know It</v>
+        <v>VINDICATE</v>
       </c>
       <c r="G149" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H149" t="str">
-        <v>Michigander</v>
+        <v>Black Veil Brides</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/cut/1879494510</v>
       </c>
       <c r="L149" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Cut - Black Veil Brides</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>FIYAH</v>
+        <v>Freaking Out</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-12</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>FIYAH - Single</v>
+        <v>Over Before You Know It</v>
       </c>
       <c r="G150" t="str">
-        <v>3:12</v>
+        <v>3:03</v>
       </c>
       <c r="H150" t="str">
-        <v>YG Marley</v>
+        <v>Michigander</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
       </c>
       <c r="L150" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Freaking Out - Michigander</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Ten to Midnight</v>
+        <v>FIYAH</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-12</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Wild</v>
+        <v>FIYAH - Single</v>
       </c>
       <c r="G151" t="str">
         <v>3:12</v>
       </c>
       <c r="H151" t="str">
-        <v>Ashley McBryde</v>
+        <v>YG Marley</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
       </c>
       <c r="L151" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>FIYAH - YG Marley</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Carry On</v>
+        <v>Ten to Midnight</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-12</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Carry On - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G152" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H152" t="str">
-        <v>Kenny Chesney</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
       </c>
       <c r="L152" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>Ten to Midnight - Ashley McBryde</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>[PRESS]</v>
+        <v>Carry On</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-12</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Carry On - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>1:40</v>
+        <v>3:00</v>
       </c>
       <c r="H153" t="str">
-        <v>Armani White</v>
+        <v>Kenny Chesney</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
       </c>
       <c r="L153" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Carry On - Kenny Chesney</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>[PRESS]</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-12</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>[PRESS] - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:17</v>
+        <v>1:40</v>
       </c>
       <c r="H154" t="str">
-        <v>Myles Smith</v>
+        <v>Armani White</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/press/1895898254</v>
       </c>
       <c r="L154" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>[PRESS] - Armani White</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Hold Me In The Dark</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-12</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G155" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H155" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
       </c>
       <c r="L155" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Hold Me In The Dark - Myles Smith</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-12</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H156" t="str">
-        <v>Mack Keane</v>
+        <v>Sebastián Yatra</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
       </c>
       <c r="L156" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Changes</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-12</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Changes - Single</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="G157" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H157" t="str">
-        <v>Tommy Richman</v>
+        <v>Mack Keane</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
       </c>
       <c r="L157" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Wide Eyed - Mack Keane</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Changes</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-12</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Changes - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>4:33</v>
+        <v>3:18</v>
       </c>
       <c r="H158" t="str">
-        <v>The War And Treaty</v>
+        <v>Tommy Richman</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/changes/1895418156</v>
       </c>
       <c r="L158" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Changes - Tommy Richman</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>depressed on the internet</v>
+        <v>Don't Say Goodbye</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-12</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>The Story of Michael and Tanya</v>
       </c>
       <c r="G159" t="str">
-        <v>2:57</v>
+        <v>4:33</v>
       </c>
       <c r="H159" t="str">
-        <v>Bea Miller</v>
+        <v>The War And Treaty</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
       </c>
       <c r="L159" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Don't Say Goodbye - The War And Treaty</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Dear Burt</v>
+        <v>depressed on the internet</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-12</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>depressed on the internet - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:53</v>
+        <v>2:57</v>
       </c>
       <c r="H160" t="str">
-        <v>Stephan Moccio</v>
+        <v>Bea Miller</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
       </c>
       <c r="L160" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>depressed on the internet - Bea Miller</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Alla Blues</v>
+        <v>Dear Burt</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-12</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Black Mozart</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G161" t="str">
-        <v>2:50</v>
+        <v>2:53</v>
       </c>
       <c r="H161" t="str">
-        <v>Jon Batiste</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
       </c>
       <c r="L161" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>Dear Burt - Stephan Moccio</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Think About Me</v>
+        <v>Alla Blues</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-12</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Think About Me - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G162" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H162" t="str">
-        <v>Gabriella Rose</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
       </c>
       <c r="L162" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>Alla Blues - Jon Batiste</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Meet Again</v>
+        <v>Think About Me</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-12</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Meet Again - Single</v>
+        <v>Think About Me - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:26</v>
+        <v>2:39</v>
       </c>
       <c r="H163" t="str">
-        <v>Kaskade</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
       </c>
       <c r="L163" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Think About Me - Gabriella Rose</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Happy Now</v>
+        <v>Meet Again</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-12</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>The Afterparty</v>
+        <v>Meet Again - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H164" t="str">
-        <v>Lykke Li</v>
+        <v>Kaskade</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
       </c>
       <c r="L164" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Meet Again - Kaskade</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Oblivion</v>
+        <v>Happy Now</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-12</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Oblivion - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G165" t="str">
-        <v>2:21</v>
+        <v>2:42</v>
       </c>
       <c r="H165" t="str">
-        <v>Agents Of Time</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
       </c>
       <c r="L165" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>Happy Now - Lykke Li</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Oblivion</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-12</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>Oblivion - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>4:03</v>
+        <v>2:21</v>
       </c>
       <c r="H166" t="str">
-        <v>Papa Roach</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
       </c>
       <c r="L166" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Oblivion - Agents Of Time</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Top of the Hill</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-12</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>1:50</v>
+        <v>4:03</v>
       </c>
       <c r="H167" t="str">
-        <v>DDG</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
       </c>
       <c r="L167" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Oh Savannah</v>
+        <v>Top of the Hill</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-12</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Change Of Plans</v>
+        <v>Top of the Hill - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>3:05</v>
+        <v>1:50</v>
       </c>
       <c r="H168" t="str">
-        <v>49 Winchester</v>
+        <v>DDG</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/ddg/3954994</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
       </c>
       <c r="L168" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Top of the Hill - DDG</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Oh Savannah</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-12</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G169" t="str">
-        <v>2:29</v>
+        <v>3:05</v>
       </c>
       <c r="H169" t="str">
-        <v>Little Simz</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
       </c>
       <c r="L169" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Oh Savannah - 49 Winchester</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>How to Forget</v>
+        <v>Game On (feat. JT)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-12</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>ARCADE</v>
+        <v>Sugar Girl - EP</v>
       </c>
       <c r="G170" t="str">
-        <v>4:01</v>
+        <v>2:29</v>
       </c>
       <c r="H170" t="str">
-        <v>Deb Never</v>
+        <v>Little Simz</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
       </c>
       <c r="L170" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Game On (feat. JT) - Little Simz</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>How to Forget</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-12</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G171" t="str">
-        <v>2:49</v>
+        <v>4:01</v>
       </c>
       <c r="H171" t="str">
-        <v>ear</v>
+        <v>Deb Never</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
       </c>
       <c r="L171" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>How to Forget - Deb Never</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Mirror</v>
+        <v>Ne Plus Ultra</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-12</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Mirror - Single</v>
+        <v>Ne Plus Ultra - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H172" t="str">
-        <v>MOD SUN</v>
+        <v>ear</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
       </c>
       <c r="L172" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>Ne Plus Ultra - ear</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Miel Con Licor</v>
+        <v>Mirror</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-12</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Bandera Blanca</v>
+        <v>Mirror - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H173" t="str">
-        <v>Christian Nodal</v>
+        <v>MOD SUN</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/mirror/1895402181</v>
       </c>
       <c r="L173" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Mirror - MOD SUN</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Miel Con Licor</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-12</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G174" t="str">
-        <v>3:31</v>
+        <v>3:27</v>
       </c>
       <c r="H174" t="str">
-        <v>aron!</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
       </c>
       <c r="L174" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Miel Con Licor - Christian Nodal</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
+        <v>Macramé (feat. Mei Semones)</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
+        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-12</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>The Last Balloon</v>
+        <v>Macramé (feat. Mei Semones) - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H175" t="str">
-        <v>Tank and the Bangas</v>
+        <v>aron!</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
+        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
       </c>
       <c r="L175" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
+        <v>Macramé (feat. Mei Semones) - aron!</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-12</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G176" t="str">
-        <v>5:14</v>
+        <v>3:14</v>
       </c>
       <c r="H176" t="str">
-        <v>Darkthrone</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
       </c>
       <c r="L176" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Cloudfall</v>
+        <v>They Found One Of My Graves</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-12</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Pre-Historic Metal</v>
       </c>
       <c r="G177" t="str">
-        <v>4:06</v>
+        <v>5:14</v>
       </c>
       <c r="H177" t="str">
-        <v>REZN</v>
+        <v>Darkthrone</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
       </c>
       <c r="L177" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>They Found One Of My Graves - Darkthrone</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Doom in Bloom</v>
+        <v>Cloudfall</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-12</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Hum of Hurt</v>
+        <v>Cycles in the Infinite Dream</v>
       </c>
       <c r="G178" t="str">
-        <v>3:17</v>
+        <v>4:06</v>
       </c>
       <c r="H178" t="str">
-        <v>Converge</v>
+        <v>REZN</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
       </c>
       <c r="L178" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Cloudfall - REZN</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Doom in Bloom</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-12</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Remember The Humans</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G179" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H179" t="str">
-        <v>Broken Social Scene</v>
+        <v>Converge</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
       </c>
       <c r="L179" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Doom in Bloom - Converge</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Zoom 97</v>
+        <v>Only The Good I Keep</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-12</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Remember The Humans</v>
       </c>
       <c r="G180" t="str">
-        <v>4:54</v>
+        <v>3:27</v>
       </c>
       <c r="H180" t="str">
-        <v>Kurt Vile</v>
+        <v>Broken Social Scene</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
       </c>
       <c r="L180" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Only The Good I Keep - Broken Social Scene</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Switch Up</v>
+        <v>Zoom 97</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-12</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Switch Up - Single</v>
+        <v>Philadelphia's been good to me</v>
       </c>
       <c r="G181" t="str">
-        <v>3:35</v>
+        <v>4:54</v>
       </c>
       <c r="H181" t="str">
-        <v>Mike D</v>
+        <v>Kurt Vile</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
       </c>
       <c r="L181" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>Zoom 97 - Kurt Vile</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Surprise</v>
+        <v>Switch Up</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-12</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Doe Or Die III</v>
+        <v>Switch Up - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H182" t="str">
-        <v>AZ</v>
+        <v>Mike D</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
       </c>
       <c r="L182" t="str">
-        <v>Surprise - AZ</v>
+        <v>Switch Up - Mike D</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Better Days</v>
+        <v>Surprise</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-12</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Better Days - Single</v>
+        <v>Doe Or Die III</v>
       </c>
       <c r="G183" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H183" t="str">
-        <v>Naomi Sharon</v>
+        <v>AZ</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/az/35299</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/surprise/1894873352</v>
       </c>
       <c r="L183" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Surprise - AZ</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>Better Days</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-12</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Better Days - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H184" t="str">
-        <v>Debbii Dawson</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/better-days/1895293758</v>
       </c>
       <c r="L184" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>Better Days - Naomi Sharon</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>No Pressure</v>
+        <v>Where Have All The Good Men Gone?</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-12</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>No Pressure - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H185" t="str">
-        <v>JYT</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
       </c>
       <c r="L185" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>What's the Point!</v>
+        <v>No Pressure</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-12</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>No Pressure - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:43</v>
+        <v>3:09</v>
       </c>
       <c r="H186" t="str">
-        <v>Emei</v>
+        <v>JYT</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
       </c>
       <c r="L186" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>No Pressure - JYT</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Pachamama</v>
+        <v>What's the Point!</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-12</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Así Es La Vida</v>
+        <v>Night at the Opera - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:20</v>
+        <v>2:43</v>
       </c>
       <c r="H187" t="str">
-        <v>Codiciado</v>
+        <v>Emei</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/emei/1583968554</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
       </c>
       <c r="L187" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>What's the Point! - Emei</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Multiplied</v>
+        <v>Pachamama</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-12</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Multiplied - Single</v>
+        <v>Así Es La Vida</v>
       </c>
       <c r="G188" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H188" t="str">
-        <v>Luna Li</v>
+        <v>Codiciado</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
       </c>
       <c r="L188" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Pachamama - Codiciado</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Six String</v>
+        <v>Multiplied</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-12</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Six String - Single</v>
+        <v>Multiplied - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H189" t="str">
-        <v>Lila Dupont</v>
+        <v>Luna Li</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
       </c>
       <c r="L189" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Multiplied - Luna Li</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Take Heart</v>
+        <v>Six String</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-12</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Harbour</v>
+        <v>Six String - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>4:07</v>
+        <v>3:11</v>
       </c>
       <c r="H190" t="str">
-        <v>Jon Bryant</v>
+        <v>Lila Dupont</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/six-string/1892171725</v>
       </c>
       <c r="L190" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Six String - Lila Dupont</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Clarion</v>
+        <v>Take Heart</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-12</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>You Are Spring!</v>
+        <v>Harbour</v>
       </c>
       <c r="G191" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H191" t="str">
-        <v>Tasha</v>
+        <v>Jon Bryant</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
       </c>
       <c r="L191" t="str">
-        <v>Clarion - Tasha</v>
+        <v>Take Heart - Jon Bryant</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Stepping Stone</v>
+        <v>Clarion</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-12</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Beams - Single</v>
+        <v>You Are Spring!</v>
       </c>
       <c r="G192" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H192" t="str">
-        <v>DERBY</v>
+        <v>Tasha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/clarion/1887589690</v>
       </c>
       <c r="L192" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>Clarion - Tasha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>confessions part iii</v>
+        <v>Stepping Stone</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-12</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>autogratis</v>
+        <v>Beams - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>2:01</v>
+        <v>2:49</v>
       </c>
       <c r="H193" t="str">
-        <v>Chanpan</v>
+        <v>DERBY</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/derby/1772719795</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
       </c>
       <c r="L193" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Stepping Stone - DERBY</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>cherry garcia</v>
+        <v>confessions part iii</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-12</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>cherry garcia - Single</v>
+        <v>autogratis</v>
       </c>
       <c r="G194" t="str">
-        <v>2:30</v>
+        <v>2:01</v>
       </c>
       <c r="H194" t="str">
-        <v>supermodel*</v>
+        <v>Chanpan</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
       </c>
       <c r="L194" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>confessions part iii - Chanpan</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Disco Cherry</v>
+        <v>cherry garcia</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-12</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>cherry garcia - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:20</v>
+        <v>2:30</v>
       </c>
       <c r="H195" t="str">
-        <v>Purple Disco Machine</v>
+        <v>supermodel*</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
       </c>
       <c r="L195" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>cherry garcia - supermodel*</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Tal Vez</v>
+        <v>Disco Cherry</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-12</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>El Amante</v>
+        <v>Disco Cherry - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H196" t="str">
-        <v>Dariel Amant</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
       </c>
       <c r="L196" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>Disco Cherry - Purple Disco Machine</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>The Voyager</v>
+        <v>Tal Vez</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-12</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Voyager - Single</v>
+        <v>El Amante</v>
       </c>
       <c r="G197" t="str">
-        <v>4:37</v>
+        <v>2:14</v>
       </c>
       <c r="H197" t="str">
-        <v>Chance Peña</v>
+        <v>Dariel Amant</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
       </c>
       <c r="L197" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Tal Vez - Dariel Amant</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-12</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H198" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Chance Peña</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
       </c>
       <c r="L198" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>The Voyager - Chance Peña</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Buy What U Want</v>
+        <v>Pictures of You</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-12</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>Pictures of You</v>
       </c>
       <c r="G199" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H199" t="str">
-        <v>Black Fortune</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
       </c>
       <c r="L199" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Pictures of You - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-12</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Road To Osshland: The Series</v>
       </c>
       <c r="G200" t="str">
-        <v>2:29</v>
+        <v>3:47</v>
       </c>
       <c r="H200" t="str">
-        <v>Lil Naay</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
       </c>
       <c r="L200" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>high school sweetheart</v>
+        <v>MOOD BRAZIL</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-12</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>ashley cooke</v>
+        <v>MOOD BRAZIL - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H201" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lil Naay</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
       </c>
       <c r="L201" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>MOOD BRAZIL - Lil Naay</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>high school sweetheart</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-12</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>ashley cooke</v>
       </c>
       <c r="G202" t="str">
-        <v>2:55</v>
+        <v>3:11</v>
       </c>
       <c r="H202" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
       </c>
       <c r="L202" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>big plans</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-12</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>counting horses</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H203" t="str">
-        <v>Tom Siletto</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
       </c>
       <c r="L203" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Running</v>
+        <v>big plans</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D204" t="str">
         <v>2026-05-12</v>
@@ -8127,68 +8127,106 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Running - Single</v>
+        <v>counting horses</v>
       </c>
       <c r="G204" t="str">
-        <v>2:38</v>
+        <v>3:14</v>
       </c>
       <c r="H204" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
       </c>
       <c r="L204" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>big plans - Tom Siletto</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
+        <v>Running</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/running/6764878724</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>Running - Single</v>
+      </c>
+      <c r="G205" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/running/1895947036</v>
+      </c>
+      <c r="L205" t="str">
+        <v>Running - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>FA-TAL!</v>
       </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
-      <c r="D205" t="str">
-        <v>2026-05-12</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
+      <c r="D206" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
         <v>FA-TAL! - Single</v>
       </c>
-      <c r="G205" t="str">
+      <c r="G206" t="str">
         <v>2:46</v>
       </c>
-      <c r="H205" t="str">
+      <c r="H206" t="str">
         <v>ROBI</v>
       </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
         <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
-      <c r="K205" t="str">
+      <c r="K206" t="str">
         <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
       </c>
-      <c r="L205" t="str">
+      <c r="L206" t="str">
         <v>FA-TAL! - ROBI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>11 days ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G82" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,19 +439,19 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,19 +515,19 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3 days ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,19 +553,19 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,19 +591,19 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 months ago</v>
+        <v>2mo ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,19 +667,19 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,19 +705,19 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,19 +743,19 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>2d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,19 +781,19 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,19 +819,19 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,19 +857,19 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,19 +895,19 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,19 +933,19 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,19 +971,19 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4 days ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,19 +1009,19 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,19 +1047,19 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,19 +1085,19 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,19 +1123,19 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,19 +1161,19 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,19 +1199,19 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,19 +1237,19 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,19 +1275,19 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,19 +1313,19 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,19 +1389,19 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,19 +1427,19 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,19 +1465,19 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,19 +1503,19 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,19 +1541,19 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,19 +1579,19 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,19 +1617,19 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,19 +1655,19 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,19 +1693,19 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,19 +1731,19 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,19 +1769,19 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,19 +1807,19 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,19 +1845,19 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,19 +1921,19 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,19 +1959,19 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,19 +1997,19 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,19 +2073,19 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6 days ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>6 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,19 +2149,19 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,19 +2187,19 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,19 +2225,19 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,19 +2263,19 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,19 +2301,19 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,19 +2339,19 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,19 +2377,19 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,19 +2415,19 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,19 +2453,19 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,19 +2491,19 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11 days ago</v>
+        <v>11d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,19 +2529,19 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,19 +2567,19 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,19 +2605,19 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,19 +2643,19 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,19 +2681,19 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,19 +2719,19 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,19 +2757,19 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,19 +2795,19 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,19 +2833,19 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,19 +2871,19 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,19 +2909,19 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,19 +2947,19 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,19 +2985,19 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,19 +3023,19 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,19 +3061,19 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,19 +3099,19 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,19 +3137,19 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,19 +3175,19 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,19 +3251,19 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,19 +3289,19 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,19 +3327,19 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>11 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,19 +3365,19 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,19 +3403,19 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>12 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,19 +3441,19 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,19 +3479,19 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,19 +3517,19 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,19 +3555,19 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13 days ago</v>
+        <v>13d ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,19 +3593,19 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>13 days ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,19 +3631,19 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,19 +3669,19 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,19 +3707,19 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,19 +3745,19 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,19 +3783,19 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,19 +3821,19 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,19 +3859,19 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,19 +3897,19 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,19 +3935,19 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,19 +3973,19 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,19 +4011,19 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,19 +4049,19 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,19 +4087,19 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,19 +4125,19 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,19 +4163,19 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,19 +4201,19 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2 weeks ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E206" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L206"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>5d ago</v>
+        <v>6d ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>3d ago</v>
+        <v>4d ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>3d ago</v>
+        <v>4d ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2d ago</v>
+        <v>3d ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2d ago</v>
+        <v>3d ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>4d ago</v>
+        <v>5d ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>6d ago</v>
+        <v>7d ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7d ago</v>
+        <v>8d ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>11d ago</v>
+        <v>12d ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>13d ago</v>
+        <v>2w ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-13</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G102" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H102" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L102" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="103">
@@ -4540,13 +4540,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Therapy at the Club</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-13</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>THERAPY AT THE CLUB</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G110" t="str">
-        <v>2:47</v>
+        <v>2:27</v>
       </c>
       <c r="H110" t="str">
-        <v>FLO</v>
+        <v>MICO</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/flo/1615611716</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L110" t="str">
-        <v>Therapy at the Club - FLO</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>linknb</v>
+        <v>Therapy at the Club</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D111" t="str">
         <v>2026-05-13</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>new avatar</v>
+        <v>THERAPY AT THE CLUB</v>
       </c>
       <c r="G111" t="str">
-        <v>1:55</v>
+        <v>2:47</v>
       </c>
       <c r="H111" t="str">
-        <v>Kelela</v>
+        <v>FLO</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/flo/1615611716</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/therapy-at-the-club/1895613904</v>
       </c>
       <c r="L111" t="str">
-        <v>linknb - Kelela</v>
+        <v>Therapy at the Club - FLO</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-13</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G112" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H112" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L112" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Baby</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-13</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Baby - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H113" t="str">
-        <v>Prospa</v>
+        <v>elkan</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L113" t="str">
-        <v>Baby - Prospa</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Baby</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-13</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>Baby - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:39</v>
+        <v>3:13</v>
       </c>
       <c r="H114" t="str">
-        <v>Russell Dickerson</v>
+        <v>Prospa</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/baby/1895418297</v>
       </c>
       <c r="L114" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Baby - Prospa</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Bed of Roses</v>
+        <v>Boots (feat. Fetty Wap)</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-13</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Boots (feat. Fetty Wap) - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H115" t="str">
-        <v>Teyana Taylor</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
       </c>
       <c r="L115" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Bed of Roses</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-13</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>Bed of Roses - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H116" t="str">
-        <v>Bruno Mars</v>
+        <v>Teyana Taylor</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
       </c>
       <c r="L116" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Bed of Roses - Teyana Taylor</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Big Dog</v>
+        <v>Lo Arriesgo Todo</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-13</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Big Dog - Single</v>
+        <v>Lo Arriesgo Todo - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H117" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
       </c>
       <c r="L117" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Lo Arriesgo Todo - Bruno Mars</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Eastside Girls</v>
+        <v>Big Dog</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-13</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Big Dog - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H118" t="str">
-        <v>MUNA</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
       </c>
       <c r="L118" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>Big Dog - The Last Dinner Party</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>In The Stars</v>
+        <v>Eastside Girls</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-13</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Foreign Tongues</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G119" t="str">
-        <v>4:13</v>
+        <v>3:50</v>
       </c>
       <c r="H119" t="str">
-        <v>The Rolling Stones</v>
+        <v>MUNA</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
       </c>
       <c r="L119" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Eastside Girls - MUNA</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Home to Us</v>
+        <v>In The Stars</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-13</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Foreign Tongues</v>
       </c>
       <c r="G120" t="str">
-        <v>3:11</v>
+        <v>4:13</v>
       </c>
       <c r="H120" t="str">
-        <v>Paul McCartney</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
       </c>
       <c r="L120" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>In The Stars - The Rolling Stones</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Hurts Like You</v>
+        <v>Home to Us</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-13</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>The Night Champion</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G121" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H121" t="str">
-        <v>Koe Wetzel</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
       </c>
       <c r="L121" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Home to Us - Paul McCartney</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Find Us Again</v>
+        <v>Hurts Like You</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-13</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Find Us Again - Single</v>
+        <v>The Night Champion</v>
       </c>
       <c r="G122" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H122" t="str">
-        <v>Xavi</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
       </c>
       <c r="L122" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hurts Like You - Koe Wetzel</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tied Up</v>
+        <v>Find Us Again</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-13</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tied Up - Single</v>
+        <v>Find Us Again - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H123" t="str">
-        <v>Khalid</v>
+        <v>Xavi</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
       </c>
       <c r="L123" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Find Us Again - Xavi</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Antes De Ti</v>
+        <v>Tied Up</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-13</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Tied Up - Single</v>
       </c>
       <c r="G124" t="str">
         <v>2:56</v>
       </c>
       <c r="H124" t="str">
-        <v>Silvana Estrada</v>
+        <v>Khalid</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/khalid/82842423</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
       </c>
       <c r="L124" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Tied Up - Khalid</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>En La Misma Cama</v>
+        <v>Antes De Ti</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-13</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>MUDA</v>
+        <v>Antes De Ti - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H125" t="str">
-        <v>Carín León</v>
+        <v>Silvana Estrada</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
       </c>
       <c r="L125" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Antes De Ti - Silvana Estrada</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>lovergirl</v>
+        <v>En La Misma Cama</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-13</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>locket deluxe</v>
+        <v>MUDA</v>
       </c>
       <c r="G126" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H126" t="str">
-        <v>Madison Beer</v>
+        <v>Carín León</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
       </c>
       <c r="L126" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>En La Misma Cama - Carín León</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>PANIKI</v>
+        <v>lovergirl</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-13</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>locket deluxe</v>
       </c>
       <c r="G127" t="str">
-        <v>2:36</v>
+        <v>3:21</v>
       </c>
       <c r="H127" t="str">
-        <v>Chuyin</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
       </c>
       <c r="L127" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>lovergirl - Madison Beer</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>DesOrden</v>
+        <v>PANIKI</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-13</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>DesOrden - Single</v>
+        <v>Los Locos Nunca Mueren</v>
       </c>
       <c r="G128" t="str">
         <v>2:36</v>
       </c>
       <c r="H128" t="str">
-        <v>Alleh</v>
+        <v>Chuyin</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/paniki/1892533803</v>
       </c>
       <c r="L128" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>PANIKI - Chuyin</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>LA Nights</v>
+        <v>DesOrden</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-13</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>The Ville</v>
+        <v>DesOrden - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>2:18</v>
+        <v>2:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Trap Dickey</v>
+        <v>Alleh</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/desorden/1896069663</v>
       </c>
       <c r="L129" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>DesOrden - Alleh</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>The Payoff</v>
+        <v>LA Nights</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-13</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>The Payoff - Single</v>
+        <v>The Ville</v>
       </c>
       <c r="G130" t="str">
-        <v>5:51</v>
+        <v>2:18</v>
       </c>
       <c r="H130" t="str">
-        <v>Father John Misty</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
       </c>
       <c r="L130" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>LA Nights - Trap Dickey</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>The Weak</v>
+        <v>The Payoff</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-13</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Payoff - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:15</v>
+        <v>5:51</v>
       </c>
       <c r="H131" t="str">
-        <v>Iceage</v>
+        <v>Father John Misty</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
       </c>
       <c r="L131" t="str">
-        <v>The Weak - Iceage</v>
+        <v>The Payoff - Father John Misty</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Life Of The Faaji</v>
+        <v>The Weak</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-13</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Fuji Xtra</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G132" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H132" t="str">
-        <v>Adekunle Gold</v>
+        <v>Iceage</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
       </c>
       <c r="L132" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>The Weak - Iceage</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Satisfy</v>
+        <v>Life Of The Faaji</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-13</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Satisfy - Single</v>
+        <v>Fuji Xtra</v>
       </c>
       <c r="G133" t="str">
-        <v>3:06</v>
+        <v>2:29</v>
       </c>
       <c r="H133" t="str">
-        <v>Calvin Harris</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
       </c>
       <c r="L133" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>Life Of The Faaji - Adekunle Gold</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>Satisfy</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-13</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>Satisfy - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H134" t="str">
-        <v>DEAN</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
       </c>
       <c r="L134" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>Satisfy - Calvin Harris</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-13</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:48</v>
+        <v>3:03</v>
       </c>
       <c r="H135" t="str">
-        <v>6LACK</v>
+        <v>DEAN</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/dean/2770824</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
       </c>
       <c r="L135" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>I Wanna Rock</v>
+        <v>Ashin' the Blunt</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-13</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G136" t="str">
-        <v>3:44</v>
+        <v>3:48</v>
       </c>
       <c r="H136" t="str">
-        <v>Cash Cobain</v>
+        <v>6LACK</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
       </c>
       <c r="L136" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Ashin' the Blunt - 6LACK</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-13</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>4:33</v>
+        <v>3:44</v>
       </c>
       <c r="H137" t="str">
-        <v>James Blake</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L137" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>One Two Police</v>
+        <v>Trying Times - A COLORS SHOW</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-13</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>One Two Police - Single</v>
+        <v>Trying Times - A COLORS SHOW - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>2:46</v>
+        <v>4:33</v>
       </c>
       <c r="H138" t="str">
-        <v>BUNT.</v>
+        <v>James Blake</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
       </c>
       <c r="L138" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>Trying Times - A COLORS SHOW - James Blake</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>One Two Police</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-13</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>One Two Police - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>3:16</v>
+        <v>2:46</v>
       </c>
       <c r="H139" t="str">
-        <v>Stephen Sanchez</v>
+        <v>BUNT.</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
       </c>
       <c r="L139" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>One Two Police - BUNT.</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Illuminate</v>
+        <v>HOME TO MOTHER</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-13</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G140" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H140" t="str">
-        <v>Jessie Reyez</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
       </c>
       <c r="L140" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>HOME TO MOTHER - Stephen Sanchez</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>OKAY!</v>
+        <v>Illuminate</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-13</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>OKAY! - Single</v>
+        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>4:34</v>
+        <v>3:03</v>
       </c>
       <c r="H141" t="str">
-        <v>Forrest Frank</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
       </c>
       <c r="L141" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>Illuminate - Jessie Reyez</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>FLOW</v>
+        <v>OKAY!</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-13</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>FLOW - Single</v>
+        <v>OKAY! - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:20</v>
+        <v>4:34</v>
       </c>
       <c r="H142" t="str">
-        <v>iZaak</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/okay/1896077066</v>
       </c>
       <c r="L142" t="str">
-        <v>FLOW - iZaak</v>
+        <v>OKAY! - Forrest Frank</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>aiaiaiaiai</v>
+        <v>FLOW</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-13</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>FLOW - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:20</v>
+        <v>4:20</v>
       </c>
       <c r="H143" t="str">
-        <v>Mau y Ricky</v>
+        <v>iZaak</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/flow/1895961693</v>
       </c>
       <c r="L143" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>FLOW - iZaak</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Control</v>
+        <v>aiaiaiaiai</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-13</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>God Must Really Love Me</v>
+        <v>aiaiaiaiai - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:32</v>
+        <v>2:20</v>
       </c>
       <c r="H144" t="str">
-        <v>Tori Kelly</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
       </c>
       <c r="L144" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>aiaiaiaiai - Mau y Ricky</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ORIGAMI!</v>
+        <v>Control</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-13</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>God Must Really Love Me</v>
       </c>
       <c r="G145" t="str">
-        <v>2:34</v>
+        <v>2:32</v>
       </c>
       <c r="H145" t="str">
-        <v>Kesha</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/control/1895974889</v>
       </c>
       <c r="L145" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Control - Tori Kelly</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Love Is Kind</v>
+        <v>ORIGAMI!</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-13</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>ORIGAMI! - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:07</v>
+        <v>2:34</v>
       </c>
       <c r="H146" t="str">
-        <v>The Chainsmokers</v>
+        <v>Kesha</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/kesha/334854763</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/origami/1892544026</v>
       </c>
       <c r="L146" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>ORIGAMI! - Kesha</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Love Is Kind</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-13</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Let It Die Here</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G147" t="str">
-        <v>4:00</v>
+        <v>4:07</v>
       </c>
       <c r="H147" t="str">
-        <v>Linda Perry</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
       </c>
       <c r="L147" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Love Is Kind - The Chainsmokers</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Playing God</v>
+        <v>Feathers In A Storm</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-13</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Decades</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G148" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H148" t="str">
-        <v>Motionless In White</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
       </c>
       <c r="L148" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Feathers In A Storm - Linda Perry</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Cut</v>
+        <v>Playing God</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-13</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>VINDICATE</v>
+        <v>Decades</v>
       </c>
       <c r="G149" t="str">
-        <v>3:59</v>
+        <v>3:39</v>
       </c>
       <c r="H149" t="str">
-        <v>Black Veil Brides</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
       </c>
       <c r="L149" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Playing God - Motionless In White</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Freaking Out</v>
+        <v>Cut</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-13</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Over Before You Know It</v>
+        <v>VINDICATE</v>
       </c>
       <c r="G150" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H150" t="str">
-        <v>Michigander</v>
+        <v>Black Veil Brides</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/cut/1879494510</v>
       </c>
       <c r="L150" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Cut - Black Veil Brides</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FIYAH</v>
+        <v>Freaking Out</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-13</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>FIYAH - Single</v>
+        <v>Over Before You Know It</v>
       </c>
       <c r="G151" t="str">
-        <v>3:12</v>
+        <v>3:03</v>
       </c>
       <c r="H151" t="str">
-        <v>YG Marley</v>
+        <v>Michigander</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
       </c>
       <c r="L151" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Freaking Out - Michigander</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Ten to Midnight</v>
+        <v>FIYAH</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-13</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Wild</v>
+        <v>FIYAH - Single</v>
       </c>
       <c r="G152" t="str">
         <v>3:12</v>
       </c>
       <c r="H152" t="str">
-        <v>Ashley McBryde</v>
+        <v>YG Marley</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
       </c>
       <c r="L152" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>FIYAH - YG Marley</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Carry On</v>
+        <v>Ten to Midnight</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-13</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Carry On - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G153" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H153" t="str">
-        <v>Kenny Chesney</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
       </c>
       <c r="L153" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>Ten to Midnight - Ashley McBryde</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>[PRESS]</v>
+        <v>Carry On</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-13</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Carry On - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>1:40</v>
+        <v>3:00</v>
       </c>
       <c r="H154" t="str">
-        <v>Armani White</v>
+        <v>Kenny Chesney</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
       </c>
       <c r="L154" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Carry On - Kenny Chesney</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>[PRESS]</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-13</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>[PRESS] - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:17</v>
+        <v>1:40</v>
       </c>
       <c r="H155" t="str">
-        <v>Myles Smith</v>
+        <v>Armani White</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/press/1895898254</v>
       </c>
       <c r="L155" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>[PRESS] - Armani White</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Hold Me In The Dark</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-13</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G156" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H156" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
       </c>
       <c r="L156" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Hold Me In The Dark - Myles Smith</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-13</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H157" t="str">
-        <v>Mack Keane</v>
+        <v>Sebastián Yatra</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
       </c>
       <c r="L157" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Changes</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-13</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Changes - Single</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="G158" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H158" t="str">
-        <v>Tommy Richman</v>
+        <v>Mack Keane</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
       </c>
       <c r="L158" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Wide Eyed - Mack Keane</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Changes</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-13</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Changes - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>4:33</v>
+        <v>3:18</v>
       </c>
       <c r="H159" t="str">
-        <v>The War And Treaty</v>
+        <v>Tommy Richman</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/changes/1895418156</v>
       </c>
       <c r="L159" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Changes - Tommy Richman</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>depressed on the internet</v>
+        <v>Don't Say Goodbye</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-13</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>The Story of Michael and Tanya</v>
       </c>
       <c r="G160" t="str">
-        <v>2:57</v>
+        <v>4:33</v>
       </c>
       <c r="H160" t="str">
-        <v>Bea Miller</v>
+        <v>The War And Treaty</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
       </c>
       <c r="L160" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Don't Say Goodbye - The War And Treaty</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Dear Burt</v>
+        <v>depressed on the internet</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-13</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>depressed on the internet - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:53</v>
+        <v>2:57</v>
       </c>
       <c r="H161" t="str">
-        <v>Stephan Moccio</v>
+        <v>Bea Miller</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
       </c>
       <c r="L161" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>depressed on the internet - Bea Miller</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Alla Blues</v>
+        <v>Dear Burt</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-13</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Black Mozart</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G162" t="str">
-        <v>2:50</v>
+        <v>2:53</v>
       </c>
       <c r="H162" t="str">
-        <v>Jon Batiste</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
       </c>
       <c r="L162" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>Dear Burt - Stephan Moccio</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Think About Me</v>
+        <v>Alla Blues</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-13</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Think About Me - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G163" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H163" t="str">
-        <v>Gabriella Rose</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
       </c>
       <c r="L163" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>Alla Blues - Jon Batiste</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Meet Again</v>
+        <v>Think About Me</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-13</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Meet Again - Single</v>
+        <v>Think About Me - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:26</v>
+        <v>2:39</v>
       </c>
       <c r="H164" t="str">
-        <v>Kaskade</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
       </c>
       <c r="L164" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Think About Me - Gabriella Rose</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Happy Now</v>
+        <v>Meet Again</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-13</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>The Afterparty</v>
+        <v>Meet Again - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H165" t="str">
-        <v>Lykke Li</v>
+        <v>Kaskade</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
       </c>
       <c r="L165" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Meet Again - Kaskade</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Oblivion</v>
+        <v>Happy Now</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-13</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Oblivion - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G166" t="str">
-        <v>2:21</v>
+        <v>2:42</v>
       </c>
       <c r="H166" t="str">
-        <v>Agents Of Time</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
       </c>
       <c r="L166" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>Happy Now - Lykke Li</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Oblivion</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-13</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>Oblivion - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>4:03</v>
+        <v>2:21</v>
       </c>
       <c r="H167" t="str">
-        <v>Papa Roach</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
       </c>
       <c r="L167" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Oblivion - Agents Of Time</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Top of the Hill</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-13</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>1:50</v>
+        <v>4:03</v>
       </c>
       <c r="H168" t="str">
-        <v>DDG</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
       </c>
       <c r="L168" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Oh Savannah</v>
+        <v>Top of the Hill</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-13</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Change Of Plans</v>
+        <v>Top of the Hill - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>3:05</v>
+        <v>1:50</v>
       </c>
       <c r="H169" t="str">
-        <v>49 Winchester</v>
+        <v>DDG</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/ddg/3954994</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
       </c>
       <c r="L169" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Top of the Hill - DDG</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Oh Savannah</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-13</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G170" t="str">
-        <v>2:29</v>
+        <v>3:05</v>
       </c>
       <c r="H170" t="str">
-        <v>Little Simz</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
       </c>
       <c r="L170" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Oh Savannah - 49 Winchester</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>How to Forget</v>
+        <v>Game On (feat. JT)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-13</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>ARCADE</v>
+        <v>Sugar Girl - EP</v>
       </c>
       <c r="G171" t="str">
-        <v>4:01</v>
+        <v>2:29</v>
       </c>
       <c r="H171" t="str">
-        <v>Deb Never</v>
+        <v>Little Simz</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
       </c>
       <c r="L171" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Game On (feat. JT) - Little Simz</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>How to Forget</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-13</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G172" t="str">
-        <v>2:49</v>
+        <v>4:01</v>
       </c>
       <c r="H172" t="str">
-        <v>ear</v>
+        <v>Deb Never</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
       </c>
       <c r="L172" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>How to Forget - Deb Never</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Mirror</v>
+        <v>Ne Plus Ultra</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-13</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Mirror - Single</v>
+        <v>Ne Plus Ultra - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H173" t="str">
-        <v>MOD SUN</v>
+        <v>ear</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
       </c>
       <c r="L173" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>Ne Plus Ultra - ear</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Miel Con Licor</v>
+        <v>Mirror</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-13</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Bandera Blanca</v>
+        <v>Mirror - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H174" t="str">
-        <v>Christian Nodal</v>
+        <v>MOD SUN</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/mirror/1895402181</v>
       </c>
       <c r="L174" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Mirror - MOD SUN</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Miel Con Licor</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-13</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G175" t="str">
-        <v>3:31</v>
+        <v>3:27</v>
       </c>
       <c r="H175" t="str">
-        <v>aron!</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
       </c>
       <c r="L175" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Miel Con Licor - Christian Nodal</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
+        <v>Macramé (feat. Mei Semones)</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
+        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-13</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>The Last Balloon</v>
+        <v>Macramé (feat. Mei Semones) - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H176" t="str">
-        <v>Tank and the Bangas</v>
+        <v>aron!</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
+        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
       </c>
       <c r="L176" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
+        <v>Macramé (feat. Mei Semones) - aron!</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-13</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G177" t="str">
-        <v>5:14</v>
+        <v>3:14</v>
       </c>
       <c r="H177" t="str">
-        <v>Darkthrone</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
       </c>
       <c r="L177" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Cloudfall</v>
+        <v>They Found One Of My Graves</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-13</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Pre-Historic Metal</v>
       </c>
       <c r="G178" t="str">
-        <v>4:06</v>
+        <v>5:14</v>
       </c>
       <c r="H178" t="str">
-        <v>REZN</v>
+        <v>Darkthrone</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
       </c>
       <c r="L178" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>They Found One Of My Graves - Darkthrone</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Doom in Bloom</v>
+        <v>Cloudfall</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-13</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Hum of Hurt</v>
+        <v>Cycles in the Infinite Dream</v>
       </c>
       <c r="G179" t="str">
-        <v>3:17</v>
+        <v>4:06</v>
       </c>
       <c r="H179" t="str">
-        <v>Converge</v>
+        <v>REZN</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
       </c>
       <c r="L179" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Cloudfall - REZN</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Doom in Bloom</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-13</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Remember The Humans</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G180" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H180" t="str">
-        <v>Broken Social Scene</v>
+        <v>Converge</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
       </c>
       <c r="L180" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Doom in Bloom - Converge</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Zoom 97</v>
+        <v>Only The Good I Keep</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-13</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Remember The Humans</v>
       </c>
       <c r="G181" t="str">
-        <v>4:54</v>
+        <v>3:27</v>
       </c>
       <c r="H181" t="str">
-        <v>Kurt Vile</v>
+        <v>Broken Social Scene</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
       </c>
       <c r="L181" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Only The Good I Keep - Broken Social Scene</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Switch Up</v>
+        <v>Zoom 97</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-13</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Switch Up - Single</v>
+        <v>Philadelphia's been good to me</v>
       </c>
       <c r="G182" t="str">
-        <v>3:35</v>
+        <v>4:54</v>
       </c>
       <c r="H182" t="str">
-        <v>Mike D</v>
+        <v>Kurt Vile</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
       </c>
       <c r="L182" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>Zoom 97 - Kurt Vile</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Surprise</v>
+        <v>Switch Up</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-13</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Doe Or Die III</v>
+        <v>Switch Up - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H183" t="str">
-        <v>AZ</v>
+        <v>Mike D</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
       </c>
       <c r="L183" t="str">
-        <v>Surprise - AZ</v>
+        <v>Switch Up - Mike D</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Better Days</v>
+        <v>Surprise</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-13</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Better Days - Single</v>
+        <v>Doe Or Die III</v>
       </c>
       <c r="G184" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Naomi Sharon</v>
+        <v>AZ</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/az/35299</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/surprise/1894873352</v>
       </c>
       <c r="L184" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Surprise - AZ</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>Better Days</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-13</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Better Days - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H185" t="str">
-        <v>Debbii Dawson</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/better-days/1895293758</v>
       </c>
       <c r="L185" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>Better Days - Naomi Sharon</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>No Pressure</v>
+        <v>Where Have All The Good Men Gone?</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-13</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>No Pressure - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G186" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H186" t="str">
-        <v>JYT</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
       </c>
       <c r="L186" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>What's the Point!</v>
+        <v>No Pressure</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-13</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>No Pressure - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:43</v>
+        <v>3:09</v>
       </c>
       <c r="H187" t="str">
-        <v>Emei</v>
+        <v>JYT</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
       </c>
       <c r="L187" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>No Pressure - JYT</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Pachamama</v>
+        <v>What's the Point!</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-13</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Así Es La Vida</v>
+        <v>Night at the Opera - EP</v>
       </c>
       <c r="G188" t="str">
-        <v>3:20</v>
+        <v>2:43</v>
       </c>
       <c r="H188" t="str">
-        <v>Codiciado</v>
+        <v>Emei</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/emei/1583968554</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
       </c>
       <c r="L188" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>What's the Point! - Emei</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Multiplied</v>
+        <v>Pachamama</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-13</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Multiplied - Single</v>
+        <v>Así Es La Vida</v>
       </c>
       <c r="G189" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H189" t="str">
-        <v>Luna Li</v>
+        <v>Codiciado</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
       </c>
       <c r="L189" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Pachamama - Codiciado</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Six String</v>
+        <v>Multiplied</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-13</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Six String - Single</v>
+        <v>Multiplied - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H190" t="str">
-        <v>Lila Dupont</v>
+        <v>Luna Li</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
       </c>
       <c r="L190" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Multiplied - Luna Li</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Take Heart</v>
+        <v>Six String</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-13</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Harbour</v>
+        <v>Six String - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>4:07</v>
+        <v>3:11</v>
       </c>
       <c r="H191" t="str">
-        <v>Jon Bryant</v>
+        <v>Lila Dupont</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/six-string/1892171725</v>
       </c>
       <c r="L191" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Six String - Lila Dupont</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Clarion</v>
+        <v>Take Heart</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-13</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>You Are Spring!</v>
+        <v>Harbour</v>
       </c>
       <c r="G192" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H192" t="str">
-        <v>Tasha</v>
+        <v>Jon Bryant</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
       </c>
       <c r="L192" t="str">
-        <v>Clarion - Tasha</v>
+        <v>Take Heart - Jon Bryant</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Stepping Stone</v>
+        <v>Clarion</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-13</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Beams - Single</v>
+        <v>You Are Spring!</v>
       </c>
       <c r="G193" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H193" t="str">
-        <v>DERBY</v>
+        <v>Tasha</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/clarion/1887589690</v>
       </c>
       <c r="L193" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>Clarion - Tasha</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>confessions part iii</v>
+        <v>Stepping Stone</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-13</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>autogratis</v>
+        <v>Beams - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>2:01</v>
+        <v>2:49</v>
       </c>
       <c r="H194" t="str">
-        <v>Chanpan</v>
+        <v>DERBY</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/derby/1772719795</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
       </c>
       <c r="L194" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Stepping Stone - DERBY</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>cherry garcia</v>
+        <v>confessions part iii</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-13</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>cherry garcia - Single</v>
+        <v>autogratis</v>
       </c>
       <c r="G195" t="str">
-        <v>2:30</v>
+        <v>2:01</v>
       </c>
       <c r="H195" t="str">
-        <v>supermodel*</v>
+        <v>Chanpan</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
       </c>
       <c r="L195" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>confessions part iii - Chanpan</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Disco Cherry</v>
+        <v>cherry garcia</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-13</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>cherry garcia - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>3:20</v>
+        <v>2:30</v>
       </c>
       <c r="H196" t="str">
-        <v>Purple Disco Machine</v>
+        <v>supermodel*</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
       </c>
       <c r="L196" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>cherry garcia - supermodel*</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Tal Vez</v>
+        <v>Disco Cherry</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-13</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>El Amante</v>
+        <v>Disco Cherry - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H197" t="str">
-        <v>Dariel Amant</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
       </c>
       <c r="L197" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>Disco Cherry - Purple Disco Machine</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>The Voyager</v>
+        <v>Tal Vez</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-13</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>The Voyager - Single</v>
+        <v>El Amante</v>
       </c>
       <c r="G198" t="str">
-        <v>4:37</v>
+        <v>2:14</v>
       </c>
       <c r="H198" t="str">
-        <v>Chance Peña</v>
+        <v>Dariel Amant</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
       </c>
       <c r="L198" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Tal Vez - Dariel Amant</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-13</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager - Single</v>
       </c>
       <c r="G199" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H199" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Chance Peña</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
       </c>
       <c r="L199" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>The Voyager - Chance Peña</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Buy What U Want</v>
+        <v>Pictures of You</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-13</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>Pictures of You</v>
       </c>
       <c r="G200" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H200" t="str">
-        <v>Black Fortune</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
       </c>
       <c r="L200" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Pictures of You - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-13</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Road To Osshland: The Series</v>
       </c>
       <c r="G201" t="str">
-        <v>2:29</v>
+        <v>3:47</v>
       </c>
       <c r="H201" t="str">
-        <v>Lil Naay</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
       </c>
       <c r="L201" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>high school sweetheart</v>
+        <v>MOOD BRAZIL</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-13</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>ashley cooke</v>
+        <v>MOOD BRAZIL - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H202" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lil Naay</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
       </c>
       <c r="L202" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>MOOD BRAZIL - Lil Naay</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>high school sweetheart</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-13</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>ashley cooke</v>
       </c>
       <c r="G203" t="str">
-        <v>2:55</v>
+        <v>3:11</v>
       </c>
       <c r="H203" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
       </c>
       <c r="L203" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>big plans</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D204" t="str">
         <v>2026-05-13</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>counting horses</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
       </c>
       <c r="G204" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H204" t="str">
-        <v>Tom Siletto</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
       </c>
       <c r="L204" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Running</v>
+        <v>big plans</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D205" t="str">
         <v>2026-05-13</v>
@@ -8165,68 +8165,106 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>Running - Single</v>
+        <v>counting horses</v>
       </c>
       <c r="G205" t="str">
-        <v>2:38</v>
+        <v>3:14</v>
       </c>
       <c r="H205" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
       </c>
       <c r="L205" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>big plans - Tom Siletto</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
+        <v>Running</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/running/6764878724</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Running - Single</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/running/1895947036</v>
+      </c>
+      <c r="L206" t="str">
+        <v>Running - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
         <v>FA-TAL!</v>
       </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
-      <c r="D206" t="str">
-        <v>2026-05-13</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
+      <c r="D207" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
         <v>FA-TAL! - Single</v>
       </c>
-      <c r="G206" t="str">
+      <c r="G207" t="str">
         <v>2:46</v>
       </c>
-      <c r="H206" t="str">
+      <c r="H207" t="str">
         <v>ROBI</v>
       </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
         <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
-      <c r="K206" t="str">
+      <c r="K207" t="str">
         <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
       </c>
-      <c r="L206" t="str">
+      <c r="L207" t="str">
         <v>FA-TAL! - ROBI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6d ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4d ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -553,7 +553,7 @@
         <v>Sal Da Vinci - Per Sempre Sì | Italy 🇮🇹 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B5" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C5" t="str">
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -591,7 +591,7 @@
         <v>Alis - Nân | Albania 🇦🇱 | Official Music Video | #Eurovision2026</v>
       </c>
       <c r="B6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C6" t="str">
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
@@ -603,7 +603,7 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -629,7 +629,7 @@
         <v>Monroe - Regarde ! | France 🇫🇷 | Official Music Video #Eurovision2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="C7" t="str">
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
@@ -641,7 +641,7 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2mo ago</v>
+        <v>2 months ago</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>4d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3d ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1009,7 +1009,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1085,7 +1085,7 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5d ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2111,7 +2111,7 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
@@ -2123,7 +2123,7 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7d ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8d ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12d ago</v>
+        <v>12 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13d ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3479,7 +3479,7 @@
         <v>Maya Hawke - Lioness (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C82" t="str">
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
@@ -3491,7 +3491,7 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>13d ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3517,7 +3517,7 @@
         <v>Laufey - "Blue In Green (Amazon Music Original)" – Live Performance</v>
       </c>
       <c r="B83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C83" t="str">
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3555,7 +3555,7 @@
         <v>Keith Urban - Summer Breeze (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C84" t="str">
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
@@ -3567,7 +3567,7 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3593,7 +3593,7 @@
         <v>DANNA - AGAIN</v>
       </c>
       <c r="B85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
@@ -3605,7 +3605,7 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3631,7 +3631,7 @@
         <v>Armik - Libre (2026 Remaster/Remix) (Romantic Spanish Guitar)</v>
       </c>
       <c r="B86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C86" t="str">
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
@@ -3643,7 +3643,7 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3669,7 +3669,7 @@
         <v>EUROPE - One on One (Official Video)</v>
       </c>
       <c r="B87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C87" t="str">
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
@@ -3681,7 +3681,7 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3707,7 +3707,7 @@
         <v>Foo Fighters - Caught In The Echo (SNL UK)</v>
       </c>
       <c r="B88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C88" t="str">
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
@@ -3719,7 +3719,7 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3745,7 +3745,7 @@
         <v>Lady Gaga, Doechii - RUNWAY (Official Music Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C89" t="str">
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
@@ -3757,7 +3757,7 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3783,7 +3783,7 @@
         <v>MUSE - Cryogen (Live from O2 Academy Brixton)</v>
       </c>
       <c r="B90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C90" t="str">
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
@@ -3795,7 +3795,7 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3821,7 +3821,7 @@
         <v>Nothing But Thieves - Do You Love Me Yet? (Official Audio)</v>
       </c>
       <c r="B91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C91" t="str">
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
@@ -3833,7 +3833,7 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3859,7 +3859,7 @@
         <v>Shaboozey - Born To Die (Official Video)</v>
       </c>
       <c r="B92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C92" t="str">
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
@@ -3871,7 +3871,7 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3897,7 +3897,7 @@
         <v>Scorpions - Peacemaker (Madison Square Garden 2022)</v>
       </c>
       <c r="B93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C93" t="str">
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
@@ -3909,7 +3909,7 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3935,7 +3935,7 @@
         <v>Meghan Trainor - Shimmer (Official Music Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C94" t="str">
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
@@ -3947,7 +3947,7 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3973,7 +3973,7 @@
         <v>Lolo Zouaï - Baggy Jeans (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C95" t="str">
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
@@ -3985,7 +3985,7 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4011,7 +4011,7 @@
         <v>Bonnie Tyler - One World One Home</v>
       </c>
       <c r="B96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C96" t="str">
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
@@ -4023,7 +4023,7 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4049,7 +4049,7 @@
         <v>Jacob Gurevitsch | Dream Catcher | Official Music Video</v>
       </c>
       <c r="B97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C97" t="str">
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
@@ -4061,7 +4061,7 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4087,7 +4087,7 @@
         <v>Icona Pop - Dance To This (Official Video)</v>
       </c>
       <c r="B98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C98" t="str">
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
@@ -4099,7 +4099,7 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4125,7 +4125,7 @@
         <v>Michael Jackson - Human Nature (Official Video)</v>
       </c>
       <c r="B99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C99" t="str">
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
@@ -4137,7 +4137,7 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4163,7 +4163,7 @@
         <v>The All-American Rejects - King Kong</v>
       </c>
       <c r="B100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C100" t="str">
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
@@ -4175,7 +4175,7 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4201,7 +4201,7 @@
         <v>Ringo Starr - Long Long Road (Official Music Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C101" t="str">
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
@@ -4213,7 +4213,7 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>2w ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3441,7 +3441,7 @@
         <v>Natasha Bedingfield Performs “Unwritten” Live | GRAMMY U Conference w/ Towa Bird &amp; Abigail Morris</v>
       </c>
       <c r="B81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C81" t="str">
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G81" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://www.youtube.com/watch?v=V406FAGkhyQ</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://www.youtube.com/watch?v=b9AdRrA554o</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://www.youtube.com/watch?v=ujoCYrvvTYQ</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2111,19 +2111,19 @@
         <v>DANNA - OUT OF MY BODY</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
         <v>https://www.youtube.com/watch?v=uW_Ye0kQ9Ac</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://www.youtube.com/watch?v=JXW3SOr7C4w</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://www.youtube.com/watch?v=34wY8CV6hGk</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://www.youtube.com/watch?v=GvhlIFJaqS4</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://www.youtube.com/watch?v=ec8GlqMOyVY</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://www.youtube.com/watch?v=mL1hEJM2WSY</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://www.youtube.com/watch?v=uLGyJNEkZOk</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://www.youtube.com/watch?v=0PVLyBYNFj4</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://www.youtube.com/watch?v=ZNETvyzGf1I</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://www.youtube.com/watch?v=XXIX2WnfbpE</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://www.youtube.com/watch?v=yjrB6o9D0CY</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://www.youtube.com/watch?v=cBjLLcawVWQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://www.youtube.com/watch?v=QA2vzqQ_CG8</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://www.youtube.com/watch?v=FbugtcypkLY</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://www.youtube.com/watch?v=VBqUGKcAfNA</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://www.youtube.com/watch?v=HtK461D1WPQ</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://www.youtube.com/watch?v=A8LMt3T9WgE</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://www.youtube.com/watch?v=P9cdxZr_45w</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://www.youtube.com/watch?v=mIkvkDJdXzQ</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://www.youtube.com/watch?v=YNzuiRuQNYY</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://www.youtube.com/watch?v=ocG1R2FI3LY</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://www.youtube.com/watch?v=33Ql4L4G0Jw</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/hardy-feat-clairo/1876953073</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -4321,7 +4321,7 @@
         <v>https://music.apple.com/us/song/una-a-la-vez/1890287855</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -4359,7 +4359,7 @@
         <v>https://music.apple.com/us/song/rock-music/6766314234</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -4397,7 +4397,7 @@
         <v>https://music.apple.com/us/song/tnt/1887671066</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -4435,7 +4435,7 @@
         <v>https://music.apple.com/us/song/go/6765588421</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -4473,7 +4473,7 @@
         <v>https://music.apple.com/us/song/for-the-moment/6764419271</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -4511,7 +4511,7 @@
         <v>https://music.apple.com/us/song/smoking-pt-2/1894333434</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -4549,7 +4549,7 @@
         <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -4587,7 +4587,7 @@
         <v>https://music.apple.com/us/song/therapy-at-the-club/6764050150</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -4625,7 +4625,7 @@
         <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E112" t="str">
         <v/>
@@ -4663,7 +4663,7 @@
         <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -4701,7 +4701,7 @@
         <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -4739,7 +4739,7 @@
         <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E115" t="str">
         <v/>
@@ -4777,7 +4777,7 @@
         <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -4815,7 +4815,7 @@
         <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -4853,7 +4853,7 @@
         <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E118" t="str">
         <v/>
@@ -4891,7 +4891,7 @@
         <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E119" t="str">
         <v/>
@@ -4929,7 +4929,7 @@
         <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E120" t="str">
         <v/>
@@ -4967,7 +4967,7 @@
         <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E121" t="str">
         <v/>
@@ -5005,7 +5005,7 @@
         <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E122" t="str">
         <v/>
@@ -5043,7 +5043,7 @@
         <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E123" t="str">
         <v/>
@@ -5081,7 +5081,7 @@
         <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E124" t="str">
         <v/>
@@ -5119,7 +5119,7 @@
         <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E125" t="str">
         <v/>
@@ -5157,7 +5157,7 @@
         <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E126" t="str">
         <v/>
@@ -5195,7 +5195,7 @@
         <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E127" t="str">
         <v/>
@@ -5233,7 +5233,7 @@
         <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E128" t="str">
         <v/>
@@ -5271,7 +5271,7 @@
         <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E129" t="str">
         <v/>
@@ -5309,7 +5309,7 @@
         <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E130" t="str">
         <v/>
@@ -5347,7 +5347,7 @@
         <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E131" t="str">
         <v/>
@@ -5385,7 +5385,7 @@
         <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E132" t="str">
         <v/>
@@ -5423,7 +5423,7 @@
         <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E133" t="str">
         <v/>
@@ -5461,7 +5461,7 @@
         <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E134" t="str">
         <v/>
@@ -5499,7 +5499,7 @@
         <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E135" t="str">
         <v/>
@@ -5537,7 +5537,7 @@
         <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E136" t="str">
         <v/>
@@ -5575,7 +5575,7 @@
         <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E137" t="str">
         <v/>
@@ -5613,7 +5613,7 @@
         <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E138" t="str">
         <v/>
@@ -5651,7 +5651,7 @@
         <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E139" t="str">
         <v/>
@@ -5689,7 +5689,7 @@
         <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E140" t="str">
         <v/>
@@ -5727,7 +5727,7 @@
         <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E141" t="str">
         <v/>
@@ -5765,7 +5765,7 @@
         <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E142" t="str">
         <v/>
@@ -5803,7 +5803,7 @@
         <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E143" t="str">
         <v/>
@@ -5841,7 +5841,7 @@
         <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E144" t="str">
         <v/>
@@ -5879,7 +5879,7 @@
         <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E145" t="str">
         <v/>
@@ -5917,7 +5917,7 @@
         <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E146" t="str">
         <v/>
@@ -5955,7 +5955,7 @@
         <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E147" t="str">
         <v/>
@@ -5993,7 +5993,7 @@
         <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E148" t="str">
         <v/>
@@ -6031,7 +6031,7 @@
         <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E149" t="str">
         <v/>
@@ -6069,7 +6069,7 @@
         <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E150" t="str">
         <v/>
@@ -6107,7 +6107,7 @@
         <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E151" t="str">
         <v/>
@@ -6145,7 +6145,7 @@
         <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E152" t="str">
         <v/>
@@ -6183,7 +6183,7 @@
         <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E153" t="str">
         <v/>
@@ -6221,7 +6221,7 @@
         <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E154" t="str">
         <v/>
@@ -6259,7 +6259,7 @@
         <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E155" t="str">
         <v/>
@@ -6297,7 +6297,7 @@
         <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E156" t="str">
         <v/>
@@ -6335,7 +6335,7 @@
         <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E157" t="str">
         <v/>
@@ -6373,7 +6373,7 @@
         <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E158" t="str">
         <v/>
@@ -6411,7 +6411,7 @@
         <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E159" t="str">
         <v/>
@@ -6449,7 +6449,7 @@
         <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E160" t="str">
         <v/>
@@ -6487,7 +6487,7 @@
         <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E161" t="str">
         <v/>
@@ -6525,7 +6525,7 @@
         <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E162" t="str">
         <v/>
@@ -6563,7 +6563,7 @@
         <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E163" t="str">
         <v/>
@@ -6601,7 +6601,7 @@
         <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E164" t="str">
         <v/>
@@ -6639,7 +6639,7 @@
         <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E165" t="str">
         <v/>
@@ -6677,7 +6677,7 @@
         <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E166" t="str">
         <v/>
@@ -6715,7 +6715,7 @@
         <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E167" t="str">
         <v/>
@@ -6753,7 +6753,7 @@
         <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E168" t="str">
         <v/>
@@ -6791,7 +6791,7 @@
         <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E169" t="str">
         <v/>
@@ -6829,7 +6829,7 @@
         <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E170" t="str">
         <v/>
@@ -6867,7 +6867,7 @@
         <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E171" t="str">
         <v/>
@@ -6905,7 +6905,7 @@
         <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E172" t="str">
         <v/>
@@ -6943,7 +6943,7 @@
         <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E173" t="str">
         <v/>
@@ -6981,7 +6981,7 @@
         <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E174" t="str">
         <v/>
@@ -7019,7 +7019,7 @@
         <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E175" t="str">
         <v/>
@@ -7057,7 +7057,7 @@
         <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E176" t="str">
         <v/>
@@ -7095,7 +7095,7 @@
         <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E177" t="str">
         <v/>
@@ -7133,7 +7133,7 @@
         <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E178" t="str">
         <v/>
@@ -7171,7 +7171,7 @@
         <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E179" t="str">
         <v/>
@@ -7209,7 +7209,7 @@
         <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E180" t="str">
         <v/>
@@ -7247,7 +7247,7 @@
         <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E181" t="str">
         <v/>
@@ -7285,7 +7285,7 @@
         <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E182" t="str">
         <v/>
@@ -7323,7 +7323,7 @@
         <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E183" t="str">
         <v/>
@@ -7361,7 +7361,7 @@
         <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E184" t="str">
         <v/>
@@ -7399,7 +7399,7 @@
         <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E185" t="str">
         <v/>
@@ -7437,7 +7437,7 @@
         <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E186" t="str">
         <v/>
@@ -7475,7 +7475,7 @@
         <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E187" t="str">
         <v/>
@@ -7513,7 +7513,7 @@
         <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E188" t="str">
         <v/>
@@ -7551,7 +7551,7 @@
         <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E189" t="str">
         <v/>
@@ -7589,7 +7589,7 @@
         <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E190" t="str">
         <v/>
@@ -7627,7 +7627,7 @@
         <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E191" t="str">
         <v/>
@@ -7665,7 +7665,7 @@
         <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E192" t="str">
         <v/>
@@ -7703,7 +7703,7 @@
         <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E193" t="str">
         <v/>
@@ -7741,7 +7741,7 @@
         <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E194" t="str">
         <v/>
@@ -7779,7 +7779,7 @@
         <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E195" t="str">
         <v/>
@@ -7817,7 +7817,7 @@
         <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E196" t="str">
         <v/>
@@ -7855,7 +7855,7 @@
         <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E197" t="str">
         <v/>
@@ -7893,7 +7893,7 @@
         <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E198" t="str">
         <v/>
@@ -7931,7 +7931,7 @@
         <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E199" t="str">
         <v/>
@@ -7969,7 +7969,7 @@
         <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E200" t="str">
         <v/>
@@ -8007,7 +8007,7 @@
         <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E201" t="str">
         <v/>
@@ -8045,7 +8045,7 @@
         <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E202" t="str">
         <v/>
@@ -8083,7 +8083,7 @@
         <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E203" t="str">
         <v/>
@@ -8121,7 +8121,7 @@
         <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E204" t="str">
         <v/>
@@ -8159,7 +8159,7 @@
         <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E205" t="str">
         <v/>
@@ -8197,7 +8197,7 @@
         <v>https://music.apple.com/us/song/running/6764878724</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E206" t="str">
         <v/>
@@ -8235,7 +8235,7 @@
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
       <c r="D207" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-14</v>
       </c>
       <c r="E207" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1085,7 +1085,7 @@
         <v>Porches- HABIT (Official Video)</v>
       </c>
       <c r="B19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C19" t="str">
         <v>https://www.youtube.com/watch?v=uqU-bbDGjcs</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>Charli xcx - Rock Music (Official Video)</v>
       </c>
       <c r="B20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C20" t="str">
         <v>https://www.youtube.com/watch?v=ox1Eemj8FDo</v>
@@ -1135,7 +1135,7 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1161,7 +1161,7 @@
         <v>Jon Batiste - Alla Blues (Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=lOA2XP--w1c</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1199,7 +1199,7 @@
         <v>Tigirlily Gold - I Do or Die (Official Music Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C22" t="str">
         <v>https://www.youtube.com/watch?v=Z8svQ8FXgYw</v>
@@ -1211,7 +1211,7 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1237,7 +1237,7 @@
         <v>Paul McCartney, Ringo Starr - Home to Us (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C23" t="str">
         <v>https://www.youtube.com/watch?v=bLRV8hRRUHo</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1275,7 +1275,7 @@
         <v>Bruno Mars - Lo Arriesgo Todo [Official Lyric Video]</v>
       </c>
       <c r="B24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C24" t="str">
         <v>https://www.youtube.com/watch?v=bwuUarZDeyA</v>
@@ -1287,7 +1287,7 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1313,7 +1313,7 @@
         <v>Tori Kelly - Control (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C25" t="str">
         <v>https://www.youtube.com/watch?v=TUn5is8toW0</v>
@@ -1325,7 +1325,7 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1351,7 +1351,7 @@
         <v>Bea Miller - depressed on the internet (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C26" t="str">
         <v>https://www.youtube.com/watch?v=K59vT2PV3T0</v>
@@ -1363,7 +1363,7 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1389,7 +1389,7 @@
         <v>The Chainsmokers, Oaks - Love Is Kind (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C27" t="str">
         <v>https://www.youtube.com/watch?v=DtU94kpPeFM</v>
@@ -1401,7 +1401,7 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1427,7 +1427,7 @@
         <v>Madison Beer - free (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C28" t="str">
         <v>https://www.youtube.com/watch?v=VFNsNBOXQyU</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1465,7 +1465,7 @@
         <v>Tori Kelly - Dive (Official Audio)</v>
       </c>
       <c r="B29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C29" t="str">
         <v>https://www.youtube.com/watch?v=URXND4fdm6E</v>
@@ -1477,7 +1477,7 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1503,7 +1503,7 @@
         <v>Jeremy Camp - Reflector (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C30" t="str">
         <v>https://www.youtube.com/watch?v=tectUPnIrLo</v>
@@ -1515,7 +1515,7 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1541,7 +1541,7 @@
         <v>The Chainsmokers, Oaks - Five Past Three (Official Visualizer)</v>
       </c>
       <c r="B31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C31" t="str">
         <v>https://www.youtube.com/watch?v=H_Z0Kv-LWkU</v>
@@ -1553,7 +1553,7 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1579,7 +1579,7 @@
         <v>Ashley Cooke - high school sweetheart</v>
       </c>
       <c r="B32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C32" t="str">
         <v>https://www.youtube.com/watch?v=I_t7z3cA3Jo</v>
@@ -1591,7 +1591,7 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1617,7 +1617,7 @@
         <v>Ari Abdul - Ego (Visualizer)</v>
       </c>
       <c r="B33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C33" t="str">
         <v>https://www.youtube.com/watch?v=L0FjVr6LpVU</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1655,7 +1655,7 @@
         <v>Quinn XCII - HOOPLA (Official Music Video)</v>
       </c>
       <c r="B34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C34" t="str">
         <v>https://www.youtube.com/watch?v=eNbGA1pgmFk</v>
@@ -1667,7 +1667,7 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1693,7 +1693,7 @@
         <v>Madison Beer - lovergirl (Official Music Video)</v>
       </c>
       <c r="B35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C35" t="str">
         <v>https://www.youtube.com/watch?v=q4lU1N3oqYQ</v>
@@ -1705,7 +1705,7 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1731,7 +1731,7 @@
         <v>David J - WHAT IF I'M IN LOVE (Official Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C36" t="str">
         <v>https://www.youtube.com/watch?v=-SF7Hm_ikaY</v>
@@ -1743,7 +1743,7 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -2225,7 +2225,7 @@
         <v>SIENNA SPIRO - Material Lover (The Devil Wears Prada 2)</v>
       </c>
       <c r="B49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C49" t="str">
         <v>https://www.youtube.com/watch?v=EZOiy1-cnxM</v>
@@ -2237,7 +2237,7 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2567,7 +2567,7 @@
         <v>Anna Graves - Damn In Love (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C58" t="str">
         <v>https://www.youtube.com/watch?v=HahAtUuq1QI</v>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2605,7 +2605,7 @@
         <v>Brandon Lake, Nick Jonas - The Author (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C59" t="str">
         <v>https://www.youtube.com/watch?v=vKzPmy3VUzY</v>
@@ -2617,7 +2617,7 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2643,7 +2643,7 @@
         <v>Letdown. - Do It For The Love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C60" t="str">
         <v>https://www.youtube.com/watch?v=vCvZbTEywr8</v>
@@ -2655,7 +2655,7 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2681,7 +2681,7 @@
         <v>Maroon 5 - Heroine (Official Lyric Video)</v>
       </c>
       <c r="B61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C61" t="str">
         <v>https://www.youtube.com/watch?v=izP-4q4YtNw</v>
@@ -2693,7 +2693,7 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2719,7 +2719,7 @@
         <v>Olivia O'Brien - I'm Perfect (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C62" t="str">
         <v>https://www.youtube.com/watch?v=leHb8CowDSw</v>
@@ -2731,7 +2731,7 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2757,7 +2757,7 @@
         <v>ERNEST - What's A Little Rain (Official Music Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C63" t="str">
         <v>https://www.youtube.com/watch?v=U-3AGDH3mf4</v>
@@ -2769,7 +2769,7 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2795,7 +2795,7 @@
         <v>Claire Rosinkranz - Just A Man (Official Audio)</v>
       </c>
       <c r="B64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C64" t="str">
         <v>https://www.youtube.com/watch?v=Ta2I3EHXaDI</v>
@@ -2807,7 +2807,7 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2833,7 +2833,7 @@
         <v>Halsey - Nothing! (Official Audio)</v>
       </c>
       <c r="B65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C65" t="str">
         <v>https://www.youtube.com/watch?v=PBv71KbKvHA</v>
@@ -2845,7 +2845,7 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2871,7 +2871,7 @@
         <v>Zara Larsson, Madison Beer, BAMBII - The Ambition (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C66" t="str">
         <v>https://www.youtube.com/watch?v=5-f07ca1Zfg</v>
@@ -2883,7 +2883,7 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2909,7 +2909,7 @@
         <v>Halsey - Carry the Weight (Official Audio)</v>
       </c>
       <c r="B67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C67" t="str">
         <v>https://www.youtube.com/watch?v=6MewHp8BX0w</v>
@@ -2921,7 +2921,7 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2947,7 +2947,7 @@
         <v>Bishop Briggs - Blood From A Stone (Official)</v>
       </c>
       <c r="B68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C68" t="str">
         <v>https://www.youtube.com/watch?v=3CK6Zbdk-Nw</v>
@@ -2959,7 +2959,7 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>Louis Tomlinson - Save Me Time (Demo) (Official Audio)</v>
       </c>
       <c r="B69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C69" t="str">
         <v>https://www.youtube.com/watch?v=6-AWBV5FCN4</v>
@@ -2997,7 +2997,7 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3023,7 +3023,7 @@
         <v>almost monday - no more regrets (official video)</v>
       </c>
       <c r="B70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C70" t="str">
         <v>https://www.youtube.com/watch?v=iczsZVZxHKs</v>
@@ -3035,7 +3035,7 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3061,7 +3061,7 @@
         <v>FULL CIRCLE BOYS - BLEACHERS (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C71" t="str">
         <v>https://www.youtube.com/watch?v=lJM-z0ohbkc</v>
@@ -3073,7 +3073,7 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3099,7 +3099,7 @@
         <v>Kacey Musgraves - I Believe In Ghosts (Official Lyric Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C72" t="str">
         <v>https://www.youtube.com/watch?v=6AjhDPwpoLI</v>
@@ -3111,7 +3111,7 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>Nightly (feat. Fly By Midnight) - 1989 (Official Lyric Video)</v>
       </c>
       <c r="B73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C73" t="str">
         <v>https://www.youtube.com/watch?v=F4ndJUCsHKg</v>
@@ -3149,7 +3149,7 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3175,7 +3175,7 @@
         <v>Zara Larsson, Shakira - Eurosummer (Girls Trip - Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C74" t="str">
         <v>https://www.youtube.com/watch?v=-IEb-ym7VeQ</v>
@@ -3187,7 +3187,7 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3213,7 +3213,7 @@
         <v>JORDANA BRYANT - Truth Is (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C75" t="str">
         <v>https://www.youtube.com/watch?v=D4meCyyV7SQ</v>
@@ -3225,7 +3225,7 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3251,7 +3251,7 @@
         <v>Leanna Crawford - Thank God (Lyric Video)</v>
       </c>
       <c r="B76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C76" t="str">
         <v>https://www.youtube.com/watch?v=QqcSoUft03s</v>
@@ -3263,7 +3263,7 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3289,7 +3289,7 @@
         <v>Girl Tones - Stubborn Mouth (Official Music Video)</v>
       </c>
       <c r="B77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=_-PyPUWZTDY</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Tauren Wells - What A Miracle Feels Like (Official Audio)</v>
       </c>
       <c r="B78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C78" t="str">
         <v>https://www.youtube.com/watch?v=ZojFIe4Swmk</v>
@@ -3339,7 +3339,7 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3403,7 +3403,7 @@
         <v>Dons - Is There Something</v>
       </c>
       <c r="B80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C80" t="str">
         <v>https://www.youtube.com/watch?v=AgWIjvD-i0E</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G80" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1009,7 +1009,7 @@
         <v>Caity Baser - Holiday Song (Official Video)</v>
       </c>
       <c r="B17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C17" t="str">
         <v>https://www.youtube.com/watch?v=v-UVL6XW8l8</v>
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1047,7 +1047,7 @@
         <v>Sam Fischer - A Heart Doesn't Hurt Itself (Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C18" t="str">
         <v>https://www.youtube.com/watch?v=PGpaSK7G25I</v>
@@ -1059,7 +1059,7 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -2301,7 +2301,7 @@
         <v>Jessie J - THREW IT AWAY (Official Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C51" t="str">
         <v>https://www.youtube.com/watch?v=epsIrMBnxJk</v>
@@ -2313,7 +2313,7 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2491,7 +2491,7 @@
         <v>The Kiffness - Serafino (Singing Cat Song)</v>
       </c>
       <c r="B56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C56" t="str">
         <v>https://www.youtube.com/watch?v=YYA1zwRP9z8</v>
@@ -2503,7 +2503,7 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2529,7 +2529,7 @@
         <v>Dennis Lloyd - A Place I'm Calling Home (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C57" t="str">
         <v>https://www.youtube.com/watch?v=3BzvnTnBQIY</v>
@@ -2541,7 +2541,7 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G57" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -743,7 +743,7 @@
         <v>Talking Heads - Stay Up Late (Official Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C10" t="str">
         <v>https://www.youtube.com/watch?v=agnEV5frxC0</v>
@@ -755,7 +755,7 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -2073,7 +2073,7 @@
         <v>Holly Humberstone - White Noise (Live) | Presented By Spotify</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C45" t="str">
         <v>https://www.youtube.com/watch?v=-CNhkM5DgrU</v>
@@ -2085,7 +2085,7 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2453,7 +2453,7 @@
         <v>The Beaches - Should've Known Better (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C55" t="str">
         <v>https://www.youtube.com/watch?v=nhTdgpPXbe8</v>
@@ -2465,7 +2465,7 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G55" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,7 +439,7 @@
         <v>Harry Styles - Dance No More (Official Video)</v>
       </c>
       <c r="B2" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C2" t="str">
         <v>https://www.youtube.com/watch?v=-rkjE0xc730</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -477,7 +477,7 @@
         <v>Eagles - One Of These Nights (Through The Years - Official Video)</v>
       </c>
       <c r="B3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=bgvZCCAvChY</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -515,7 +515,7 @@
         <v>Body Roll - Nora Fatehi feat. Yo Yo Honey Singh [Official Music Video]</v>
       </c>
       <c r="B4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C4" t="str">
         <v>https://www.youtube.com/watch?v=hOrvqKLbZY4</v>
@@ -527,7 +527,7 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -705,7 +705,7 @@
         <v>Simply Red - Something Got Me Started (Live in Santiago)</v>
       </c>
       <c r="B9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C9" t="str">
         <v>https://www.youtube.com/watch?v=27Vl-z67UBQ</v>
@@ -717,7 +717,7 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -781,7 +781,7 @@
         <v>Ellise - Liplock (Official Music Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C11" t="str">
         <v>https://www.youtube.com/watch?v=Qrh2meycGdk</v>
@@ -793,7 +793,7 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -819,7 +819,7 @@
         <v>Tori Kelly - Dive (Official Music Video)</v>
       </c>
       <c r="B12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C12" t="str">
         <v>https://www.youtube.com/watch?v=g28_yFMfjkc</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -857,7 +857,7 @@
         <v>David Gilmour with Romany Gilmour - Between Two Points (Later... with Jools Holland, 02/11/2024)</v>
       </c>
       <c r="B13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C13" t="str">
         <v>https://www.youtube.com/watch?v=tA8c0Ek0dlM</v>
@@ -869,7 +869,7 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -895,7 +895,7 @@
         <v>Scorpions - Bad Boys Running Wild (Madison Square Garden 2022)</v>
       </c>
       <c r="B14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=MwsMTgbQ46M</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -933,7 +933,7 @@
         <v>Claire Leslie - Passenger Seat (Official Music Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=7JdV8lTp4H8</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -971,7 +971,7 @@
         <v>Michael Schulte - Lovesick (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=dx3H9Merx5M</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1921,7 +1921,7 @@
         <v>Paris Paloma - Stem the Flow [Official Music Video]</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C41" t="str">
         <v>https://www.youtube.com/watch?v=HasPLp596MU</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1959,7 +1959,7 @@
         <v>Lucy Blue - Who you love (Visualiser)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C42" t="str">
         <v>https://www.youtube.com/watch?v=CblE3TfIYWE</v>
@@ -1971,7 +1971,7 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Olivia Dean - A Couple Minutes (Live from The MOBO Awards 2026)</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C43" t="str">
         <v>https://www.youtube.com/watch?v=sNeiL75ZMRI</v>
@@ -2009,7 +2009,7 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2035,7 +2035,7 @@
         <v>Aaron Frazer - It's A Shame (Official Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C44" t="str">
         <v>https://www.youtube.com/watch?v=kAlb5pd7sNU</v>
@@ -2047,7 +2047,7 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2149,7 +2149,7 @@
         <v>The Rolling Stones - In The Stars (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C47" t="str">
         <v>https://www.youtube.com/watch?v=F-F_oHOvBsM</v>
@@ -2161,7 +2161,7 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2187,7 +2187,7 @@
         <v>Dermot Kennedy - The Only Time I Prayed (Official Visualiser)</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C48" t="str">
         <v>https://www.youtube.com/watch?v=4JKrT3sak5A</v>
@@ -2199,7 +2199,7 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2263,7 +2263,7 @@
         <v>Rick Astley - Raindrops (Official Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C50" t="str">
         <v>https://www.youtube.com/watch?v=LjmOX9jGoR4</v>
@@ -2275,7 +2275,7 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2339,7 +2339,7 @@
         <v>The Takes - Ain't Love (Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C52" t="str">
         <v>https://www.youtube.com/watch?v=YIKR9fN8by0</v>
@@ -2351,7 +2351,7 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2377,7 +2377,7 @@
         <v>The Offspring - Bad Habit (Live from The Honda Center 2024) | SMASH 30th Anniversary</v>
       </c>
       <c r="B53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C53" t="str">
         <v>https://www.youtube.com/watch?v=6eBNIVQAZXY</v>
@@ -2389,7 +2389,7 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2415,7 +2415,7 @@
         <v>Louis Tomlinson - Sunflowers (Official Performance Video)</v>
       </c>
       <c r="B54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="C54" t="str">
         <v>https://www.youtube.com/watch?v=weCNpsGFzd8</v>
@@ -2427,7 +2427,7 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>12 days ago</v>
+        <v>13 days ago</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -4236,13 +4236,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dirty Rosie</v>
+        <v>Tu recuerdo</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
+        <v>https://music.apple.com/us/song/tu-recuerdo/6763660843</v>
       </c>
       <c r="D102" t="str">
         <v>2026-05-14</v>
@@ -4251,25 +4251,25 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Little Miss Twain</v>
+        <v>Loco X Volver</v>
       </c>
       <c r="G102" t="str">
-        <v>2:46</v>
+        <v>3:55</v>
       </c>
       <c r="H102" t="str">
-        <v>Shania Twain</v>
+        <v>Maluma</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
+        <v>https://music.apple.com/us/album/tu-recuerdo/1895423065</v>
       </c>
       <c r="L102" t="str">
-        <v>Dirty Rosie - Shania Twain</v>
+        <v>Tu recuerdo - Maluma</v>
       </c>
     </row>
     <row r="103">
@@ -4540,13 +4540,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Like you mean it</v>
+        <v>Dirty Rosie</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
+        <v>https://music.apple.com/us/song/dirty-rosie/6767044374</v>
       </c>
       <c r="D110" t="str">
         <v>2026-05-14</v>
@@ -4555,25 +4555,25 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>When the lights turn on</v>
+        <v>Little Miss Twain</v>
       </c>
       <c r="G110" t="str">
-        <v>2:27</v>
+        <v>2:46</v>
       </c>
       <c r="H110" t="str">
-        <v>MICO</v>
+        <v>Shania Twain</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/mico/1457367370</v>
+        <v>https://music.apple.com/us/artist/shania-twain/129974</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
+        <v>https://music.apple.com/us/album/dirty-rosie/1896356105</v>
       </c>
       <c r="L110" t="str">
-        <v>Like you mean it - MICO</v>
+        <v>Dirty Rosie - Shania Twain</v>
       </c>
     </row>
     <row r="111">
@@ -4616,13 +4616,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>linknb</v>
+        <v>Like you mean it</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/linknb/1888561848</v>
+        <v>https://music.apple.com/us/song/like-you-mean-it/6767024693</v>
       </c>
       <c r="D112" t="str">
         <v>2026-05-14</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>new avatar</v>
+        <v>When the lights turn on</v>
       </c>
       <c r="G112" t="str">
-        <v>1:55</v>
+        <v>2:27</v>
       </c>
       <c r="H112" t="str">
-        <v>Kelela</v>
+        <v>MICO</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/mico/1457367370</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/linknb/1888561538</v>
+        <v>https://music.apple.com/us/album/like-you-mean-it/6767024688</v>
       </c>
       <c r="L112" t="str">
-        <v>linknb - Kelela</v>
+        <v>Like you mean it - MICO</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Robotic Love</v>
+        <v>linknb</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
+        <v>https://music.apple.com/us/song/linknb/1888561848</v>
       </c>
       <c r="D113" t="str">
         <v>2026-05-14</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Robotic Love - Single</v>
+        <v>new avatar</v>
       </c>
       <c r="G113" t="str">
-        <v>3:25</v>
+        <v>1:55</v>
       </c>
       <c r="H113" t="str">
-        <v>elkan</v>
+        <v>Kelela</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
+        <v>https://music.apple.com/us/album/linknb/1888561538</v>
       </c>
       <c r="L113" t="str">
-        <v>Robotic Love - elkan</v>
+        <v>linknb - Kelela</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Baby</v>
+        <v>Robotic Love</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/baby/6763651180</v>
+        <v>https://music.apple.com/us/song/robotic-love/6763638857</v>
       </c>
       <c r="D114" t="str">
         <v>2026-05-14</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Baby - Single</v>
+        <v>Robotic Love - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H114" t="str">
-        <v>Prospa</v>
+        <v>elkan</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/prospa/962366708</v>
+        <v>https://music.apple.com/us/artist/elkan/1805013361</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/baby/1895418297</v>
+        <v>https://music.apple.com/us/album/robotic-love/1895412608</v>
       </c>
       <c r="L114" t="str">
-        <v>Baby - Prospa</v>
+        <v>Robotic Love - elkan</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Boots (feat. Fetty Wap)</v>
+        <v>Baby</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
+        <v>https://music.apple.com/us/song/baby/6763651180</v>
       </c>
       <c r="D115" t="str">
         <v>2026-05-14</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Boots (feat. Fetty Wap) - Single</v>
+        <v>Baby - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>2:39</v>
+        <v>3:13</v>
       </c>
       <c r="H115" t="str">
-        <v>Russell Dickerson</v>
+        <v>Prospa</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
+        <v>https://music.apple.com/us/artist/prospa/962366708</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
+        <v>https://music.apple.com/us/album/baby/1895418297</v>
       </c>
       <c r="L115" t="str">
-        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
+        <v>Baby - Prospa</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Bed of Roses</v>
+        <v>Boots (feat. Fetty Wap)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
+        <v>https://music.apple.com/us/song/boots-feat-fetty-wap/6763152116</v>
       </c>
       <c r="D116" t="str">
         <v>2026-05-14</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Bed of Roses - Single</v>
+        <v>Boots (feat. Fetty Wap) - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:05</v>
+        <v>2:39</v>
       </c>
       <c r="H116" t="str">
-        <v>Teyana Taylor</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
+        <v>https://music.apple.com/us/artist/russell-dickerson/415673786</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
+        <v>https://music.apple.com/us/album/boots-feat-fetty-wap/1895187005</v>
       </c>
       <c r="L116" t="str">
-        <v>Bed of Roses - Teyana Taylor</v>
+        <v>Boots (feat. Fetty Wap) - Russell Dickerson</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Lo Arriesgo Todo</v>
+        <v>Bed of Roses</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
+        <v>https://music.apple.com/us/song/bed-of-roses/6765599768</v>
       </c>
       <c r="D117" t="str">
         <v>2026-05-14</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Lo Arriesgo Todo - Single</v>
+        <v>Bed of Roses - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:24</v>
+        <v>3:05</v>
       </c>
       <c r="H117" t="str">
-        <v>Bruno Mars</v>
+        <v>Teyana Taylor</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
+        <v>https://music.apple.com/us/artist/teyana-taylor/216698214</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
+        <v>https://music.apple.com/us/album/bed-of-roses/1896005623</v>
       </c>
       <c r="L117" t="str">
-        <v>Lo Arriesgo Todo - Bruno Mars</v>
+        <v>Bed of Roses - Teyana Taylor</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Big Dog</v>
+        <v>Lo Arriesgo Todo</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
+        <v>https://music.apple.com/us/song/lo-arriesgo-todo/6766999307</v>
       </c>
       <c r="D118" t="str">
         <v>2026-05-14</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Big Dog - Single</v>
+        <v>Lo Arriesgo Todo - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>2:59</v>
+        <v>3:24</v>
       </c>
       <c r="H118" t="str">
-        <v>The Last Dinner Party</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
+        <v>https://music.apple.com/us/artist/bruno-mars/278873078</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
+        <v>https://music.apple.com/us/album/lo-arriesgo-todo/6766999303</v>
       </c>
       <c r="L118" t="str">
-        <v>Big Dog - The Last Dinner Party</v>
+        <v>Lo Arriesgo Todo - Bruno Mars</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Eastside Girls</v>
+        <v>Big Dog</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
+        <v>https://music.apple.com/us/song/big-dog/6762481627</v>
       </c>
       <c r="D119" t="str">
         <v>2026-05-14</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Dancing On The Wall</v>
+        <v>Big Dog - Single</v>
       </c>
       <c r="G119" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H119" t="str">
-        <v>MUNA</v>
+        <v>The Last Dinner Party</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-last-dinner-party/1680519203</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
+        <v>https://music.apple.com/us/album/big-dog/1894318010</v>
       </c>
       <c r="L119" t="str">
-        <v>Eastside Girls - MUNA</v>
+        <v>Big Dog - The Last Dinner Party</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>In The Stars</v>
+        <v>Eastside Girls</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
+        <v>https://music.apple.com/us/song/eastside-girls/1870703307</v>
       </c>
       <c r="D120" t="str">
         <v>2026-05-14</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Foreign Tongues</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G120" t="str">
-        <v>4:13</v>
+        <v>3:50</v>
       </c>
       <c r="H120" t="str">
-        <v>The Rolling Stones</v>
+        <v>MUNA</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
+        <v>https://music.apple.com/us/album/eastside-girls/1870702692</v>
       </c>
       <c r="L120" t="str">
-        <v>In The Stars - The Rolling Stones</v>
+        <v>Eastside Girls - MUNA</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Home to Us</v>
+        <v>In The Stars</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
+        <v>https://music.apple.com/us/song/in-the-stars/6764865395</v>
       </c>
       <c r="D121" t="str">
         <v>2026-05-14</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>The Boys of Dungeon Lane</v>
+        <v>Foreign Tongues</v>
       </c>
       <c r="G121" t="str">
-        <v>3:11</v>
+        <v>4:13</v>
       </c>
       <c r="H121" t="str">
-        <v>Paul McCartney</v>
+        <v>The Rolling Stones</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
+        <v>https://music.apple.com/us/artist/the-rolling-stones/1249595</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
+        <v>https://music.apple.com/us/album/in-the-stars/1895941732</v>
       </c>
       <c r="L121" t="str">
-        <v>Home to Us - Paul McCartney</v>
+        <v>In The Stars - The Rolling Stones</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Hurts Like You</v>
+        <v>Home to Us</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
+        <v>https://music.apple.com/us/song/home-to-us/1887403096</v>
       </c>
       <c r="D122" t="str">
         <v>2026-05-14</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>The Night Champion</v>
+        <v>The Boys of Dungeon Lane</v>
       </c>
       <c r="G122" t="str">
-        <v>3:15</v>
+        <v>3:11</v>
       </c>
       <c r="H122" t="str">
-        <v>Koe Wetzel</v>
+        <v>Paul McCartney</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
+        <v>https://music.apple.com/us/artist/paul-mccartney/12224</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
+        <v>https://music.apple.com/us/album/home-to-us/1887402919</v>
       </c>
       <c r="L122" t="str">
-        <v>Hurts Like You - Koe Wetzel</v>
+        <v>Home to Us - Paul McCartney</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Find Us Again</v>
+        <v>Hurts Like You</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
+        <v>https://music.apple.com/us/song/hurts-like-you/6765521189</v>
       </c>
       <c r="D123" t="str">
         <v>2026-05-14</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Find Us Again - Single</v>
+        <v>The Night Champion</v>
       </c>
       <c r="G123" t="str">
-        <v>2:58</v>
+        <v>3:15</v>
       </c>
       <c r="H123" t="str">
-        <v>Xavi</v>
+        <v>Koe Wetzel</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
+        <v>https://music.apple.com/us/artist/koe-wetzel/1139953953</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
+        <v>https://music.apple.com/us/album/hurts-like-you/1895978438</v>
       </c>
       <c r="L123" t="str">
-        <v>Find Us Again - Xavi</v>
+        <v>Hurts Like You - Koe Wetzel</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tied Up</v>
+        <v>Find Us Again</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
+        <v>https://music.apple.com/us/song/find-us-again/6764638179</v>
       </c>
       <c r="D124" t="str">
         <v>2026-05-14</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tied Up - Single</v>
+        <v>Find Us Again - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>2:56</v>
+        <v>2:58</v>
       </c>
       <c r="H124" t="str">
-        <v>Khalid</v>
+        <v>Xavi</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/khalid/82842423</v>
+        <v>https://music.apple.com/us/artist/xavi/1525566726</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
+        <v>https://music.apple.com/us/album/find-us-again/1895860349</v>
       </c>
       <c r="L124" t="str">
-        <v>Tied Up - Khalid</v>
+        <v>Find Us Again - Xavi</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Antes De Ti</v>
+        <v>Tied Up</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
+        <v>https://music.apple.com/us/song/tied-up/6765699130</v>
       </c>
       <c r="D125" t="str">
         <v>2026-05-14</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Antes De Ti - Single</v>
+        <v>Tied Up - Single</v>
       </c>
       <c r="G125" t="str">
         <v>2:56</v>
       </c>
       <c r="H125" t="str">
-        <v>Silvana Estrada</v>
+        <v>Khalid</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
+        <v>https://music.apple.com/us/artist/khalid/82842423</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
+        <v>https://music.apple.com/us/album/tied-up/1896041630</v>
       </c>
       <c r="L125" t="str">
-        <v>Antes De Ti - Silvana Estrada</v>
+        <v>Tied Up - Khalid</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>En La Misma Cama</v>
+        <v>Antes De Ti</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
+        <v>https://music.apple.com/us/song/antes-de-ti/1891167102</v>
       </c>
       <c r="D126" t="str">
         <v>2026-05-14</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>MUDA</v>
+        <v>Antes De Ti - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>2:51</v>
+        <v>2:56</v>
       </c>
       <c r="H126" t="str">
-        <v>Carín León</v>
+        <v>Silvana Estrada</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
+        <v>https://music.apple.com/us/artist/silvana-estrada/1277235729</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
+        <v>https://music.apple.com/us/album/antes-de-ti/1891167099</v>
       </c>
       <c r="L126" t="str">
-        <v>En La Misma Cama - Carín León</v>
+        <v>Antes De Ti - Silvana Estrada</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>lovergirl</v>
+        <v>En La Misma Cama</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
+        <v>https://music.apple.com/us/song/en-la-misma-cama/6763670999</v>
       </c>
       <c r="D127" t="str">
         <v>2026-05-14</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>locket deluxe</v>
+        <v>MUDA</v>
       </c>
       <c r="G127" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H127" t="str">
-        <v>Madison Beer</v>
+        <v>Carín León</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
+        <v>https://music.apple.com/us/artist/car%C3%ADn-le%C3%B3n/1370196486</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
+        <v>https://music.apple.com/us/album/en-la-misma-cama/1895429814</v>
       </c>
       <c r="L127" t="str">
-        <v>lovergirl - Madison Beer</v>
+        <v>En La Misma Cama - Carín León</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>PANIKI</v>
+        <v>lovergirl</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/paniki/1892534080</v>
+        <v>https://music.apple.com/us/song/lovergirl/6766366578</v>
       </c>
       <c r="D128" t="str">
         <v>2026-05-14</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Los Locos Nunca Mueren</v>
+        <v>locket deluxe</v>
       </c>
       <c r="G128" t="str">
-        <v>2:36</v>
+        <v>3:21</v>
       </c>
       <c r="H128" t="str">
-        <v>Chuyin</v>
+        <v>Madison Beer</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
+        <v>https://music.apple.com/us/artist/madison-beer/696146587</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/paniki/1892533803</v>
+        <v>https://music.apple.com/us/album/lovergirl/6766366564</v>
       </c>
       <c r="L128" t="str">
-        <v>PANIKI - Chuyin</v>
+        <v>lovergirl - Madison Beer</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>DesOrden</v>
+        <v>PANIKI</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/desorden/6765776443</v>
+        <v>https://music.apple.com/us/song/paniki/1892534080</v>
       </c>
       <c r="D129" t="str">
         <v>2026-05-14</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>DesOrden - Single</v>
+        <v>Los Locos Nunca Mueren</v>
       </c>
       <c r="G129" t="str">
         <v>2:36</v>
       </c>
       <c r="H129" t="str">
-        <v>Alleh</v>
+        <v>Chuyin</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
+        <v>https://music.apple.com/us/artist/chuyin/1766532018</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/desorden/1896069663</v>
+        <v>https://music.apple.com/us/album/paniki/1892533803</v>
       </c>
       <c r="L129" t="str">
-        <v>DesOrden - Alleh</v>
+        <v>PANIKI - Chuyin</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>LA Nights</v>
+        <v>DesOrden</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
+        <v>https://music.apple.com/us/song/desorden/6765776443</v>
       </c>
       <c r="D130" t="str">
         <v>2026-05-14</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>The Ville</v>
+        <v>DesOrden - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:18</v>
+        <v>2:36</v>
       </c>
       <c r="H130" t="str">
-        <v>Trap Dickey</v>
+        <v>Alleh</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/alleh/1644755393</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
+        <v>https://music.apple.com/us/album/desorden/1896069663</v>
       </c>
       <c r="L130" t="str">
-        <v>LA Nights - Trap Dickey</v>
+        <v>DesOrden - Alleh</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>The Payoff</v>
+        <v>LA Nights</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
+        <v>https://music.apple.com/us/song/la-nights/6763580223</v>
       </c>
       <c r="D131" t="str">
         <v>2026-05-14</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>The Payoff - Single</v>
+        <v>The Ville</v>
       </c>
       <c r="G131" t="str">
-        <v>5:51</v>
+        <v>2:18</v>
       </c>
       <c r="H131" t="str">
-        <v>Father John Misty</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
+        <v>https://music.apple.com/us/album/la-nights/1895384937</v>
       </c>
       <c r="L131" t="str">
-        <v>The Payoff - Father John Misty</v>
+        <v>LA Nights - Trap Dickey</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>The Weak</v>
+        <v>The Payoff</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
+        <v>https://music.apple.com/us/song/the-payoff/1891518506</v>
       </c>
       <c r="D132" t="str">
         <v>2026-05-14</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>The Payoff - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:15</v>
+        <v>5:51</v>
       </c>
       <c r="H132" t="str">
-        <v>Iceage</v>
+        <v>Father John Misty</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/father-john-misty/514361724</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
+        <v>https://music.apple.com/us/album/the-payoff/1891518505</v>
       </c>
       <c r="L132" t="str">
-        <v>The Weak - Iceage</v>
+        <v>The Payoff - Father John Misty</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Life Of The Faaji</v>
+        <v>The Weak</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
+        <v>https://music.apple.com/us/song/the-weak/1880484489</v>
       </c>
       <c r="D133" t="str">
         <v>2026-05-14</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Fuji Xtra</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G133" t="str">
-        <v>2:29</v>
+        <v>3:15</v>
       </c>
       <c r="H133" t="str">
-        <v>Adekunle Gold</v>
+        <v>Iceage</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
+        <v>https://music.apple.com/us/album/the-weak/1880484160</v>
       </c>
       <c r="L133" t="str">
-        <v>Life Of The Faaji - Adekunle Gold</v>
+        <v>The Weak - Iceage</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Satisfy</v>
+        <v>Life Of The Faaji</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
+        <v>https://music.apple.com/us/song/life-of-the-faaji/1893417486</v>
       </c>
       <c r="D134" t="str">
         <v>2026-05-14</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Satisfy - Single</v>
+        <v>Fuji Xtra</v>
       </c>
       <c r="G134" t="str">
-        <v>3:06</v>
+        <v>2:29</v>
       </c>
       <c r="H134" t="str">
-        <v>Calvin Harris</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
+        <v>https://music.apple.com/us/album/life-of-the-faaji/1893417480</v>
       </c>
       <c r="L134" t="str">
-        <v>Satisfy - Calvin Harris</v>
+        <v>Life Of The Faaji - Adekunle Gold</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
+        <v>Satisfy</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
+        <v>https://music.apple.com/us/song/satisfy/1894316978</v>
       </c>
       <c r="D135" t="str">
         <v>2026-05-14</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
+        <v>Satisfy - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H135" t="str">
-        <v>DEAN</v>
+        <v>Calvin Harris</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/dean/2770824</v>
+        <v>https://music.apple.com/us/artist/calvin-harris/201955086</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
+        <v>https://music.apple.com/us/album/satisfy/1894316975</v>
       </c>
       <c r="L135" t="str">
-        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
+        <v>Satisfy - Calvin Harris</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Ashin' the Blunt</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!)</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
+        <v>https://music.apple.com/us/song/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316768</v>
       </c>
       <c r="D136" t="str">
         <v>2026-05-14</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:48</v>
+        <v>3:03</v>
       </c>
       <c r="H136" t="str">
-        <v>6LACK</v>
+        <v>DEAN</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/dean/2770824</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
+        <v>https://music.apple.com/us/album/aftertaste-from-original-motion-picture-soundtrack-k-pops/6766316765</v>
       </c>
       <c r="L136" t="str">
-        <v>Ashin' the Blunt - 6LACK</v>
+        <v>Aftertaste (from Original Motion Picture Soundtrack K-POPS!) - DEAN</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>I Wanna Rock</v>
+        <v>Ashin' the Blunt</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
+        <v>https://music.apple.com/us/song/ashin-the-blunt/1884792300</v>
       </c>
       <c r="D137" t="str">
         <v>2026-05-14</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>I Wanna Rock - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G137" t="str">
-        <v>3:44</v>
+        <v>3:48</v>
       </c>
       <c r="H137" t="str">
-        <v>Cash Cobain</v>
+        <v>6LACK</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
+        <v>https://music.apple.com/us/album/ashin-the-blunt/1884792154</v>
       </c>
       <c r="L137" t="str">
-        <v>I Wanna Rock - Cash Cobain</v>
+        <v>Ashin' the Blunt - 6LACK</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Trying Times - A COLORS SHOW</v>
+        <v>I Wanna Rock</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
+        <v>https://music.apple.com/us/song/i-wanna-rock/1889577010</v>
       </c>
       <c r="D138" t="str">
         <v>2026-05-14</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Trying Times - A COLORS SHOW - Single</v>
+        <v>I Wanna Rock - Single</v>
       </c>
       <c r="G138" t="str">
-        <v>4:33</v>
+        <v>3:44</v>
       </c>
       <c r="H138" t="str">
-        <v>James Blake</v>
+        <v>Cash Cobain</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
+        <v>https://music.apple.com/us/artist/cash-cobain/953108105</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
+        <v>https://music.apple.com/us/album/i-wanna-rock/1889577009</v>
       </c>
       <c r="L138" t="str">
-        <v>Trying Times - A COLORS SHOW - James Blake</v>
+        <v>I Wanna Rock - Cash Cobain</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>One Two Police</v>
+        <v>Trying Times - A COLORS SHOW</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
+        <v>https://music.apple.com/us/song/trying-times-a-colors-show/6764557224</v>
       </c>
       <c r="D139" t="str">
         <v>2026-05-14</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>One Two Police - Single</v>
+        <v>Trying Times - A COLORS SHOW - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:46</v>
+        <v>4:33</v>
       </c>
       <c r="H139" t="str">
-        <v>BUNT.</v>
+        <v>James Blake</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
+        <v>https://music.apple.com/us/artist/james-blake/59504818</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
+        <v>https://music.apple.com/us/album/trying-times-a-colors-show/1895832124</v>
       </c>
       <c r="L139" t="str">
-        <v>One Two Police - BUNT.</v>
+        <v>Trying Times - A COLORS SHOW - James Blake</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>HOME TO MOTHER</v>
+        <v>One Two Police</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
+        <v>https://music.apple.com/us/song/one-two-police/6766293223</v>
       </c>
       <c r="D140" t="str">
         <v>2026-05-14</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>One Two Police - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:16</v>
+        <v>2:46</v>
       </c>
       <c r="H140" t="str">
-        <v>Stephen Sanchez</v>
+        <v>BUNT.</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/bunt/1436090348</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
+        <v>https://music.apple.com/us/album/one-two-police/1896268827</v>
       </c>
       <c r="L140" t="str">
-        <v>HOME TO MOTHER - Stephen Sanchez</v>
+        <v>One Two Police - BUNT.</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Illuminate</v>
+        <v>HOME TO MOTHER</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
+        <v>https://music.apple.com/us/song/home-to-mother/1880198197</v>
       </c>
       <c r="D141" t="str">
         <v>2026-05-14</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G141" t="str">
-        <v>3:03</v>
+        <v>3:16</v>
       </c>
       <c r="H141" t="str">
-        <v>Jessie Reyez</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
+        <v>https://music.apple.com/us/album/home-to-mother/1880197844</v>
       </c>
       <c r="L141" t="str">
-        <v>Illuminate - Jessie Reyez</v>
+        <v>HOME TO MOTHER - Stephen Sanchez</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>OKAY!</v>
+        <v>Illuminate</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/okay/6765792669</v>
+        <v>https://music.apple.com/us/song/illuminate/6764646733</v>
       </c>
       <c r="D142" t="str">
         <v>2026-05-14</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>OKAY! - Single</v>
+        <v>Illuminate (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>4:34</v>
+        <v>3:03</v>
       </c>
       <c r="H142" t="str">
-        <v>Forrest Frank</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/okay/1896077066</v>
+        <v>https://music.apple.com/us/album/illuminate/1895862895</v>
       </c>
       <c r="L142" t="str">
-        <v>OKAY! - Forrest Frank</v>
+        <v>Illuminate - Jessie Reyez</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>FLOW</v>
+        <v>OKAY!</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/flow/6765469196</v>
+        <v>https://music.apple.com/us/song/okay/6765792669</v>
       </c>
       <c r="D143" t="str">
         <v>2026-05-14</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>FLOW - Single</v>
+        <v>OKAY! - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>4:20</v>
+        <v>4:34</v>
       </c>
       <c r="H143" t="str">
-        <v>iZaak</v>
+        <v>Forrest Frank</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
+        <v>https://music.apple.com/us/artist/forrest-frank/1436657314</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/flow/1895961693</v>
+        <v>https://music.apple.com/us/album/okay/1896077066</v>
       </c>
       <c r="L143" t="str">
-        <v>FLOW - iZaak</v>
+        <v>OKAY! - Forrest Frank</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>aiaiaiaiai</v>
+        <v>FLOW</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
+        <v>https://music.apple.com/us/song/flow/6765469196</v>
       </c>
       <c r="D144" t="str">
         <v>2026-05-14</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>aiaiaiaiai - Single</v>
+        <v>FLOW - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:20</v>
+        <v>4:20</v>
       </c>
       <c r="H144" t="str">
-        <v>Mau y Ricky</v>
+        <v>iZaak</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/izaak/1295819563</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
+        <v>https://music.apple.com/us/album/flow/1895961693</v>
       </c>
       <c r="L144" t="str">
-        <v>aiaiaiaiai - Mau y Ricky</v>
+        <v>FLOW - iZaak</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Control</v>
+        <v>aiaiaiaiai</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/control/6765502013</v>
+        <v>https://music.apple.com/us/song/aiaiaiaiai/6764338271</v>
       </c>
       <c r="D145" t="str">
         <v>2026-05-14</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>God Must Really Love Me</v>
+        <v>aiaiaiaiai - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:32</v>
+        <v>2:20</v>
       </c>
       <c r="H145" t="str">
-        <v>Tori Kelly</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/control/1895974889</v>
+        <v>https://music.apple.com/us/album/aiaiaiaiai/1895739038</v>
       </c>
       <c r="L145" t="str">
-        <v>Control - Tori Kelly</v>
+        <v>aiaiaiaiai - Mau y Ricky</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ORIGAMI!</v>
+        <v>Control</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/origami/1892544033</v>
+        <v>https://music.apple.com/us/song/control/6765502013</v>
       </c>
       <c r="D146" t="str">
         <v>2026-05-14</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>ORIGAMI! - Single</v>
+        <v>God Must Really Love Me</v>
       </c>
       <c r="G146" t="str">
-        <v>2:34</v>
+        <v>2:32</v>
       </c>
       <c r="H146" t="str">
-        <v>Kesha</v>
+        <v>Tori Kelly</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/kesha/334854763</v>
+        <v>https://music.apple.com/us/artist/tori-kelly/437581991</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/origami/1892544026</v>
+        <v>https://music.apple.com/us/album/control/1895974889</v>
       </c>
       <c r="L146" t="str">
-        <v>ORIGAMI! - Kesha</v>
+        <v>Control - Tori Kelly</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Love Is Kind</v>
+        <v>ORIGAMI!</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
+        <v>https://music.apple.com/us/song/origami/1892544033</v>
       </c>
       <c r="D147" t="str">
         <v>2026-05-14</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Love Is Kind - EP</v>
+        <v>ORIGAMI! - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:07</v>
+        <v>2:34</v>
       </c>
       <c r="H147" t="str">
-        <v>The Chainsmokers</v>
+        <v>Kesha</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/kesha/334854763</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
+        <v>https://music.apple.com/us/album/origami/1892544026</v>
       </c>
       <c r="L147" t="str">
-        <v>Love Is Kind - The Chainsmokers</v>
+        <v>ORIGAMI! - Kesha</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Feathers In A Storm</v>
+        <v>Love Is Kind</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
+        <v>https://music.apple.com/us/song/love-is-kind/1894074886</v>
       </c>
       <c r="D148" t="str">
         <v>2026-05-14</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Let It Die Here</v>
+        <v>Love Is Kind - EP</v>
       </c>
       <c r="G148" t="str">
-        <v>4:00</v>
+        <v>4:07</v>
       </c>
       <c r="H148" t="str">
-        <v>Linda Perry</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
+        <v>https://music.apple.com/us/album/love-is-kind/1894074877</v>
       </c>
       <c r="L148" t="str">
-        <v>Feathers In A Storm - Linda Perry</v>
+        <v>Love Is Kind - The Chainsmokers</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Playing God</v>
+        <v>Feathers In A Storm</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
+        <v>https://music.apple.com/us/song/feathers-in-a-storm/1864390075</v>
       </c>
       <c r="D149" t="str">
         <v>2026-05-14</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Decades</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G149" t="str">
-        <v>3:39</v>
+        <v>4:00</v>
       </c>
       <c r="H149" t="str">
-        <v>Motionless In White</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
+        <v>https://music.apple.com/us/album/feathers-in-a-storm/1864389779</v>
       </c>
       <c r="L149" t="str">
-        <v>Playing God - Motionless In White</v>
+        <v>Feathers In A Storm - Linda Perry</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Cut</v>
+        <v>Playing God</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/cut/1879494712</v>
+        <v>https://music.apple.com/us/song/playing-god/6765780293</v>
       </c>
       <c r="D150" t="str">
         <v>2026-05-14</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>VINDICATE</v>
+        <v>Decades</v>
       </c>
       <c r="G150" t="str">
-        <v>3:59</v>
+        <v>3:39</v>
       </c>
       <c r="H150" t="str">
-        <v>Black Veil Brides</v>
+        <v>Motionless In White</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
+        <v>https://music.apple.com/us/artist/motionless-in-white/266666216</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/cut/1879494510</v>
+        <v>https://music.apple.com/us/album/playing-god/1896071360</v>
       </c>
       <c r="L150" t="str">
-        <v>Cut - Black Veil Brides</v>
+        <v>Playing God - Motionless In White</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Freaking Out</v>
+        <v>Cut</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
+        <v>https://music.apple.com/us/song/cut/1879494712</v>
       </c>
       <c r="D151" t="str">
         <v>2026-05-14</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Over Before You Know It</v>
+        <v>VINDICATE</v>
       </c>
       <c r="G151" t="str">
-        <v>3:03</v>
+        <v>3:59</v>
       </c>
       <c r="H151" t="str">
-        <v>Michigander</v>
+        <v>Black Veil Brides</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
+        <v>https://music.apple.com/us/artist/black-veil-brides/276789923</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
+        <v>https://music.apple.com/us/album/cut/1879494510</v>
       </c>
       <c r="L151" t="str">
-        <v>Freaking Out - Michigander</v>
+        <v>Cut - Black Veil Brides</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>FIYAH</v>
+        <v>Freaking Out</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
+        <v>https://music.apple.com/us/song/freaking-out/1894067912</v>
       </c>
       <c r="D152" t="str">
         <v>2026-05-14</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>FIYAH - Single</v>
+        <v>Over Before You Know It</v>
       </c>
       <c r="G152" t="str">
-        <v>3:12</v>
+        <v>3:03</v>
       </c>
       <c r="H152" t="str">
-        <v>YG Marley</v>
+        <v>Michigander</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
+        <v>https://music.apple.com/us/artist/michigander/1096482927</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
+        <v>https://music.apple.com/us/album/freaking-out/1894067897</v>
       </c>
       <c r="L152" t="str">
-        <v>FIYAH - YG Marley</v>
+        <v>Freaking Out - Michigander</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ten to Midnight</v>
+        <v>FIYAH</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
+        <v>https://music.apple.com/us/song/fiyah/6764321306</v>
       </c>
       <c r="D153" t="str">
         <v>2026-05-14</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Wild</v>
+        <v>FIYAH - Single</v>
       </c>
       <c r="G153" t="str">
         <v>3:12</v>
       </c>
       <c r="H153" t="str">
-        <v>Ashley McBryde</v>
+        <v>YG Marley</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/yg-marley/1496864889</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
+        <v>https://music.apple.com/us/album/fiyah/1895732105</v>
       </c>
       <c r="L153" t="str">
-        <v>Ten to Midnight - Ashley McBryde</v>
+        <v>FIYAH - YG Marley</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Carry On</v>
+        <v>Ten to Midnight</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
+        <v>https://music.apple.com/us/song/ten-to-midnight/1885047105</v>
       </c>
       <c r="D154" t="str">
         <v>2026-05-14</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Carry On - Single</v>
+        <v>Wild</v>
       </c>
       <c r="G154" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H154" t="str">
-        <v>Kenny Chesney</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
+        <v>https://music.apple.com/us/album/ten-to-midnight/1885046822</v>
       </c>
       <c r="L154" t="str">
-        <v>Carry On - Kenny Chesney</v>
+        <v>Ten to Midnight - Ashley McBryde</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>[PRESS]</v>
+        <v>Carry On</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/press/6764735125</v>
+        <v>https://music.apple.com/us/song/carry-on/1893511608</v>
       </c>
       <c r="D155" t="str">
         <v>2026-05-14</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>[PRESS] - Single</v>
+        <v>Carry On - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>1:40</v>
+        <v>3:00</v>
       </c>
       <c r="H155" t="str">
-        <v>Armani White</v>
+        <v>Kenny Chesney</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
+        <v>https://music.apple.com/us/artist/kenny-chesney/205322</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/press/1895898254</v>
+        <v>https://music.apple.com/us/album/carry-on/1893511607</v>
       </c>
       <c r="L155" t="str">
-        <v>[PRESS] - Armani White</v>
+        <v>Carry On - Kenny Chesney</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Hold Me In The Dark</v>
+        <v>[PRESS]</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
+        <v>https://music.apple.com/us/song/press/6764735125</v>
       </c>
       <c r="D156" t="str">
         <v>2026-05-14</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>[PRESS] - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>3:17</v>
+        <v>1:40</v>
       </c>
       <c r="H156" t="str">
-        <v>Myles Smith</v>
+        <v>Armani White</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/armani-white/1129439109</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
+        <v>https://music.apple.com/us/album/press/1895898254</v>
       </c>
       <c r="L156" t="str">
-        <v>Hold Me In The Dark - Myles Smith</v>
+        <v>[PRESS] - Armani White</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Lo Que Me Pasa Con Vos</v>
+        <v>Hold Me In The Dark</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
+        <v>https://music.apple.com/us/song/hold-me-in-the-dark/1886119371</v>
       </c>
       <c r="D157" t="str">
         <v>2026-05-14</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Lo Que Me Pasa Con Vos - Single</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G157" t="str">
-        <v>2:53</v>
+        <v>3:17</v>
       </c>
       <c r="H157" t="str">
-        <v>Sebastián Yatra</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
+        <v>https://music.apple.com/us/album/hold-me-in-the-dark/1886119367</v>
       </c>
       <c r="L157" t="str">
-        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
+        <v>Hold Me In The Dark - Myles Smith</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
+        <v>https://music.apple.com/us/song/lo-que-me-pasa-con-vos/6765831961</v>
       </c>
       <c r="D158" t="str">
         <v>2026-05-14</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Wide Eyed</v>
+        <v>Lo Que Me Pasa Con Vos - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:22</v>
+        <v>2:53</v>
       </c>
       <c r="H158" t="str">
-        <v>Mack Keane</v>
+        <v>Sebastián Yatra</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
+        <v>https://music.apple.com/us/artist/sebasti%C3%A1n-yatra/722264654</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
+        <v>https://music.apple.com/us/album/lo-que-me-pasa-con-vos/1896093008</v>
       </c>
       <c r="L158" t="str">
-        <v>Wide Eyed - Mack Keane</v>
+        <v>Lo Que Me Pasa Con Vos - Sebastián Yatra</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Changes</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/changes/6763650807</v>
+        <v>https://music.apple.com/us/song/wide-eyed/1884734079</v>
       </c>
       <c r="D159" t="str">
         <v>2026-05-14</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Changes - Single</v>
+        <v>Wide Eyed</v>
       </c>
       <c r="G159" t="str">
-        <v>3:18</v>
+        <v>3:22</v>
       </c>
       <c r="H159" t="str">
-        <v>Tommy Richman</v>
+        <v>Mack Keane</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
+        <v>https://music.apple.com/us/artist/mack-keane/899781096</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/changes/1895418156</v>
+        <v>https://music.apple.com/us/album/wide-eyed/1884733813</v>
       </c>
       <c r="L159" t="str">
-        <v>Changes - Tommy Richman</v>
+        <v>Wide Eyed - Mack Keane</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Don't Say Goodbye</v>
+        <v>Changes</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
+        <v>https://music.apple.com/us/song/changes/6763650807</v>
       </c>
       <c r="D160" t="str">
         <v>2026-05-14</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>The Story of Michael and Tanya</v>
+        <v>Changes - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>4:33</v>
+        <v>3:18</v>
       </c>
       <c r="H160" t="str">
-        <v>The War And Treaty</v>
+        <v>Tommy Richman</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
+        <v>https://music.apple.com/us/artist/tommy-richman/1447723583</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
+        <v>https://music.apple.com/us/album/changes/1895418156</v>
       </c>
       <c r="L160" t="str">
-        <v>Don't Say Goodbye - The War And Treaty</v>
+        <v>Changes - Tommy Richman</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>depressed on the internet</v>
+        <v>Don't Say Goodbye</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
+        <v>https://music.apple.com/us/song/dont-say-goodbye/6765758054</v>
       </c>
       <c r="D161" t="str">
         <v>2026-05-14</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>depressed on the internet - Single</v>
+        <v>The Story of Michael and Tanya</v>
       </c>
       <c r="G161" t="str">
-        <v>2:57</v>
+        <v>4:33</v>
       </c>
       <c r="H161" t="str">
-        <v>Bea Miller</v>
+        <v>The War And Treaty</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
+        <v>https://music.apple.com/us/artist/the-war-and-treaty/951165936</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
+        <v>https://music.apple.com/us/album/dont-say-goodbye/1896061742</v>
       </c>
       <c r="L161" t="str">
-        <v>depressed on the internet - Bea Miller</v>
+        <v>Don't Say Goodbye - The War And Treaty</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Dear Burt</v>
+        <v>depressed on the internet</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
+        <v>https://music.apple.com/us/song/depressed-on-the-internet/6763440792</v>
       </c>
       <c r="D162" t="str">
         <v>2026-05-14</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>depressed on the internet - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:53</v>
+        <v>2:57</v>
       </c>
       <c r="H162" t="str">
-        <v>Stephan Moccio</v>
+        <v>Bea Miller</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/bea-miller/706171903</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
+        <v>https://music.apple.com/us/album/depressed-on-the-internet/1895316228</v>
       </c>
       <c r="L162" t="str">
-        <v>Dear Burt - Stephan Moccio</v>
+        <v>depressed on the internet - Bea Miller</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Alla Blues</v>
+        <v>Dear Burt</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
+        <v>https://music.apple.com/us/song/dear-burt/1886736665</v>
       </c>
       <c r="D163" t="str">
         <v>2026-05-14</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Black Mozart</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G163" t="str">
-        <v>2:50</v>
+        <v>2:53</v>
       </c>
       <c r="H163" t="str">
-        <v>Jon Batiste</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
+        <v>https://music.apple.com/us/album/dear-burt/1886736650</v>
       </c>
       <c r="L163" t="str">
-        <v>Alla Blues - Jon Batiste</v>
+        <v>Dear Burt - Stephan Moccio</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Think About Me</v>
+        <v>Alla Blues</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
+        <v>https://music.apple.com/us/song/alla-blues/6764654322</v>
       </c>
       <c r="D164" t="str">
         <v>2026-05-14</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Think About Me - Single</v>
+        <v>Black Mozart</v>
       </c>
       <c r="G164" t="str">
-        <v>2:39</v>
+        <v>2:50</v>
       </c>
       <c r="H164" t="str">
-        <v>Gabriella Rose</v>
+        <v>Jon Batiste</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
+        <v>https://music.apple.com/us/artist/jon-batiste/211400086</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
+        <v>https://music.apple.com/us/album/alla-blues/1895866355</v>
       </c>
       <c r="L164" t="str">
-        <v>Think About Me - Gabriella Rose</v>
+        <v>Alla Blues - Jon Batiste</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Meet Again</v>
+        <v>Think About Me</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
+        <v>https://music.apple.com/us/song/think-about-me/6765783932</v>
       </c>
       <c r="D165" t="str">
         <v>2026-05-14</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Meet Again - Single</v>
+        <v>Think About Me - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:26</v>
+        <v>2:39</v>
       </c>
       <c r="H165" t="str">
-        <v>Kaskade</v>
+        <v>Gabriella Rose</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
+        <v>https://music.apple.com/us/artist/gabriella-rose/645706232</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
+        <v>https://music.apple.com/us/album/think-about-me/1896073124</v>
       </c>
       <c r="L165" t="str">
-        <v>Meet Again - Kaskade</v>
+        <v>Think About Me - Gabriella Rose</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Happy Now</v>
+        <v>Meet Again</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
+        <v>https://music.apple.com/us/song/meet-again/6764129305</v>
       </c>
       <c r="D166" t="str">
         <v>2026-05-14</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>The Afterparty</v>
+        <v>Meet Again - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:42</v>
+        <v>3:26</v>
       </c>
       <c r="H166" t="str">
-        <v>Lykke Li</v>
+        <v>Kaskade</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/kaskade/2827464</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
+        <v>https://music.apple.com/us/album/meet-again/1895652592</v>
       </c>
       <c r="L166" t="str">
-        <v>Happy Now - Lykke Li</v>
+        <v>Meet Again - Kaskade</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Oblivion</v>
+        <v>Happy Now</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
+        <v>https://music.apple.com/us/song/happy-now/1857952261</v>
       </c>
       <c r="D167" t="str">
         <v>2026-05-14</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Oblivion - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G167" t="str">
-        <v>2:21</v>
+        <v>2:42</v>
       </c>
       <c r="H167" t="str">
-        <v>Agents Of Time</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
+        <v>https://music.apple.com/us/album/happy-now/1857952252</v>
       </c>
       <c r="L167" t="str">
-        <v>Oblivion - Agents Of Time</v>
+        <v>Happy Now - Lykke Li</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
+        <v>Oblivion</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
+        <v>https://music.apple.com/us/song/oblivion/1888236202</v>
       </c>
       <c r="D168" t="str">
         <v>2026-05-14</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
+        <v>Oblivion - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>4:03</v>
+        <v>2:21</v>
       </c>
       <c r="H168" t="str">
-        <v>Papa Roach</v>
+        <v>Agents Of Time</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
+        <v>https://music.apple.com/us/artist/agents-of-time/794971951</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
+        <v>https://music.apple.com/us/album/oblivion/1888236199</v>
       </c>
       <c r="L168" t="str">
-        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
+        <v>Oblivion - Agents Of Time</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Top of the Hill</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry")</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
+        <v>https://music.apple.com/us/song/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386678</v>
       </c>
       <c r="D169" t="str">
         <v>2026-05-14</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Top of the Hill - Single</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Single</v>
       </c>
       <c r="G169" t="str">
-        <v>1:50</v>
+        <v>4:03</v>
       </c>
       <c r="H169" t="str">
-        <v>DDG</v>
+        <v>Papa Roach</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/ddg/3954994</v>
+        <v>https://music.apple.com/us/artist/papa-roach/3445763</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
+        <v>https://music.apple.com/us/album/see-u-in-hell-from-the-netflix-series-devil-may-cry/1894386676</v>
       </c>
       <c r="L169" t="str">
-        <v>Top of the Hill - DDG</v>
+        <v>See U in Hell (From the Netflix Series "Devil May Cry") - Papa Roach</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Oh Savannah</v>
+        <v>Top of the Hill</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
+        <v>https://music.apple.com/us/song/top-of-the-hill/6766614503</v>
       </c>
       <c r="D170" t="str">
         <v>2026-05-14</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Change Of Plans</v>
+        <v>Top of the Hill - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>3:05</v>
+        <v>1:50</v>
       </c>
       <c r="H170" t="str">
-        <v>49 Winchester</v>
+        <v>DDG</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
+        <v>https://music.apple.com/us/artist/ddg/3954994</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
+        <v>https://music.apple.com/us/album/top-of-the-hill/6766614303</v>
       </c>
       <c r="L170" t="str">
-        <v>Oh Savannah - 49 Winchester</v>
+        <v>Top of the Hill - DDG</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Game On (feat. JT)</v>
+        <v>Oh Savannah</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
+        <v>https://music.apple.com/us/song/oh-savannah/1869140944</v>
       </c>
       <c r="D171" t="str">
         <v>2026-05-14</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Sugar Girl - EP</v>
+        <v>Change Of Plans</v>
       </c>
       <c r="G171" t="str">
-        <v>2:29</v>
+        <v>3:05</v>
       </c>
       <c r="H171" t="str">
-        <v>Little Simz</v>
+        <v>49 Winchester</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
+        <v>https://music.apple.com/us/artist/49-winchester/869425058</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
+        <v>https://music.apple.com/us/album/oh-savannah/1869140544</v>
       </c>
       <c r="L171" t="str">
-        <v>Game On (feat. JT) - Little Simz</v>
+        <v>Oh Savannah - 49 Winchester</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>How to Forget</v>
+        <v>Game On (feat. JT)</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
+        <v>https://music.apple.com/us/song/game-on-feat-jt/6763271985</v>
       </c>
       <c r="D172" t="str">
         <v>2026-05-14</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>ARCADE</v>
+        <v>Sugar Girl - EP</v>
       </c>
       <c r="G172" t="str">
-        <v>4:01</v>
+        <v>2:29</v>
       </c>
       <c r="H172" t="str">
-        <v>Deb Never</v>
+        <v>Little Simz</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
+        <v>https://music.apple.com/us/artist/little-simz/627674564</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
+        <v>https://music.apple.com/us/album/game-on-feat-jt/1895242144</v>
       </c>
       <c r="L172" t="str">
-        <v>How to Forget - Deb Never</v>
+        <v>Game On (feat. JT) - Little Simz</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Ne Plus Ultra</v>
+        <v>How to Forget</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
+        <v>https://music.apple.com/us/song/how-to-forget/1874100607</v>
       </c>
       <c r="D173" t="str">
         <v>2026-05-14</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Ne Plus Ultra - Single</v>
+        <v>ARCADE</v>
       </c>
       <c r="G173" t="str">
-        <v>2:49</v>
+        <v>4:01</v>
       </c>
       <c r="H173" t="str">
-        <v>ear</v>
+        <v>Deb Never</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/ear/1829661500</v>
+        <v>https://music.apple.com/us/artist/deb-never/1421902332</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
+        <v>https://music.apple.com/us/album/how-to-forget/1874100412</v>
       </c>
       <c r="L173" t="str">
-        <v>Ne Plus Ultra - ear</v>
+        <v>How to Forget - Deb Never</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Mirror</v>
+        <v>Ne Plus Ultra</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/mirror/6763620093</v>
+        <v>https://music.apple.com/us/song/ne-plus-ultra/6765530891</v>
       </c>
       <c r="D174" t="str">
         <v>2026-05-14</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Mirror - Single</v>
+        <v>Ne Plus Ultra - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H174" t="str">
-        <v>MOD SUN</v>
+        <v>ear</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
+        <v>https://music.apple.com/us/artist/ear/1829661500</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/mirror/1895402181</v>
+        <v>https://music.apple.com/us/album/ne-plus-ultra/1895982136</v>
       </c>
       <c r="L174" t="str">
-        <v>Mirror - MOD SUN</v>
+        <v>Ne Plus Ultra - ear</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Miel Con Licor</v>
+        <v>Mirror</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
+        <v>https://music.apple.com/us/song/mirror/6763620093</v>
       </c>
       <c r="D175" t="str">
         <v>2026-05-14</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Bandera Blanca</v>
+        <v>Mirror - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:27</v>
+        <v>3:19</v>
       </c>
       <c r="H175" t="str">
-        <v>Christian Nodal</v>
+        <v>MOD SUN</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
+        <v>https://music.apple.com/us/artist/mod-sun/373888452</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
+        <v>https://music.apple.com/us/album/mirror/1895402181</v>
       </c>
       <c r="L175" t="str">
-        <v>Miel Con Licor - Christian Nodal</v>
+        <v>Mirror - MOD SUN</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Macramé (feat. Mei Semones)</v>
+        <v>Miel Con Licor</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
+        <v>https://music.apple.com/us/song/miel-con-licor/6763085043</v>
       </c>
       <c r="D176" t="str">
         <v>2026-05-14</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Macramé (feat. Mei Semones) - Single</v>
+        <v>Bandera Blanca</v>
       </c>
       <c r="G176" t="str">
-        <v>3:31</v>
+        <v>3:27</v>
       </c>
       <c r="H176" t="str">
-        <v>aron!</v>
+        <v>Christian Nodal</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/aron/1673838787</v>
+        <v>https://music.apple.com/us/artist/christian-nodal/1079597775</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
+        <v>https://music.apple.com/us/album/miel-con-licor/1895154946</v>
       </c>
       <c r="L176" t="str">
-        <v>Macramé (feat. Mei Semones) - aron!</v>
+        <v>Miel Con Licor - Christian Nodal</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
+        <v>Macramé (feat. Mei Semones)</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
+        <v>https://music.apple.com/us/song/macram%C3%A9-feat-mei-semones/6763155997</v>
       </c>
       <c r="D177" t="str">
         <v>2026-05-14</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>The Last Balloon</v>
+        <v>Macramé (feat. Mei Semones) - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>3:14</v>
+        <v>3:31</v>
       </c>
       <c r="H177" t="str">
-        <v>Tank and the Bangas</v>
+        <v>aron!</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
+        <v>https://music.apple.com/us/artist/aron/1673838787</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
+        <v>https://music.apple.com/us/album/macram%C3%A9-feat-mei-semones/1895189295</v>
       </c>
       <c r="L177" t="str">
-        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
+        <v>Macramé (feat. Mei Semones) - aron!</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>They Found One Of My Graves</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw)</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
+        <v>https://music.apple.com/us/song/nighttime-feat-austin-brown-david-shaw/1882831738</v>
       </c>
       <c r="D178" t="str">
         <v>2026-05-14</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Pre-Historic Metal</v>
+        <v>The Last Balloon</v>
       </c>
       <c r="G178" t="str">
-        <v>5:14</v>
+        <v>3:14</v>
       </c>
       <c r="H178" t="str">
-        <v>Darkthrone</v>
+        <v>Tank and the Bangas</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
+        <v>https://music.apple.com/us/artist/tank-and-the-bangas/685630243</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
+        <v>https://music.apple.com/us/album/nighttime-feat-austin-brown-david-shaw/1882831446</v>
       </c>
       <c r="L178" t="str">
-        <v>They Found One Of My Graves - Darkthrone</v>
+        <v>Nighttime (feat. Austin Brown &amp; David Shaw) - Tank and the Bangas</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Cloudfall</v>
+        <v>They Found One Of My Graves</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
+        <v>https://music.apple.com/us/song/they-found-one-of-my-graves/1881564857</v>
       </c>
       <c r="D179" t="str">
         <v>2026-05-14</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Cycles in the Infinite Dream</v>
+        <v>Pre-Historic Metal</v>
       </c>
       <c r="G179" t="str">
-        <v>4:06</v>
+        <v>5:14</v>
       </c>
       <c r="H179" t="str">
-        <v>REZN</v>
+        <v>Darkthrone</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
+        <v>https://music.apple.com/us/artist/darkthrone/112417640</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
+        <v>https://music.apple.com/us/album/they-found-one-of-my-graves/1881564845</v>
       </c>
       <c r="L179" t="str">
-        <v>Cloudfall - REZN</v>
+        <v>They Found One Of My Graves - Darkthrone</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Doom in Bloom</v>
+        <v>Cloudfall</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
+        <v>https://music.apple.com/us/song/cloudfall/1892921580</v>
       </c>
       <c r="D180" t="str">
         <v>2026-05-14</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Hum of Hurt</v>
+        <v>Cycles in the Infinite Dream</v>
       </c>
       <c r="G180" t="str">
-        <v>3:17</v>
+        <v>4:06</v>
       </c>
       <c r="H180" t="str">
-        <v>Converge</v>
+        <v>REZN</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/converge/15405383</v>
+        <v>https://music.apple.com/us/artist/rezn/1441800527</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
+        <v>https://music.apple.com/us/album/cloudfall/1892921394</v>
       </c>
       <c r="L180" t="str">
-        <v>Doom in Bloom - Converge</v>
+        <v>Cloudfall - REZN</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Only The Good I Keep</v>
+        <v>Doom in Bloom</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
+        <v>https://music.apple.com/us/song/doom-in-bloom/1883081839</v>
       </c>
       <c r="D181" t="str">
         <v>2026-05-14</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Remember The Humans</v>
+        <v>Hum of Hurt</v>
       </c>
       <c r="G181" t="str">
-        <v>3:27</v>
+        <v>3:17</v>
       </c>
       <c r="H181" t="str">
-        <v>Broken Social Scene</v>
+        <v>Converge</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
+        <v>https://music.apple.com/us/artist/converge/15405383</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
+        <v>https://music.apple.com/us/album/doom-in-bloom/1883081837</v>
       </c>
       <c r="L181" t="str">
-        <v>Only The Good I Keep - Broken Social Scene</v>
+        <v>Doom in Bloom - Converge</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Zoom 97</v>
+        <v>Only The Good I Keep</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
+        <v>https://music.apple.com/us/song/only-the-good-i-keep/1871484973</v>
       </c>
       <c r="D182" t="str">
         <v>2026-05-14</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Philadelphia's been good to me</v>
+        <v>Remember The Humans</v>
       </c>
       <c r="G182" t="str">
-        <v>4:54</v>
+        <v>3:27</v>
       </c>
       <c r="H182" t="str">
-        <v>Kurt Vile</v>
+        <v>Broken Social Scene</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
+        <v>https://music.apple.com/us/artist/broken-social-scene/6925799</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
+        <v>https://music.apple.com/us/album/only-the-good-i-keep/1871484971</v>
       </c>
       <c r="L182" t="str">
-        <v>Zoom 97 - Kurt Vile</v>
+        <v>Only The Good I Keep - Broken Social Scene</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Switch Up</v>
+        <v>Zoom 97</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
+        <v>https://music.apple.com/us/song/zoom-97/1884970574</v>
       </c>
       <c r="D183" t="str">
         <v>2026-05-14</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Switch Up - Single</v>
+        <v>Philadelphia's been good to me</v>
       </c>
       <c r="G183" t="str">
-        <v>3:35</v>
+        <v>4:54</v>
       </c>
       <c r="H183" t="str">
-        <v>Mike D</v>
+        <v>Kurt Vile</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
+        <v>https://music.apple.com/us/artist/kurt-vile/274234314</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
+        <v>https://music.apple.com/us/album/zoom-97/1884970572</v>
       </c>
       <c r="L183" t="str">
-        <v>Switch Up - Mike D</v>
+        <v>Zoom 97 - Kurt Vile</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Surprise</v>
+        <v>Switch Up</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/surprise/1894873625</v>
+        <v>https://music.apple.com/us/song/switch-up/6764419407</v>
       </c>
       <c r="D184" t="str">
         <v>2026-05-14</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Doe Or Die III</v>
+        <v>Switch Up - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:48</v>
+        <v>3:35</v>
       </c>
       <c r="H184" t="str">
-        <v>AZ</v>
+        <v>Mike D</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/az/35299</v>
+        <v>https://music.apple.com/us/artist/mike-d/1646443127</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/surprise/1894873352</v>
+        <v>https://music.apple.com/us/album/switch-up/1895772278</v>
       </c>
       <c r="L184" t="str">
-        <v>Surprise - AZ</v>
+        <v>Switch Up - Mike D</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Better Days</v>
+        <v>Surprise</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/better-days/6763394083</v>
+        <v>https://music.apple.com/us/song/surprise/1894873625</v>
       </c>
       <c r="D185" t="str">
         <v>2026-05-14</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Better Days - Single</v>
+        <v>Doe Or Die III</v>
       </c>
       <c r="G185" t="str">
-        <v>3:22</v>
+        <v>2:48</v>
       </c>
       <c r="H185" t="str">
-        <v>Naomi Sharon</v>
+        <v>AZ</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
+        <v>https://music.apple.com/us/artist/az/35299</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/better-days/1895293758</v>
+        <v>https://music.apple.com/us/album/surprise/1894873352</v>
       </c>
       <c r="L185" t="str">
-        <v>Better Days - Naomi Sharon</v>
+        <v>Surprise - AZ</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Where Have All The Good Men Gone?</v>
+        <v>Better Days</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
+        <v>https://music.apple.com/us/song/better-days/6763394083</v>
       </c>
       <c r="D186" t="str">
         <v>2026-05-14</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Where Have All The Good Men Gone? - EP</v>
+        <v>Better Days - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:14</v>
+        <v>3:22</v>
       </c>
       <c r="H186" t="str">
-        <v>Debbii Dawson</v>
+        <v>Naomi Sharon</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
+        <v>https://music.apple.com/us/artist/naomi-sharon/1459356994</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
+        <v>https://music.apple.com/us/album/better-days/1895293758</v>
       </c>
       <c r="L186" t="str">
-        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
+        <v>Better Days - Naomi Sharon</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>No Pressure</v>
+        <v>Where Have All The Good Men Gone?</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
+        <v>https://music.apple.com/us/song/where-have-all-the-good-men-gone/6765484424</v>
       </c>
       <c r="D187" t="str">
         <v>2026-05-14</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>No Pressure - Single</v>
+        <v>Where Have All The Good Men Gone? - EP</v>
       </c>
       <c r="G187" t="str">
-        <v>3:09</v>
+        <v>3:14</v>
       </c>
       <c r="H187" t="str">
-        <v>JYT</v>
+        <v>Debbii Dawson</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
+        <v>https://music.apple.com/us/artist/debbii-dawson/1507525420</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
+        <v>https://music.apple.com/us/album/where-have-all-the-good-men-gone/1895967802</v>
       </c>
       <c r="L187" t="str">
-        <v>No Pressure - JYT</v>
+        <v>Where Have All The Good Men Gone? - Debbii Dawson</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>What's the Point!</v>
+        <v>No Pressure</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
+        <v>https://music.apple.com/us/song/no-pressure/6763448750</v>
       </c>
       <c r="D188" t="str">
         <v>2026-05-14</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Night at the Opera - EP</v>
+        <v>No Pressure - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>2:43</v>
+        <v>3:09</v>
       </c>
       <c r="H188" t="str">
-        <v>Emei</v>
+        <v>JYT</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/emei/1583968554</v>
+        <v>https://music.apple.com/us/artist/jyt/1058722413</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
+        <v>https://music.apple.com/us/album/no-pressure/1895321101</v>
       </c>
       <c r="L188" t="str">
-        <v>What's the Point! - Emei</v>
+        <v>No Pressure - JYT</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Pachamama</v>
+        <v>What's the Point!</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
+        <v>https://music.apple.com/us/song/whats-the-point/1886811061</v>
       </c>
       <c r="D189" t="str">
         <v>2026-05-14</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Así Es La Vida</v>
+        <v>Night at the Opera - EP</v>
       </c>
       <c r="G189" t="str">
-        <v>3:20</v>
+        <v>2:43</v>
       </c>
       <c r="H189" t="str">
-        <v>Codiciado</v>
+        <v>Emei</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/emei/1583968554</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
+        <v>https://music.apple.com/us/album/whats-the-point/1886811055</v>
       </c>
       <c r="L189" t="str">
-        <v>Pachamama - Codiciado</v>
+        <v>What's the Point! - Emei</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Multiplied</v>
+        <v>Pachamama</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
+        <v>https://music.apple.com/us/song/pachamama/1893815453</v>
       </c>
       <c r="D190" t="str">
         <v>2026-05-14</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Multiplied - Single</v>
+        <v>Así Es La Vida</v>
       </c>
       <c r="G190" t="str">
-        <v>3:02</v>
+        <v>3:20</v>
       </c>
       <c r="H190" t="str">
-        <v>Luna Li</v>
+        <v>Codiciado</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
+        <v>https://music.apple.com/us/album/pachamama/1893815448</v>
       </c>
       <c r="L190" t="str">
-        <v>Multiplied - Luna Li</v>
+        <v>Pachamama - Codiciado</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Six String</v>
+        <v>Multiplied</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/six-string/1892171728</v>
+        <v>https://music.apple.com/us/song/multiplied/1889977459</v>
       </c>
       <c r="D191" t="str">
         <v>2026-05-14</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Six String - Single</v>
+        <v>Multiplied - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H191" t="str">
-        <v>Lila Dupont</v>
+        <v>Luna Li</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
+        <v>https://music.apple.com/us/artist/luna-li/1242663809</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/six-string/1892171725</v>
+        <v>https://music.apple.com/us/album/multiplied/1889977458</v>
       </c>
       <c r="L191" t="str">
-        <v>Six String - Lila Dupont</v>
+        <v>Multiplied - Luna Li</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Take Heart</v>
+        <v>Six String</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
+        <v>https://music.apple.com/us/song/six-string/1892171728</v>
       </c>
       <c r="D192" t="str">
         <v>2026-05-14</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Harbour</v>
+        <v>Six String - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>4:07</v>
+        <v>3:11</v>
       </c>
       <c r="H192" t="str">
-        <v>Jon Bryant</v>
+        <v>Lila Dupont</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
+        <v>https://music.apple.com/us/artist/lila-dupont/1508792561</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
+        <v>https://music.apple.com/us/album/six-string/1892171725</v>
       </c>
       <c r="L192" t="str">
-        <v>Take Heart - Jon Bryant</v>
+        <v>Six String - Lila Dupont</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Clarion</v>
+        <v>Take Heart</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/clarion/1887589702</v>
+        <v>https://music.apple.com/us/song/take-heart/1877993013</v>
       </c>
       <c r="D193" t="str">
         <v>2026-05-14</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>You Are Spring!</v>
+        <v>Harbour</v>
       </c>
       <c r="G193" t="str">
-        <v>3:23</v>
+        <v>4:07</v>
       </c>
       <c r="H193" t="str">
-        <v>Tasha</v>
+        <v>Jon Bryant</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/jon-bryant/341294359</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/clarion/1887589690</v>
+        <v>https://music.apple.com/us/album/take-heart/1877992810</v>
       </c>
       <c r="L193" t="str">
-        <v>Clarion - Tasha</v>
+        <v>Take Heart - Jon Bryant</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Stepping Stone</v>
+        <v>Clarion</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
+        <v>https://music.apple.com/us/song/clarion/1887589702</v>
       </c>
       <c r="D194" t="str">
         <v>2026-05-14</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Beams - Single</v>
+        <v>You Are Spring!</v>
       </c>
       <c r="G194" t="str">
-        <v>2:49</v>
+        <v>3:23</v>
       </c>
       <c r="H194" t="str">
-        <v>DERBY</v>
+        <v>Tasha</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/derby/1772719795</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
+        <v>https://music.apple.com/us/album/clarion/1887589690</v>
       </c>
       <c r="L194" t="str">
-        <v>Stepping Stone - DERBY</v>
+        <v>Clarion - Tasha</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>confessions part iii</v>
+        <v>Stepping Stone</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
+        <v>https://music.apple.com/us/song/stepping-stone/1889387056</v>
       </c>
       <c r="D195" t="str">
         <v>2026-05-14</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>autogratis</v>
+        <v>Beams - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>2:01</v>
+        <v>2:49</v>
       </c>
       <c r="H195" t="str">
-        <v>Chanpan</v>
+        <v>DERBY</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
+        <v>https://music.apple.com/us/artist/derby/1772719795</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
+        <v>https://music.apple.com/us/album/stepping-stone/1889387054</v>
       </c>
       <c r="L195" t="str">
-        <v>confessions part iii - Chanpan</v>
+        <v>Stepping Stone - DERBY</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>cherry garcia</v>
+        <v>confessions part iii</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
+        <v>https://music.apple.com/us/song/confessions-part-iii/1892181989</v>
       </c>
       <c r="D196" t="str">
         <v>2026-05-14</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>cherry garcia - Single</v>
+        <v>autogratis</v>
       </c>
       <c r="G196" t="str">
-        <v>2:30</v>
+        <v>2:01</v>
       </c>
       <c r="H196" t="str">
-        <v>supermodel*</v>
+        <v>Chanpan</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
+        <v>https://music.apple.com/us/artist/chanpan/1704417748</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
+        <v>https://music.apple.com/us/album/confessions-part-iii/1892181981</v>
       </c>
       <c r="L196" t="str">
-        <v>cherry garcia - supermodel*</v>
+        <v>confessions part iii - Chanpan</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Disco Cherry</v>
+        <v>cherry garcia</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
+        <v>https://music.apple.com/us/song/cherry-garcia/1885000655</v>
       </c>
       <c r="D197" t="str">
         <v>2026-05-14</v>
@@ -7861,36 +7861,36 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Disco Cherry - Single</v>
+        <v>cherry garcia - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:20</v>
+        <v>2:30</v>
       </c>
       <c r="H197" t="str">
-        <v>Purple Disco Machine</v>
+        <v>supermodel*</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
+        <v>https://music.apple.com/us/artist/supermodel/1817515489</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
+        <v>https://music.apple.com/us/album/cherry-garcia/1885000654</v>
       </c>
       <c r="L197" t="str">
-        <v>Disco Cherry - Purple Disco Machine</v>
+        <v>cherry garcia - supermodel*</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Tal Vez</v>
+        <v>Disco Cherry</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
+        <v>https://music.apple.com/us/song/disco-cherry/1890195881</v>
       </c>
       <c r="D198" t="str">
         <v>2026-05-14</v>
@@ -7899,36 +7899,36 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>El Amante</v>
+        <v>Disco Cherry - Single</v>
       </c>
       <c r="G198" t="str">
-        <v>2:14</v>
+        <v>3:20</v>
       </c>
       <c r="H198" t="str">
-        <v>Dariel Amant</v>
+        <v>Purple Disco Machine</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
+        <v>https://music.apple.com/us/artist/purple-disco-machine/357397685</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
+        <v>https://music.apple.com/us/album/disco-cherry/1890195880</v>
       </c>
       <c r="L198" t="str">
-        <v>Tal Vez - Dariel Amant</v>
+        <v>Disco Cherry - Purple Disco Machine</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>The Voyager</v>
+        <v>Tal Vez</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
+        <v>https://music.apple.com/us/song/tal-vez/1894892261</v>
       </c>
       <c r="D199" t="str">
         <v>2026-05-14</v>
@@ -7937,36 +7937,36 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>The Voyager - Single</v>
+        <v>El Amante</v>
       </c>
       <c r="G199" t="str">
-        <v>4:37</v>
+        <v>2:14</v>
       </c>
       <c r="H199" t="str">
-        <v>Chance Peña</v>
+        <v>Dariel Amant</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
+        <v>https://music.apple.com/us/artist/dariel-amant/1595935945</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
+        <v>https://music.apple.com/us/album/tal-vez/1894892257</v>
       </c>
       <c r="L199" t="str">
-        <v>The Voyager - Chance Peña</v>
+        <v>Tal Vez - Dariel Amant</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
+        <v>https://music.apple.com/us/song/the-voyager/6764897214</v>
       </c>
       <c r="D200" t="str">
         <v>2026-05-14</v>
@@ -7975,36 +7975,36 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Pictures of You</v>
+        <v>The Voyager - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:34</v>
+        <v>4:37</v>
       </c>
       <c r="H200" t="str">
-        <v>Buffalo Traffic Jam</v>
+        <v>Chance Peña</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
+        <v>https://music.apple.com/us/artist/chance-pe%C3%B1a/1042737143</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
+        <v>https://music.apple.com/us/album/the-voyager/1895954206</v>
       </c>
       <c r="L200" t="str">
-        <v>Pictures of You - Buffalo Traffic Jam</v>
+        <v>The Voyager - Chance Peña</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Buy What U Want</v>
+        <v>Pictures of You</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
+        <v>https://music.apple.com/us/song/pictures-of-you/6764176261</v>
       </c>
       <c r="D201" t="str">
         <v>2026-05-14</v>
@@ -8013,36 +8013,36 @@
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>Road To Osshland: The Series</v>
+        <v>Pictures of You</v>
       </c>
       <c r="G201" t="str">
-        <v>3:47</v>
+        <v>3:34</v>
       </c>
       <c r="H201" t="str">
-        <v>Black Fortune</v>
+        <v>Buffalo Traffic Jam</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
+        <v>https://music.apple.com/us/artist/buffalo-traffic-jam/1744636210</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
+        <v>https://music.apple.com/us/album/pictures-of-you/1895672454</v>
       </c>
       <c r="L201" t="str">
-        <v>Buy What U Want - Black Fortune</v>
+        <v>Pictures of You - Buffalo Traffic Jam</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>MOOD BRAZIL</v>
+        <v>Buy What U Want</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
+        <v>https://music.apple.com/us/song/buy-what-u-want/6763137223</v>
       </c>
       <c r="D202" t="str">
         <v>2026-05-14</v>
@@ -8051,36 +8051,36 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>MOOD BRAZIL - Single</v>
+        <v>Road To Osshland: The Series</v>
       </c>
       <c r="G202" t="str">
-        <v>2:29</v>
+        <v>3:47</v>
       </c>
       <c r="H202" t="str">
-        <v>Lil Naay</v>
+        <v>Black Fortune</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
+        <v>https://music.apple.com/us/artist/black-fortune/557044567</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
+        <v>https://music.apple.com/us/album/buy-what-u-want/1895178841</v>
       </c>
       <c r="L202" t="str">
-        <v>MOOD BRAZIL - Lil Naay</v>
+        <v>Buy What U Want - Black Fortune</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>high school sweetheart</v>
+        <v>MOOD BRAZIL</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
+        <v>https://music.apple.com/us/song/mood-brazil/6766985126</v>
       </c>
       <c r="D203" t="str">
         <v>2026-05-14</v>
@@ -8089,36 +8089,36 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>ashley cooke</v>
+        <v>MOOD BRAZIL - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:11</v>
+        <v>2:29</v>
       </c>
       <c r="H203" t="str">
-        <v>Ashley Cooke</v>
+        <v>Lil Naay</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
+        <v>https://music.apple.com/us/artist/lil-naay/1513690516</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
+        <v>https://music.apple.com/us/album/mood-brazil/6766984734</v>
       </c>
       <c r="L203" t="str">
-        <v>high school sweetheart - Ashley Cooke</v>
+        <v>MOOD BRAZIL - Lil Naay</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
+        <v>high school sweetheart</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
+        <v>https://music.apple.com/us/song/high-school-sweetheart/6763491151</v>
       </c>
       <c r="D204" t="str">
         <v>2026-05-14</v>
@@ -8127,36 +8127,36 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
+        <v>ashley cooke</v>
       </c>
       <c r="G204" t="str">
-        <v>2:55</v>
+        <v>3:11</v>
       </c>
       <c r="H204" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ashley Cooke</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ashley-cooke/346835058</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
+        <v>https://music.apple.com/us/album/high-school-sweetheart/1895339553</v>
       </c>
       <c r="L204" t="str">
-        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
+        <v>high school sweetheart - Ashley Cooke</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>big plans</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad)</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
+        <v>https://music.apple.com/us/song/vibe-responsibly-feat-isaiah-rashad/6766279282</v>
       </c>
       <c r="D205" t="str">
         <v>2026-05-14</v>
@@ -8165,36 +8165,36 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>counting horses</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:14</v>
+        <v>2:55</v>
       </c>
       <c r="H205" t="str">
-        <v>Tom Siletto</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
+        <v>https://music.apple.com/us/album/vibe-responsibly-feat-isaiah-rashad/1896264288</v>
       </c>
       <c r="L205" t="str">
-        <v>big plans - Tom Siletto</v>
+        <v>Vibe Responsibly (feat. Isaiah Rashad) - Ray Vaughn</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Running</v>
+        <v>big plans</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/running/6764878724</v>
+        <v>https://music.apple.com/us/song/big-plans/1893684291</v>
       </c>
       <c r="D206" t="str">
         <v>2026-05-14</v>
@@ -8203,68 +8203,106 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Running - Single</v>
+        <v>counting horses</v>
       </c>
       <c r="G206" t="str">
-        <v>2:38</v>
+        <v>3:14</v>
       </c>
       <c r="H206" t="str">
-        <v>Kameron Marlowe</v>
+        <v>Tom Siletto</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+        <v>https://music.apple.com/us/artist/tom-siletto/1530304047</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/running/1895947036</v>
+        <v>https://music.apple.com/us/album/big-plans/1893684101</v>
       </c>
       <c r="L206" t="str">
-        <v>Running - Kameron Marlowe</v>
+        <v>big plans - Tom Siletto</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
+        <v>Running</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/running/6764878724</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Running - Single</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2:38</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Kameron Marlowe</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/kameron-marlowe/1467288596</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/running/1895947036</v>
+      </c>
+      <c r="L207" t="str">
+        <v>Running - Kameron Marlowe</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
         <v>FA-TAL!</v>
       </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
         <v>https://music.apple.com/us/song/fa-tal/6764684234</v>
       </c>
-      <c r="D207" t="str">
-        <v>2026-05-14</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
+      <c r="D208" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
         <v>FA-TAL! - Single</v>
       </c>
-      <c r="G207" t="str">
+      <c r="G208" t="str">
         <v>2:46</v>
       </c>
-      <c r="H207" t="str">
+      <c r="H208" t="str">
         <v>ROBI</v>
       </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
         <v>https://music.apple.com/us/artist/robi/1458047972</v>
       </c>
-      <c r="K207" t="str">
+      <c r="K208" t="str">
         <v>https://music.apple.com/us/album/fa-tal/1895877867</v>
       </c>
-      <c r="L207" t="str">
+      <c r="L208" t="str">
         <v>FA-TAL! - ROBI</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -667,7 +667,7 @@
         <v>The Head And The Heart - Grace (Official Music Video)</v>
       </c>
       <c r="B8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C8" t="str">
         <v>https://www.youtube.com/watch?v=zpdtoIbKUxY</v>
@@ -679,7 +679,7 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -1845,7 +1845,7 @@
         <v>Dagny - Closet Disco Queen (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C39" t="str">
         <v>https://www.youtube.com/watch?v=G_4K2sbeyA4</v>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1883,7 +1883,7 @@
         <v>Purple Disco Machine - Disco Cherry (Official Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C40" t="str">
         <v>https://www.youtube.com/watch?v=GTgR8ks88Yw</v>
@@ -1895,7 +1895,7 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -3365,7 +3365,7 @@
         <v>Matthew Ifield - Thinking (Official Video)</v>
       </c>
       <c r="B79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C79" t="str">
         <v>https://www.youtube.com/watch?v=nFmhsDVOm5U</v>
@@ -3377,7 +3377,7 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>13 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G79" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/global/2026-05-week02/titles.xlsx
@@ -1769,7 +1769,7 @@
         <v>The Last Dinner Party - Big Dog (On The Road)</v>
       </c>
       <c r="B37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C37" t="str">
         <v>https://www.youtube.com/watch?v=tCnvd5QYEns</v>
@@ -1781,7 +1781,7 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1807,7 +1807,7 @@
         <v>OCEAN ALLEY - HOLD ON (Official Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C38" t="str">
         <v>https://www.youtube.com/watch?v=Fduq3t9y5Bg</v>
@@ -1819,7 +1819,7 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G38" t="str">
         <v/>
